--- a/modelo_simulador.xlsx
+++ b/modelo_simulador.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L03569417\Downloads\simulador_matricula_base_real_v55\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L03569417\Downloads\simulador_matricula_base_real_v56\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{484BE5A7-7C2A-4F14-854B-1C09E846426A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDC00D4D-BBCC-4796-975C-6F044F5EA54D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEEME" sheetId="1" r:id="rId1"/>

--- a/modelo_simulador.xlsx
+++ b/modelo_simulador.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L03569417\Downloads\simulador_matricula_base_real_v70\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D77F4A2B-1EBB-49E8-8FBD-116E23780B98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C962B84-0C50-43E0-844A-5FC2378B43BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="12" activeTab="14" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="12" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEEME" sheetId="1" r:id="rId1"/>
@@ -2543,10 +2543,14 @@
     <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2561,10 +2565,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2823,7 +2823,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="5.5" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="38"/>
@@ -2835,7 +2835,7 @@
       <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:8" ht="6.75" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="38"/>
@@ -3001,7 +3001,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="4.9000000000000004" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="47" t="s">
         <v>170</v>
       </c>
       <c r="B1" s="38"/>
@@ -7762,7 +7762,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="4.9000000000000004" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="47" t="s">
         <v>343</v>
       </c>
       <c r="B1" s="38"/>
@@ -11710,7 +11710,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="4.9000000000000004" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="47" t="s">
         <v>353</v>
       </c>
       <c r="B1" s="38"/>
@@ -16368,7 +16368,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="4.9000000000000004" customHeight="1">
-      <c r="A1" s="45" t="s">
+      <c r="A1" s="47" t="s">
         <v>617</v>
       </c>
       <c r="B1" s="38"/>
@@ -16452,9 +16452,7 @@
       <c r="G4" s="19">
         <v>117</v>
       </c>
-      <c r="H4" s="20">
-        <v>0.2</v>
-      </c>
+      <c r="H4" s="20"/>
       <c r="I4" s="19" t="s">
         <v>628</v>
       </c>
@@ -25903,7 +25901,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="37" t="s">
         <v>715</v>
       </c>
       <c r="B1" s="38"/>
@@ -25917,18 +25915,18 @@
       <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="47" t="s">
+      <c r="A2" s="39" t="s">
         <v>716</v>
       </c>
-      <c r="B2" s="47"/>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
+      <c r="B2" s="39"/>
+      <c r="C2" s="39"/>
+      <c r="D2" s="39"/>
+      <c r="E2" s="39"/>
+      <c r="F2" s="39"/>
+      <c r="G2" s="39"/>
+      <c r="H2" s="39"/>
+      <c r="I2" s="39"/>
+      <c r="J2" s="39"/>
     </row>
     <row r="3" spans="1:10" ht="28">
       <c r="A3" s="36" t="s">
@@ -28694,7 +28692,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="5.5" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>34</v>
       </c>
       <c r="B1" s="38"/>
@@ -28706,7 +28704,7 @@
       <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:17" ht="6.75" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>35</v>
       </c>
       <c r="B2" s="38"/>
@@ -29052,21 +29050,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="5.5" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>96</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
       <c r="D1" s="38"/>
       <c r="E1" s="38"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="40"/>
-      <c r="H1" s="40"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="42"/>
+      <c r="H1" s="42"/>
       <c r="I1" s="38"/>
       <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>97</v>
       </c>
       <c r="B2" s="38"/>
@@ -59631,21 +59629,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="5.5" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>107</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
       <c r="D1" s="38"/>
       <c r="E1" s="38"/>
-      <c r="F1" s="40"/>
-      <c r="G1" s="41"/>
+      <c r="F1" s="42"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="38"/>
       <c r="I1" s="38"/>
       <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>108</v>
       </c>
       <c r="B2" s="38"/>
@@ -65248,7 +65246,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="5.5" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>113</v>
       </c>
       <c r="B1" s="38"/>
@@ -65256,13 +65254,13 @@
       <c r="D1" s="38"/>
       <c r="E1" s="38"/>
       <c r="F1" s="38"/>
-      <c r="G1" s="41"/>
+      <c r="G1" s="43"/>
       <c r="H1" s="38"/>
       <c r="I1" s="38"/>
       <c r="J1" s="38"/>
     </row>
     <row r="2" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>114</v>
       </c>
       <c r="B2" s="38"/>
@@ -75575,19 +75573,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="5.5" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>120</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
       <c r="D1" s="38"/>
-      <c r="E1" s="42"/>
+      <c r="E1" s="44"/>
       <c r="F1" s="38"/>
       <c r="G1" s="38"/>
       <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:8" ht="6.75" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>121</v>
       </c>
       <c r="B2" s="38"/>
@@ -80302,20 +80300,20 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="5.5" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>124</v>
       </c>
       <c r="B1" s="38"/>
       <c r="C1" s="38"/>
       <c r="D1" s="38"/>
       <c r="E1" s="38"/>
-      <c r="F1" s="41"/>
+      <c r="F1" s="43"/>
       <c r="G1" s="38"/>
       <c r="H1" s="38"/>
       <c r="I1" s="38"/>
     </row>
     <row r="2" spans="1:9" ht="6.75" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>125</v>
       </c>
       <c r="B2" s="38"/>
@@ -87745,7 +87743,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="5.5" customHeight="1">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="40" t="s">
         <v>128</v>
       </c>
       <c r="B1" s="38"/>
@@ -87757,7 +87755,7 @@
       <c r="H1" s="38"/>
     </row>
     <row r="2" spans="1:8" ht="6.75" customHeight="1">
-      <c r="A2" s="39" t="s">
+      <c r="A2" s="41" t="s">
         <v>129</v>
       </c>
       <c r="B2" s="38"/>
@@ -87844,11 +87842,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="4.9000000000000004" customHeight="1">
-      <c r="A1" s="43" t="s">
+      <c r="A1" s="45" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="44"/>
-      <c r="C1" s="44"/>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
       <c r="E1" s="29" t="s">
         <v>639</v>
       </c>

--- a/modelo_simulador.xlsx
+++ b/modelo_simulador.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L03569417\Downloads\simulador_matricula_base_real_v75(1)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\L03569417\Downloads\simulador_matricula_base_real_v90\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD1CB8C3-334C-404B-AD6D-B08F7FB9EA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D26DB316-CB9C-4B89-A819-4997B266CE90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" firstSheet="10" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LEEME" sheetId="1" r:id="rId1"/>
@@ -2571,10 +2571,14 @@
     <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -2587,14 +2591,10 @@
     <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2614,18 +2614,7 @@
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="tbl_base_ni_ri" displayName="tbl_base_ni_ri" ref="A4:J1000">
-  <autoFilter ref="A4:J1000" xr:uid="{00000000-0009-0000-0100-000001000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="2026"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="3">
-      <filters>
-        <filter val="Profesional"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A4:J1000" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}"/>
   <tableColumns count="10">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="anio"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="periodo"/>
@@ -2863,28 +2852,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="5.5" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:8" ht="6.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="4" spans="1:8" ht="6.4" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -3041,14 +3030,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="4.9000000000000004" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="39" t="s">
         <v>170</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="3" spans="1:6" ht="4.4000000000000004" customHeight="1">
       <c r="A3" s="17" t="s">
@@ -7802,14 +7791,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="4.9000000000000004" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="39" t="s">
         <v>343</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
     </row>
     <row r="3" spans="1:6" ht="4.4000000000000004" customHeight="1">
       <c r="A3" s="17" t="s">
@@ -11750,14 +11739,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="4.9000000000000004" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="39" t="s">
         <v>353</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
       <c r="H1" s="28" t="s">
         <v>354</v>
       </c>
@@ -16408,17 +16397,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="4.9000000000000004" customHeight="1">
-      <c r="A1" s="46" t="s">
+      <c r="A1" s="39" t="s">
         <v>617</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
       <c r="J1" s="23" t="s">
         <v>618</v>
       </c>
@@ -16838,7 +16827,7 @@
       <c r="G18">
         <v>107</v>
       </c>
-      <c r="H18" s="49">
+      <c r="H18" s="38">
         <v>1E-3</v>
       </c>
     </row>
@@ -17320,7 +17309,7 @@
       <c r="G38">
         <v>95</v>
       </c>
-      <c r="H38" s="49">
+      <c r="H38" s="38">
         <v>1E-3</v>
       </c>
     </row>
@@ -18284,7 +18273,7 @@
       <c r="G78">
         <v>98</v>
       </c>
-      <c r="H78" s="49">
+      <c r="H78" s="38">
         <v>1E-3</v>
       </c>
     </row>
@@ -26023,32 +26012,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="18">
-      <c r="A1" s="47" t="s">
+      <c r="A1" s="48" t="s">
         <v>715</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10" ht="30.65" customHeight="1">
-      <c r="A2" s="48" t="s">
+      <c r="A2" s="49" t="s">
         <v>716</v>
       </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="48"/>
-      <c r="G2" s="48"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="48"/>
-      <c r="J2" s="48"/>
+      <c r="B2" s="49"/>
+      <c r="C2" s="49"/>
+      <c r="D2" s="49"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="49"/>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
     </row>
     <row r="3" spans="1:10" ht="28">
       <c r="A3" s="37" t="s">
@@ -29394,28 +29383,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="5.5" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:17" ht="6.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>35</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="4" spans="1:17" ht="6.4" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -29752,32 +29741,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="5.5" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="41"/>
-      <c r="H1" s="41"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>97</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="4" spans="1:10" ht="6.4" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -29811,7 +29800,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1">
+    <row r="5" spans="1:10">
       <c r="A5" s="2">
         <v>2030</v>
       </c>
@@ -29845,7 +29834,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1">
+    <row r="6" spans="1:10">
       <c r="A6" s="5">
         <v>2031</v>
       </c>
@@ -29879,7 +29868,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1">
+    <row r="7" spans="1:10">
       <c r="A7" s="5">
         <v>2032</v>
       </c>
@@ -29913,7 +29902,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1">
+    <row r="8" spans="1:10">
       <c r="A8" s="5">
         <v>2033</v>
       </c>
@@ -29947,7 +29936,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1">
+    <row r="9" spans="1:10">
       <c r="A9" s="5">
         <v>2034</v>
       </c>
@@ -29981,7 +29970,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1">
+    <row r="10" spans="1:10">
       <c r="A10" s="5">
         <v>2035</v>
       </c>
@@ -30015,7 +30004,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1">
+    <row r="11" spans="1:10">
       <c r="A11" s="5">
         <v>2036</v>
       </c>
@@ -30049,7 +30038,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1">
+    <row r="12" spans="1:10">
       <c r="A12" s="5">
         <v>2037</v>
       </c>
@@ -30083,7 +30072,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1">
+    <row r="13" spans="1:10">
       <c r="A13" s="5">
         <v>2038</v>
       </c>
@@ -30117,7 +30106,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1">
+    <row r="14" spans="1:10">
       <c r="A14" s="5">
         <v>2039</v>
       </c>
@@ -30151,7 +30140,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1">
+    <row r="15" spans="1:10">
       <c r="A15" s="5">
         <v>2040</v>
       </c>
@@ -30185,7 +30174,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1">
+    <row r="16" spans="1:10">
       <c r="A16" s="5">
         <v>2030</v>
       </c>
@@ -30219,7 +30208,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1">
+    <row r="17" spans="1:10">
       <c r="A17" s="5">
         <v>2031</v>
       </c>
@@ -30253,7 +30242,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1">
+    <row r="18" spans="1:10">
       <c r="A18" s="5">
         <v>2032</v>
       </c>
@@ -30287,7 +30276,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1">
+    <row r="19" spans="1:10">
       <c r="A19" s="5">
         <v>2033</v>
       </c>
@@ -30321,7 +30310,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1">
+    <row r="20" spans="1:10">
       <c r="A20" s="5">
         <v>2034</v>
       </c>
@@ -30355,7 +30344,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1">
+    <row r="21" spans="1:10">
       <c r="A21" s="5">
         <v>2035</v>
       </c>
@@ -30389,7 +30378,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1">
+    <row r="22" spans="1:10">
       <c r="A22" s="5">
         <v>2036</v>
       </c>
@@ -30423,7 +30412,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1">
+    <row r="23" spans="1:10">
       <c r="A23" s="5">
         <v>2037</v>
       </c>
@@ -30457,7 +30446,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1">
+    <row r="24" spans="1:10">
       <c r="A24" s="5">
         <v>2038</v>
       </c>
@@ -30491,7 +30480,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1">
+    <row r="25" spans="1:10">
       <c r="A25" s="5">
         <v>2039</v>
       </c>
@@ -30525,7 +30514,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1">
+    <row r="26" spans="1:10">
       <c r="A26" s="5">
         <v>2040</v>
       </c>
@@ -30559,7 +30548,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1">
+    <row r="27" spans="1:10">
       <c r="A27" s="5">
         <v>2030</v>
       </c>
@@ -30579,11 +30568,11 @@
         <v>249.26000000000002</v>
       </c>
       <c r="G27" s="6">
-        <v>300</v>
+        <v>401</v>
       </c>
       <c r="H27" s="12">
         <f>tbl_base_ni_ri[[#This Row],[ni_total]]+tbl_base_ni_ri[[#This Row],[ri_total]]</f>
-        <v>549.26</v>
+        <v>650.26</v>
       </c>
       <c r="I27" s="6" t="str">
         <f t="shared" si="0"/>
@@ -30591,7 +30580,7 @@
       </c>
       <c r="J27" s="7"/>
     </row>
-    <row r="28" spans="1:10" hidden="1">
+    <row r="28" spans="1:10">
       <c r="A28" s="5">
         <v>2031</v>
       </c>
@@ -30611,11 +30600,11 @@
         <v>256.73780000000005</v>
       </c>
       <c r="G28" s="6">
-        <v>307</v>
+        <v>411</v>
       </c>
       <c r="H28" s="12">
         <f>tbl_base_ni_ri[[#This Row],[ni_total]]+tbl_base_ni_ri[[#This Row],[ri_total]]</f>
-        <v>563.73780000000011</v>
+        <v>667.73780000000011</v>
       </c>
       <c r="I28" s="6" t="str">
         <f t="shared" si="0"/>
@@ -30623,7 +30612,7 @@
       </c>
       <c r="J28" s="7"/>
     </row>
-    <row r="29" spans="1:10" hidden="1">
+    <row r="29" spans="1:10">
       <c r="A29" s="5">
         <v>2032</v>
       </c>
@@ -30643,11 +30632,11 @@
         <v>264.43993400000005</v>
       </c>
       <c r="G29" s="6">
-        <v>312</v>
+        <v>418</v>
       </c>
       <c r="H29" s="12">
         <f>tbl_base_ni_ri[[#This Row],[ni_total]]+tbl_base_ni_ri[[#This Row],[ri_total]]</f>
-        <v>576.43993399999999</v>
+        <v>682.43993399999999</v>
       </c>
       <c r="I29" s="6" t="str">
         <f t="shared" si="0"/>
@@ -30655,7 +30644,7 @@
       </c>
       <c r="J29" s="7"/>
     </row>
-    <row r="30" spans="1:10" hidden="1">
+    <row r="30" spans="1:10">
       <c r="A30" s="5">
         <v>2033</v>
       </c>
@@ -30675,11 +30664,11 @@
         <v>272.37313202000007</v>
       </c>
       <c r="G30" s="6">
-        <v>323</v>
+        <v>432</v>
       </c>
       <c r="H30" s="12">
         <f>tbl_base_ni_ri[[#This Row],[ni_total]]+tbl_base_ni_ri[[#This Row],[ri_total]]</f>
-        <v>595.37313202000007</v>
+        <v>704.37313202000007</v>
       </c>
       <c r="I30" s="6" t="str">
         <f t="shared" si="0"/>
@@ -30687,7 +30676,7 @@
       </c>
       <c r="J30" s="7"/>
     </row>
-    <row r="31" spans="1:10" hidden="1">
+    <row r="31" spans="1:10">
       <c r="A31" s="5">
         <v>2034</v>
       </c>
@@ -30707,11 +30696,11 @@
         <v>277.8205946604001</v>
       </c>
       <c r="G31" s="6">
-        <v>345</v>
+        <v>443</v>
       </c>
       <c r="H31" s="12">
         <f>tbl_base_ni_ri[[#This Row],[ni_total]]+tbl_base_ni_ri[[#This Row],[ri_total]]</f>
-        <v>622.82059466040005</v>
+        <v>720.82059466040005</v>
       </c>
       <c r="I31" s="6" t="str">
         <f t="shared" si="0"/>
@@ -30719,7 +30708,7 @@
       </c>
       <c r="J31" s="7"/>
     </row>
-    <row r="32" spans="1:10" hidden="1">
+    <row r="32" spans="1:10">
       <c r="A32" s="5">
         <v>2035</v>
       </c>
@@ -30739,11 +30728,11 @@
         <v>283.37700655360811</v>
       </c>
       <c r="G32" s="6">
-        <v>376</v>
+        <v>454</v>
       </c>
       <c r="H32" s="12">
         <f>tbl_base_ni_ri[[#This Row],[ni_total]]+tbl_base_ni_ri[[#This Row],[ri_total]]</f>
-        <v>659.37700655360811</v>
+        <v>737.37700655360811</v>
       </c>
       <c r="I32" s="6" t="str">
         <f t="shared" si="0"/>
@@ -30751,7 +30740,7 @@
       </c>
       <c r="J32" s="7"/>
     </row>
-    <row r="33" spans="1:10" hidden="1">
+    <row r="33" spans="1:10">
       <c r="A33" s="5">
         <v>2036</v>
       </c>
@@ -30771,11 +30760,11 @@
         <v>289.04454668468026</v>
       </c>
       <c r="G33" s="6">
-        <v>396</v>
+        <v>467</v>
       </c>
       <c r="H33" s="12">
         <f>tbl_base_ni_ri[[#This Row],[ni_total]]+tbl_base_ni_ri[[#This Row],[ri_total]]</f>
-        <v>685.0445466846802</v>
+        <v>756.0445466846802</v>
       </c>
       <c r="I33" s="6" t="str">
         <f t="shared" si="0"/>
@@ -30783,7 +30772,7 @@
       </c>
       <c r="J33" s="7"/>
     </row>
-    <row r="34" spans="1:10" hidden="1">
+    <row r="34" spans="1:10">
       <c r="A34" s="5">
         <v>2037</v>
       </c>
@@ -30803,11 +30792,11 @@
         <v>291.64594760484238</v>
       </c>
       <c r="G34" s="6">
-        <v>412</v>
+        <v>475</v>
       </c>
       <c r="H34" s="12">
         <f>tbl_base_ni_ri[[#This Row],[ni_total]]+tbl_base_ni_ri[[#This Row],[ri_total]]</f>
-        <v>703.64594760484238</v>
+        <v>766.64594760484238</v>
       </c>
       <c r="I34" s="6" t="str">
         <f t="shared" si="0"/>
@@ -30815,7 +30804,7 @@
       </c>
       <c r="J34" s="7"/>
     </row>
-    <row r="35" spans="1:10" hidden="1">
+    <row r="35" spans="1:10">
       <c r="A35" s="5">
         <v>2038</v>
       </c>
@@ -30835,11 +30824,11 @@
         <v>294.27076113328593</v>
       </c>
       <c r="G35" s="6">
-        <v>443</v>
+        <v>482</v>
       </c>
       <c r="H35" s="12">
         <f>tbl_base_ni_ri[[#This Row],[ni_total]]+tbl_base_ni_ri[[#This Row],[ri_total]]</f>
-        <v>737.27076113328599</v>
+        <v>776.27076113328599</v>
       </c>
       <c r="I35" s="6" t="str">
         <f t="shared" si="0"/>
@@ -30847,7 +30836,7 @@
       </c>
       <c r="J35" s="7"/>
     </row>
-    <row r="36" spans="1:10" hidden="1">
+    <row r="36" spans="1:10">
       <c r="A36" s="5">
         <v>2039</v>
       </c>
@@ -30867,11 +30856,11 @@
         <v>296.91919798348545</v>
       </c>
       <c r="G36" s="6">
-        <v>476</v>
+        <v>491</v>
       </c>
       <c r="H36" s="12">
         <f>tbl_base_ni_ri[[#This Row],[ni_total]]+tbl_base_ni_ri[[#This Row],[ri_total]]</f>
-        <v>772.91919798348545</v>
+        <v>787.91919798348545</v>
       </c>
       <c r="I36" s="6" t="str">
         <f t="shared" si="0"/>
@@ -30879,7 +30868,7 @@
       </c>
       <c r="J36" s="7"/>
     </row>
-    <row r="37" spans="1:10" hidden="1">
+    <row r="37" spans="1:10">
       <c r="A37" s="5">
         <v>2040</v>
       </c>
@@ -30911,7 +30900,7 @@
       </c>
       <c r="J37" s="7"/>
     </row>
-    <row r="38" spans="1:10" hidden="1">
+    <row r="38" spans="1:10">
       <c r="A38" s="5">
         <v>2030</v>
       </c>
@@ -30943,7 +30932,7 @@
       </c>
       <c r="J38" s="7"/>
     </row>
-    <row r="39" spans="1:10" hidden="1">
+    <row r="39" spans="1:10">
       <c r="A39" s="5">
         <v>2031</v>
       </c>
@@ -30975,7 +30964,7 @@
       </c>
       <c r="J39" s="7"/>
     </row>
-    <row r="40" spans="1:10" hidden="1">
+    <row r="40" spans="1:10">
       <c r="A40" s="5">
         <v>2032</v>
       </c>
@@ -31007,7 +30996,7 @@
       </c>
       <c r="J40" s="7"/>
     </row>
-    <row r="41" spans="1:10" hidden="1">
+    <row r="41" spans="1:10">
       <c r="A41" s="5">
         <v>2033</v>
       </c>
@@ -31039,7 +31028,7 @@
       </c>
       <c r="J41" s="7"/>
     </row>
-    <row r="42" spans="1:10" hidden="1">
+    <row r="42" spans="1:10">
       <c r="A42" s="5">
         <v>2034</v>
       </c>
@@ -31071,7 +31060,7 @@
       </c>
       <c r="J42" s="7"/>
     </row>
-    <row r="43" spans="1:10" hidden="1">
+    <row r="43" spans="1:10">
       <c r="A43" s="5">
         <v>2035</v>
       </c>
@@ -31103,7 +31092,7 @@
       </c>
       <c r="J43" s="7"/>
     </row>
-    <row r="44" spans="1:10" hidden="1">
+    <row r="44" spans="1:10">
       <c r="A44" s="5">
         <v>2036</v>
       </c>
@@ -31135,7 +31124,7 @@
       </c>
       <c r="J44" s="7"/>
     </row>
-    <row r="45" spans="1:10" hidden="1">
+    <row r="45" spans="1:10">
       <c r="A45" s="5">
         <v>2037</v>
       </c>
@@ -31167,7 +31156,7 @@
       </c>
       <c r="J45" s="7"/>
     </row>
-    <row r="46" spans="1:10" hidden="1">
+    <row r="46" spans="1:10">
       <c r="A46" s="5">
         <v>2038</v>
       </c>
@@ -31199,7 +31188,7 @@
       </c>
       <c r="J46" s="7"/>
     </row>
-    <row r="47" spans="1:10" hidden="1">
+    <row r="47" spans="1:10">
       <c r="A47" s="5">
         <v>2039</v>
       </c>
@@ -31231,7 +31220,7 @@
       </c>
       <c r="J47" s="7"/>
     </row>
-    <row r="48" spans="1:10" hidden="1">
+    <row r="48" spans="1:10">
       <c r="A48" s="5">
         <v>2040</v>
       </c>
@@ -31263,7 +31252,7 @@
       </c>
       <c r="J48" s="7"/>
     </row>
-    <row r="49" spans="1:10" hidden="1">
+    <row r="49" spans="1:10">
       <c r="A49" s="5">
         <v>2030</v>
       </c>
@@ -31295,7 +31284,7 @@
       </c>
       <c r="J49" s="7"/>
     </row>
-    <row r="50" spans="1:10" hidden="1">
+    <row r="50" spans="1:10">
       <c r="A50" s="5">
         <v>2031</v>
       </c>
@@ -31327,7 +31316,7 @@
       </c>
       <c r="J50" s="7"/>
     </row>
-    <row r="51" spans="1:10" hidden="1">
+    <row r="51" spans="1:10">
       <c r="A51" s="5">
         <v>2032</v>
       </c>
@@ -31359,7 +31348,7 @@
       </c>
       <c r="J51" s="7"/>
     </row>
-    <row r="52" spans="1:10" hidden="1">
+    <row r="52" spans="1:10">
       <c r="A52" s="5">
         <v>2033</v>
       </c>
@@ -31391,7 +31380,7 @@
       </c>
       <c r="J52" s="7"/>
     </row>
-    <row r="53" spans="1:10" hidden="1">
+    <row r="53" spans="1:10">
       <c r="A53" s="5">
         <v>2034</v>
       </c>
@@ -31423,7 +31412,7 @@
       </c>
       <c r="J53" s="7"/>
     </row>
-    <row r="54" spans="1:10" hidden="1">
+    <row r="54" spans="1:10">
       <c r="A54" s="5">
         <v>2035</v>
       </c>
@@ -31455,7 +31444,7 @@
       </c>
       <c r="J54" s="7"/>
     </row>
-    <row r="55" spans="1:10" hidden="1">
+    <row r="55" spans="1:10">
       <c r="A55" s="5">
         <v>2036</v>
       </c>
@@ -31487,7 +31476,7 @@
       </c>
       <c r="J55" s="7"/>
     </row>
-    <row r="56" spans="1:10" hidden="1">
+    <row r="56" spans="1:10">
       <c r="A56" s="5">
         <v>2037</v>
       </c>
@@ -31519,7 +31508,7 @@
       </c>
       <c r="J56" s="7"/>
     </row>
-    <row r="57" spans="1:10" hidden="1">
+    <row r="57" spans="1:10">
       <c r="A57" s="5">
         <v>2038</v>
       </c>
@@ -31551,7 +31540,7 @@
       </c>
       <c r="J57" s="7"/>
     </row>
-    <row r="58" spans="1:10" hidden="1">
+    <row r="58" spans="1:10">
       <c r="A58" s="5">
         <v>2039</v>
       </c>
@@ -31583,7 +31572,7 @@
       </c>
       <c r="J58" s="7"/>
     </row>
-    <row r="59" spans="1:10" hidden="1">
+    <row r="59" spans="1:10">
       <c r="A59" s="5">
         <v>2040</v>
       </c>
@@ -31615,7 +31604,7 @@
       </c>
       <c r="J59" s="7"/>
     </row>
-    <row r="60" spans="1:10" hidden="1">
+    <row r="60" spans="1:10">
       <c r="A60" s="5">
         <v>2030</v>
       </c>
@@ -31647,7 +31636,7 @@
       </c>
       <c r="J60" s="7"/>
     </row>
-    <row r="61" spans="1:10" hidden="1">
+    <row r="61" spans="1:10">
       <c r="A61" s="5">
         <v>2031</v>
       </c>
@@ -31679,7 +31668,7 @@
       </c>
       <c r="J61" s="7"/>
     </row>
-    <row r="62" spans="1:10" hidden="1">
+    <row r="62" spans="1:10">
       <c r="A62" s="5">
         <v>2032</v>
       </c>
@@ -31711,7 +31700,7 @@
       </c>
       <c r="J62" s="7"/>
     </row>
-    <row r="63" spans="1:10" hidden="1">
+    <row r="63" spans="1:10">
       <c r="A63" s="5">
         <v>2033</v>
       </c>
@@ -31743,7 +31732,7 @@
       </c>
       <c r="J63" s="7"/>
     </row>
-    <row r="64" spans="1:10" hidden="1">
+    <row r="64" spans="1:10">
       <c r="A64" s="5">
         <v>2034</v>
       </c>
@@ -31775,7 +31764,7 @@
       </c>
       <c r="J64" s="7"/>
     </row>
-    <row r="65" spans="1:10" hidden="1">
+    <row r="65" spans="1:10">
       <c r="A65" s="5">
         <v>2035</v>
       </c>
@@ -31807,7 +31796,7 @@
       </c>
       <c r="J65" s="7"/>
     </row>
-    <row r="66" spans="1:10" hidden="1">
+    <row r="66" spans="1:10">
       <c r="A66" s="5">
         <v>2036</v>
       </c>
@@ -31839,7 +31828,7 @@
       </c>
       <c r="J66" s="7"/>
     </row>
-    <row r="67" spans="1:10" hidden="1">
+    <row r="67" spans="1:10">
       <c r="A67" s="5">
         <v>2037</v>
       </c>
@@ -31871,7 +31860,7 @@
       </c>
       <c r="J67" s="7"/>
     </row>
-    <row r="68" spans="1:10" hidden="1">
+    <row r="68" spans="1:10">
       <c r="A68" s="5">
         <v>2038</v>
       </c>
@@ -31903,7 +31892,7 @@
       </c>
       <c r="J68" s="7"/>
     </row>
-    <row r="69" spans="1:10" hidden="1">
+    <row r="69" spans="1:10">
       <c r="A69" s="5">
         <v>2039</v>
       </c>
@@ -31935,7 +31924,7 @@
       </c>
       <c r="J69" s="7"/>
     </row>
-    <row r="70" spans="1:10" hidden="1">
+    <row r="70" spans="1:10">
       <c r="A70" s="5">
         <v>2040</v>
       </c>
@@ -31967,7 +31956,7 @@
       </c>
       <c r="J70" s="7"/>
     </row>
-    <row r="71" spans="1:10" hidden="1">
+    <row r="71" spans="1:10">
       <c r="A71" s="5">
         <v>2030</v>
       </c>
@@ -31999,7 +31988,7 @@
       </c>
       <c r="J71" s="7"/>
     </row>
-    <row r="72" spans="1:10" hidden="1">
+    <row r="72" spans="1:10">
       <c r="A72" s="5">
         <v>2031</v>
       </c>
@@ -32031,7 +32020,7 @@
       </c>
       <c r="J72" s="7"/>
     </row>
-    <row r="73" spans="1:10" hidden="1">
+    <row r="73" spans="1:10">
       <c r="A73" s="5">
         <v>2032</v>
       </c>
@@ -32063,7 +32052,7 @@
       </c>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:10" hidden="1">
+    <row r="74" spans="1:10">
       <c r="A74" s="5">
         <v>2033</v>
       </c>
@@ -32095,7 +32084,7 @@
       </c>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:10" hidden="1">
+    <row r="75" spans="1:10">
       <c r="A75" s="5">
         <v>2034</v>
       </c>
@@ -32127,7 +32116,7 @@
       </c>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:10" hidden="1">
+    <row r="76" spans="1:10">
       <c r="A76" s="5">
         <v>2035</v>
       </c>
@@ -32159,7 +32148,7 @@
       </c>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:10" hidden="1">
+    <row r="77" spans="1:10">
       <c r="A77" s="5">
         <v>2036</v>
       </c>
@@ -32191,7 +32180,7 @@
       </c>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:10" hidden="1">
+    <row r="78" spans="1:10">
       <c r="A78" s="5">
         <v>2037</v>
       </c>
@@ -32223,7 +32212,7 @@
       </c>
       <c r="J78" s="7"/>
     </row>
-    <row r="79" spans="1:10" hidden="1">
+    <row r="79" spans="1:10">
       <c r="A79" s="5">
         <v>2038</v>
       </c>
@@ -32255,7 +32244,7 @@
       </c>
       <c r="J79" s="7"/>
     </row>
-    <row r="80" spans="1:10" hidden="1">
+    <row r="80" spans="1:10">
       <c r="A80" s="5">
         <v>2039</v>
       </c>
@@ -32287,7 +32276,7 @@
       </c>
       <c r="J80" s="7"/>
     </row>
-    <row r="81" spans="1:10" hidden="1">
+    <row r="81" spans="1:10">
       <c r="A81" s="5">
         <v>2040</v>
       </c>
@@ -32319,7 +32308,7 @@
       </c>
       <c r="J81" s="7"/>
     </row>
-    <row r="82" spans="1:10" hidden="1">
+    <row r="82" spans="1:10">
       <c r="A82" s="5">
         <v>2030</v>
       </c>
@@ -32351,7 +32340,7 @@
       </c>
       <c r="J82" s="7"/>
     </row>
-    <row r="83" spans="1:10" hidden="1">
+    <row r="83" spans="1:10">
       <c r="A83" s="5">
         <v>2031</v>
       </c>
@@ -32383,7 +32372,7 @@
       </c>
       <c r="J83" s="7"/>
     </row>
-    <row r="84" spans="1:10" hidden="1">
+    <row r="84" spans="1:10">
       <c r="A84" s="5">
         <v>2032</v>
       </c>
@@ -32415,7 +32404,7 @@
       </c>
       <c r="J84" s="7"/>
     </row>
-    <row r="85" spans="1:10" hidden="1">
+    <row r="85" spans="1:10">
       <c r="A85" s="5">
         <v>2033</v>
       </c>
@@ -32447,7 +32436,7 @@
       </c>
       <c r="J85" s="7"/>
     </row>
-    <row r="86" spans="1:10" hidden="1">
+    <row r="86" spans="1:10">
       <c r="A86" s="5">
         <v>2034</v>
       </c>
@@ -32479,7 +32468,7 @@
       </c>
       <c r="J86" s="7"/>
     </row>
-    <row r="87" spans="1:10" hidden="1">
+    <row r="87" spans="1:10">
       <c r="A87" s="5">
         <v>2035</v>
       </c>
@@ -32511,7 +32500,7 @@
       </c>
       <c r="J87" s="7"/>
     </row>
-    <row r="88" spans="1:10" hidden="1">
+    <row r="88" spans="1:10">
       <c r="A88" s="5">
         <v>2036</v>
       </c>
@@ -32543,7 +32532,7 @@
       </c>
       <c r="J88" s="7"/>
     </row>
-    <row r="89" spans="1:10" hidden="1">
+    <row r="89" spans="1:10">
       <c r="A89" s="5">
         <v>2037</v>
       </c>
@@ -32575,7 +32564,7 @@
       </c>
       <c r="J89" s="7"/>
     </row>
-    <row r="90" spans="1:10" hidden="1">
+    <row r="90" spans="1:10">
       <c r="A90" s="5">
         <v>2038</v>
       </c>
@@ -32607,7 +32596,7 @@
       </c>
       <c r="J90" s="7"/>
     </row>
-    <row r="91" spans="1:10" hidden="1">
+    <row r="91" spans="1:10">
       <c r="A91" s="5">
         <v>2039</v>
       </c>
@@ -32639,7 +32628,7 @@
       </c>
       <c r="J91" s="7"/>
     </row>
-    <row r="92" spans="1:10" hidden="1">
+    <row r="92" spans="1:10">
       <c r="A92" s="5">
         <v>2040</v>
       </c>
@@ -32671,7 +32660,7 @@
       </c>
       <c r="J92" s="7"/>
     </row>
-    <row r="93" spans="1:10" hidden="1">
+    <row r="93" spans="1:10">
       <c r="A93" s="5">
         <v>2030</v>
       </c>
@@ -32703,7 +32692,7 @@
       </c>
       <c r="J93" s="7"/>
     </row>
-    <row r="94" spans="1:10" hidden="1">
+    <row r="94" spans="1:10">
       <c r="A94" s="5">
         <v>2031</v>
       </c>
@@ -32735,7 +32724,7 @@
       </c>
       <c r="J94" s="7"/>
     </row>
-    <row r="95" spans="1:10" hidden="1">
+    <row r="95" spans="1:10">
       <c r="A95" s="5">
         <v>2032</v>
       </c>
@@ -32767,7 +32756,7 @@
       </c>
       <c r="J95" s="7"/>
     </row>
-    <row r="96" spans="1:10" hidden="1">
+    <row r="96" spans="1:10">
       <c r="A96" s="5">
         <v>2033</v>
       </c>
@@ -32799,7 +32788,7 @@
       </c>
       <c r="J96" s="7"/>
     </row>
-    <row r="97" spans="1:10" hidden="1">
+    <row r="97" spans="1:10">
       <c r="A97" s="5">
         <v>2034</v>
       </c>
@@ -32831,7 +32820,7 @@
       </c>
       <c r="J97" s="7"/>
     </row>
-    <row r="98" spans="1:10" hidden="1">
+    <row r="98" spans="1:10">
       <c r="A98" s="5">
         <v>2035</v>
       </c>
@@ -32863,7 +32852,7 @@
       </c>
       <c r="J98" s="7"/>
     </row>
-    <row r="99" spans="1:10" hidden="1">
+    <row r="99" spans="1:10">
       <c r="A99" s="5">
         <v>2036</v>
       </c>
@@ -32895,7 +32884,7 @@
       </c>
       <c r="J99" s="7"/>
     </row>
-    <row r="100" spans="1:10" hidden="1">
+    <row r="100" spans="1:10">
       <c r="A100" s="5">
         <v>2037</v>
       </c>
@@ -32927,7 +32916,7 @@
       </c>
       <c r="J100" s="7"/>
     </row>
-    <row r="101" spans="1:10" hidden="1">
+    <row r="101" spans="1:10">
       <c r="A101" s="5">
         <v>2038</v>
       </c>
@@ -32959,7 +32948,7 @@
       </c>
       <c r="J101" s="7"/>
     </row>
-    <row r="102" spans="1:10" hidden="1">
+    <row r="102" spans="1:10">
       <c r="A102" s="5">
         <v>2039</v>
       </c>
@@ -32991,7 +32980,7 @@
       </c>
       <c r="J102" s="7"/>
     </row>
-    <row r="103" spans="1:10" hidden="1">
+    <row r="103" spans="1:10">
       <c r="A103" s="5">
         <v>2040</v>
       </c>
@@ -33023,7 +33012,7 @@
       </c>
       <c r="J103" s="7"/>
     </row>
-    <row r="104" spans="1:10" hidden="1">
+    <row r="104" spans="1:10">
       <c r="A104" s="5">
         <v>2030</v>
       </c>
@@ -33055,7 +33044,7 @@
       </c>
       <c r="J104" s="7"/>
     </row>
-    <row r="105" spans="1:10" hidden="1">
+    <row r="105" spans="1:10">
       <c r="A105" s="5">
         <v>2031</v>
       </c>
@@ -33087,7 +33076,7 @@
       </c>
       <c r="J105" s="7"/>
     </row>
-    <row r="106" spans="1:10" hidden="1">
+    <row r="106" spans="1:10">
       <c r="A106" s="5">
         <v>2032</v>
       </c>
@@ -33119,7 +33108,7 @@
       </c>
       <c r="J106" s="7"/>
     </row>
-    <row r="107" spans="1:10" hidden="1">
+    <row r="107" spans="1:10">
       <c r="A107" s="5">
         <v>2033</v>
       </c>
@@ -33151,7 +33140,7 @@
       </c>
       <c r="J107" s="7"/>
     </row>
-    <row r="108" spans="1:10" hidden="1">
+    <row r="108" spans="1:10">
       <c r="A108" s="5">
         <v>2034</v>
       </c>
@@ -33183,7 +33172,7 @@
       </c>
       <c r="J108" s="7"/>
     </row>
-    <row r="109" spans="1:10" hidden="1">
+    <row r="109" spans="1:10">
       <c r="A109" s="5">
         <v>2035</v>
       </c>
@@ -33215,7 +33204,7 @@
       </c>
       <c r="J109" s="7"/>
     </row>
-    <row r="110" spans="1:10" hidden="1">
+    <row r="110" spans="1:10">
       <c r="A110" s="5">
         <v>2036</v>
       </c>
@@ -33247,7 +33236,7 @@
       </c>
       <c r="J110" s="7"/>
     </row>
-    <row r="111" spans="1:10" hidden="1">
+    <row r="111" spans="1:10">
       <c r="A111" s="5">
         <v>2037</v>
       </c>
@@ -33279,7 +33268,7 @@
       </c>
       <c r="J111" s="7"/>
     </row>
-    <row r="112" spans="1:10" hidden="1">
+    <row r="112" spans="1:10">
       <c r="A112" s="5">
         <v>2038</v>
       </c>
@@ -33311,7 +33300,7 @@
       </c>
       <c r="J112" s="7"/>
     </row>
-    <row r="113" spans="1:10" hidden="1">
+    <row r="113" spans="1:10">
       <c r="A113" s="5">
         <v>2039</v>
       </c>
@@ -33343,7 +33332,7 @@
       </c>
       <c r="J113" s="7"/>
     </row>
-    <row r="114" spans="1:10" hidden="1">
+    <row r="114" spans="1:10">
       <c r="A114" s="5">
         <v>2040</v>
       </c>
@@ -33375,7 +33364,7 @@
       </c>
       <c r="J114" s="7"/>
     </row>
-    <row r="115" spans="1:10" hidden="1">
+    <row r="115" spans="1:10">
       <c r="A115" s="5">
         <v>2030</v>
       </c>
@@ -33407,7 +33396,7 @@
       </c>
       <c r="J115" s="7"/>
     </row>
-    <row r="116" spans="1:10" hidden="1">
+    <row r="116" spans="1:10">
       <c r="A116" s="5">
         <v>2031</v>
       </c>
@@ -33439,7 +33428,7 @@
       </c>
       <c r="J116" s="7"/>
     </row>
-    <row r="117" spans="1:10" hidden="1">
+    <row r="117" spans="1:10">
       <c r="A117" s="5">
         <v>2032</v>
       </c>
@@ -33471,7 +33460,7 @@
       </c>
       <c r="J117" s="7"/>
     </row>
-    <row r="118" spans="1:10" hidden="1">
+    <row r="118" spans="1:10">
       <c r="A118" s="5">
         <v>2033</v>
       </c>
@@ -33503,7 +33492,7 @@
       </c>
       <c r="J118" s="7"/>
     </row>
-    <row r="119" spans="1:10" hidden="1">
+    <row r="119" spans="1:10">
       <c r="A119" s="5">
         <v>2034</v>
       </c>
@@ -33535,7 +33524,7 @@
       </c>
       <c r="J119" s="7"/>
     </row>
-    <row r="120" spans="1:10" hidden="1">
+    <row r="120" spans="1:10">
       <c r="A120" s="5">
         <v>2035</v>
       </c>
@@ -33567,7 +33556,7 @@
       </c>
       <c r="J120" s="7"/>
     </row>
-    <row r="121" spans="1:10" hidden="1">
+    <row r="121" spans="1:10">
       <c r="A121" s="5">
         <v>2036</v>
       </c>
@@ -33599,7 +33588,7 @@
       </c>
       <c r="J121" s="7"/>
     </row>
-    <row r="122" spans="1:10" hidden="1">
+    <row r="122" spans="1:10">
       <c r="A122" s="5">
         <v>2037</v>
       </c>
@@ -33631,7 +33620,7 @@
       </c>
       <c r="J122" s="7"/>
     </row>
-    <row r="123" spans="1:10" hidden="1">
+    <row r="123" spans="1:10">
       <c r="A123" s="5">
         <v>2038</v>
       </c>
@@ -33663,7 +33652,7 @@
       </c>
       <c r="J123" s="7"/>
     </row>
-    <row r="124" spans="1:10" hidden="1">
+    <row r="124" spans="1:10">
       <c r="A124" s="5">
         <v>2039</v>
       </c>
@@ -33695,7 +33684,7 @@
       </c>
       <c r="J124" s="7"/>
     </row>
-    <row r="125" spans="1:10" hidden="1">
+    <row r="125" spans="1:10">
       <c r="A125" s="5">
         <v>2040</v>
       </c>
@@ -33727,7 +33716,7 @@
       </c>
       <c r="J125" s="7"/>
     </row>
-    <row r="126" spans="1:10" hidden="1">
+    <row r="126" spans="1:10">
       <c r="A126" s="5">
         <v>2030</v>
       </c>
@@ -33759,7 +33748,7 @@
       </c>
       <c r="J126" s="7"/>
     </row>
-    <row r="127" spans="1:10" hidden="1">
+    <row r="127" spans="1:10">
       <c r="A127" s="5">
         <v>2031</v>
       </c>
@@ -33791,7 +33780,7 @@
       </c>
       <c r="J127" s="7"/>
     </row>
-    <row r="128" spans="1:10" hidden="1">
+    <row r="128" spans="1:10">
       <c r="A128" s="5">
         <v>2032</v>
       </c>
@@ -33823,7 +33812,7 @@
       </c>
       <c r="J128" s="7"/>
     </row>
-    <row r="129" spans="1:10" hidden="1">
+    <row r="129" spans="1:10">
       <c r="A129" s="5">
         <v>2033</v>
       </c>
@@ -33855,7 +33844,7 @@
       </c>
       <c r="J129" s="7"/>
     </row>
-    <row r="130" spans="1:10" hidden="1">
+    <row r="130" spans="1:10">
       <c r="A130" s="5">
         <v>2034</v>
       </c>
@@ -33887,7 +33876,7 @@
       </c>
       <c r="J130" s="7"/>
     </row>
-    <row r="131" spans="1:10" hidden="1">
+    <row r="131" spans="1:10">
       <c r="A131" s="5">
         <v>2035</v>
       </c>
@@ -33919,7 +33908,7 @@
       </c>
       <c r="J131" s="7"/>
     </row>
-    <row r="132" spans="1:10" hidden="1">
+    <row r="132" spans="1:10">
       <c r="A132" s="5">
         <v>2036</v>
       </c>
@@ -33951,7 +33940,7 @@
       </c>
       <c r="J132" s="7"/>
     </row>
-    <row r="133" spans="1:10" hidden="1">
+    <row r="133" spans="1:10">
       <c r="A133" s="5">
         <v>2037</v>
       </c>
@@ -33983,7 +33972,7 @@
       </c>
       <c r="J133" s="7"/>
     </row>
-    <row r="134" spans="1:10" hidden="1">
+    <row r="134" spans="1:10">
       <c r="A134" s="5">
         <v>2038</v>
       </c>
@@ -34015,7 +34004,7 @@
       </c>
       <c r="J134" s="7"/>
     </row>
-    <row r="135" spans="1:10" hidden="1">
+    <row r="135" spans="1:10">
       <c r="A135" s="5">
         <v>2039</v>
       </c>
@@ -34047,7 +34036,7 @@
       </c>
       <c r="J135" s="7"/>
     </row>
-    <row r="136" spans="1:10" hidden="1">
+    <row r="136" spans="1:10">
       <c r="A136" s="5">
         <v>2040</v>
       </c>
@@ -34079,7 +34068,7 @@
       </c>
       <c r="J136" s="7"/>
     </row>
-    <row r="137" spans="1:10" hidden="1">
+    <row r="137" spans="1:10">
       <c r="A137" s="5">
         <v>2030</v>
       </c>
@@ -34111,7 +34100,7 @@
       </c>
       <c r="J137" s="7"/>
     </row>
-    <row r="138" spans="1:10" hidden="1">
+    <row r="138" spans="1:10">
       <c r="A138" s="5">
         <v>2031</v>
       </c>
@@ -34143,7 +34132,7 @@
       </c>
       <c r="J138" s="7"/>
     </row>
-    <row r="139" spans="1:10" hidden="1">
+    <row r="139" spans="1:10">
       <c r="A139" s="5">
         <v>2032</v>
       </c>
@@ -34175,7 +34164,7 @@
       </c>
       <c r="J139" s="7"/>
     </row>
-    <row r="140" spans="1:10" hidden="1">
+    <row r="140" spans="1:10">
       <c r="A140" s="5">
         <v>2033</v>
       </c>
@@ -34207,7 +34196,7 @@
       </c>
       <c r="J140" s="7"/>
     </row>
-    <row r="141" spans="1:10" hidden="1">
+    <row r="141" spans="1:10">
       <c r="A141" s="5">
         <v>2034</v>
       </c>
@@ -34239,7 +34228,7 @@
       </c>
       <c r="J141" s="7"/>
     </row>
-    <row r="142" spans="1:10" hidden="1">
+    <row r="142" spans="1:10">
       <c r="A142" s="5">
         <v>2035</v>
       </c>
@@ -34271,7 +34260,7 @@
       </c>
       <c r="J142" s="7"/>
     </row>
-    <row r="143" spans="1:10" hidden="1">
+    <row r="143" spans="1:10">
       <c r="A143" s="5">
         <v>2036</v>
       </c>
@@ -34303,7 +34292,7 @@
       </c>
       <c r="J143" s="7"/>
     </row>
-    <row r="144" spans="1:10" hidden="1">
+    <row r="144" spans="1:10">
       <c r="A144" s="5">
         <v>2037</v>
       </c>
@@ -34335,7 +34324,7 @@
       </c>
       <c r="J144" s="7"/>
     </row>
-    <row r="145" spans="1:10" hidden="1">
+    <row r="145" spans="1:10">
       <c r="A145" s="5">
         <v>2038</v>
       </c>
@@ -34367,7 +34356,7 @@
       </c>
       <c r="J145" s="7"/>
     </row>
-    <row r="146" spans="1:10" hidden="1">
+    <row r="146" spans="1:10">
       <c r="A146" s="5">
         <v>2039</v>
       </c>
@@ -34399,7 +34388,7 @@
       </c>
       <c r="J146" s="7"/>
     </row>
-    <row r="147" spans="1:10" hidden="1">
+    <row r="147" spans="1:10">
       <c r="A147" s="5">
         <v>2040</v>
       </c>
@@ -34431,7 +34420,7 @@
       </c>
       <c r="J147" s="7"/>
     </row>
-    <row r="148" spans="1:10" hidden="1">
+    <row r="148" spans="1:10">
       <c r="A148" s="5">
         <v>2030</v>
       </c>
@@ -34463,7 +34452,7 @@
       </c>
       <c r="J148" s="7"/>
     </row>
-    <row r="149" spans="1:10" hidden="1">
+    <row r="149" spans="1:10">
       <c r="A149" s="5">
         <v>2031</v>
       </c>
@@ -34495,7 +34484,7 @@
       </c>
       <c r="J149" s="7"/>
     </row>
-    <row r="150" spans="1:10" hidden="1">
+    <row r="150" spans="1:10">
       <c r="A150" s="5">
         <v>2032</v>
       </c>
@@ -34527,7 +34516,7 @@
       </c>
       <c r="J150" s="7"/>
     </row>
-    <row r="151" spans="1:10" hidden="1">
+    <row r="151" spans="1:10">
       <c r="A151" s="5">
         <v>2033</v>
       </c>
@@ -34559,7 +34548,7 @@
       </c>
       <c r="J151" s="7"/>
     </row>
-    <row r="152" spans="1:10" hidden="1">
+    <row r="152" spans="1:10">
       <c r="A152" s="5">
         <v>2034</v>
       </c>
@@ -34591,7 +34580,7 @@
       </c>
       <c r="J152" s="7"/>
     </row>
-    <row r="153" spans="1:10" hidden="1">
+    <row r="153" spans="1:10">
       <c r="A153" s="5">
         <v>2035</v>
       </c>
@@ -34623,7 +34612,7 @@
       </c>
       <c r="J153" s="7"/>
     </row>
-    <row r="154" spans="1:10" hidden="1">
+    <row r="154" spans="1:10">
       <c r="A154" s="5">
         <v>2036</v>
       </c>
@@ -34655,7 +34644,7 @@
       </c>
       <c r="J154" s="7"/>
     </row>
-    <row r="155" spans="1:10" hidden="1">
+    <row r="155" spans="1:10">
       <c r="A155" s="5">
         <v>2037</v>
       </c>
@@ -34687,7 +34676,7 @@
       </c>
       <c r="J155" s="7"/>
     </row>
-    <row r="156" spans="1:10" hidden="1">
+    <row r="156" spans="1:10">
       <c r="A156" s="5">
         <v>2038</v>
       </c>
@@ -34719,7 +34708,7 @@
       </c>
       <c r="J156" s="7"/>
     </row>
-    <row r="157" spans="1:10" hidden="1">
+    <row r="157" spans="1:10">
       <c r="A157" s="5">
         <v>2039</v>
       </c>
@@ -34751,7 +34740,7 @@
       </c>
       <c r="J157" s="7"/>
     </row>
-    <row r="158" spans="1:10" hidden="1">
+    <row r="158" spans="1:10">
       <c r="A158" s="5">
         <v>2040</v>
       </c>
@@ -34783,7 +34772,7 @@
       </c>
       <c r="J158" s="7"/>
     </row>
-    <row r="159" spans="1:10" hidden="1">
+    <row r="159" spans="1:10">
       <c r="A159" s="5">
         <v>2030</v>
       </c>
@@ -34815,7 +34804,7 @@
       </c>
       <c r="J159" s="7"/>
     </row>
-    <row r="160" spans="1:10" hidden="1">
+    <row r="160" spans="1:10">
       <c r="A160" s="5">
         <v>2031</v>
       </c>
@@ -34847,7 +34836,7 @@
       </c>
       <c r="J160" s="7"/>
     </row>
-    <row r="161" spans="1:10" hidden="1">
+    <row r="161" spans="1:10">
       <c r="A161" s="5">
         <v>2032</v>
       </c>
@@ -34879,7 +34868,7 @@
       </c>
       <c r="J161" s="7"/>
     </row>
-    <row r="162" spans="1:10" hidden="1">
+    <row r="162" spans="1:10">
       <c r="A162" s="5">
         <v>2033</v>
       </c>
@@ -34911,7 +34900,7 @@
       </c>
       <c r="J162" s="7"/>
     </row>
-    <row r="163" spans="1:10" hidden="1">
+    <row r="163" spans="1:10">
       <c r="A163" s="5">
         <v>2034</v>
       </c>
@@ -34943,7 +34932,7 @@
       </c>
       <c r="J163" s="7"/>
     </row>
-    <row r="164" spans="1:10" hidden="1">
+    <row r="164" spans="1:10">
       <c r="A164" s="5">
         <v>2035</v>
       </c>
@@ -34975,7 +34964,7 @@
       </c>
       <c r="J164" s="7"/>
     </row>
-    <row r="165" spans="1:10" hidden="1">
+    <row r="165" spans="1:10">
       <c r="A165" s="5">
         <v>2036</v>
       </c>
@@ -35007,7 +34996,7 @@
       </c>
       <c r="J165" s="7"/>
     </row>
-    <row r="166" spans="1:10" hidden="1">
+    <row r="166" spans="1:10">
       <c r="A166" s="5">
         <v>2037</v>
       </c>
@@ -35039,7 +35028,7 @@
       </c>
       <c r="J166" s="7"/>
     </row>
-    <row r="167" spans="1:10" hidden="1">
+    <row r="167" spans="1:10">
       <c r="A167" s="5">
         <v>2038</v>
       </c>
@@ -35071,7 +35060,7 @@
       </c>
       <c r="J167" s="7"/>
     </row>
-    <row r="168" spans="1:10" hidden="1">
+    <row r="168" spans="1:10">
       <c r="A168" s="5">
         <v>2039</v>
       </c>
@@ -35103,7 +35092,7 @@
       </c>
       <c r="J168" s="7"/>
     </row>
-    <row r="169" spans="1:10" hidden="1">
+    <row r="169" spans="1:10">
       <c r="A169" s="5">
         <v>2040</v>
       </c>
@@ -35135,7 +35124,7 @@
       </c>
       <c r="J169" s="7"/>
     </row>
-    <row r="170" spans="1:10" hidden="1">
+    <row r="170" spans="1:10">
       <c r="A170" s="5">
         <v>2030</v>
       </c>
@@ -35167,7 +35156,7 @@
       </c>
       <c r="J170" s="7"/>
     </row>
-    <row r="171" spans="1:10" hidden="1">
+    <row r="171" spans="1:10">
       <c r="A171" s="5">
         <v>2031</v>
       </c>
@@ -35199,7 +35188,7 @@
       </c>
       <c r="J171" s="7"/>
     </row>
-    <row r="172" spans="1:10" hidden="1">
+    <row r="172" spans="1:10">
       <c r="A172" s="5">
         <v>2032</v>
       </c>
@@ -35231,7 +35220,7 @@
       </c>
       <c r="J172" s="7"/>
     </row>
-    <row r="173" spans="1:10" hidden="1">
+    <row r="173" spans="1:10">
       <c r="A173" s="5">
         <v>2033</v>
       </c>
@@ -35263,7 +35252,7 @@
       </c>
       <c r="J173" s="7"/>
     </row>
-    <row r="174" spans="1:10" hidden="1">
+    <row r="174" spans="1:10">
       <c r="A174" s="5">
         <v>2034</v>
       </c>
@@ -35295,7 +35284,7 @@
       </c>
       <c r="J174" s="7"/>
     </row>
-    <row r="175" spans="1:10" hidden="1">
+    <row r="175" spans="1:10">
       <c r="A175" s="5">
         <v>2035</v>
       </c>
@@ -35327,7 +35316,7 @@
       </c>
       <c r="J175" s="7"/>
     </row>
-    <row r="176" spans="1:10" hidden="1">
+    <row r="176" spans="1:10">
       <c r="A176" s="5">
         <v>2036</v>
       </c>
@@ -35359,7 +35348,7 @@
       </c>
       <c r="J176" s="7"/>
     </row>
-    <row r="177" spans="1:10" hidden="1">
+    <row r="177" spans="1:10">
       <c r="A177" s="5">
         <v>2037</v>
       </c>
@@ -35391,7 +35380,7 @@
       </c>
       <c r="J177" s="7"/>
     </row>
-    <row r="178" spans="1:10" hidden="1">
+    <row r="178" spans="1:10">
       <c r="A178" s="5">
         <v>2038</v>
       </c>
@@ -35423,7 +35412,7 @@
       </c>
       <c r="J178" s="7"/>
     </row>
-    <row r="179" spans="1:10" hidden="1">
+    <row r="179" spans="1:10">
       <c r="A179" s="5">
         <v>2039</v>
       </c>
@@ -35455,7 +35444,7 @@
       </c>
       <c r="J179" s="7"/>
     </row>
-    <row r="180" spans="1:10" hidden="1">
+    <row r="180" spans="1:10">
       <c r="A180" s="5">
         <v>2040</v>
       </c>
@@ -35487,7 +35476,7 @@
       </c>
       <c r="J180" s="7"/>
     </row>
-    <row r="181" spans="1:10" hidden="1">
+    <row r="181" spans="1:10">
       <c r="A181" s="5">
         <v>2030</v>
       </c>
@@ -35519,7 +35508,7 @@
       </c>
       <c r="J181" s="7"/>
     </row>
-    <row r="182" spans="1:10" hidden="1">
+    <row r="182" spans="1:10">
       <c r="A182" s="5">
         <v>2031</v>
       </c>
@@ -35551,7 +35540,7 @@
       </c>
       <c r="J182" s="7"/>
     </row>
-    <row r="183" spans="1:10" hidden="1">
+    <row r="183" spans="1:10">
       <c r="A183" s="5">
         <v>2032</v>
       </c>
@@ -35583,7 +35572,7 @@
       </c>
       <c r="J183" s="7"/>
     </row>
-    <row r="184" spans="1:10" hidden="1">
+    <row r="184" spans="1:10">
       <c r="A184" s="5">
         <v>2033</v>
       </c>
@@ -35615,7 +35604,7 @@
       </c>
       <c r="J184" s="7"/>
     </row>
-    <row r="185" spans="1:10" hidden="1">
+    <row r="185" spans="1:10">
       <c r="A185" s="5">
         <v>2034</v>
       </c>
@@ -35647,7 +35636,7 @@
       </c>
       <c r="J185" s="7"/>
     </row>
-    <row r="186" spans="1:10" hidden="1">
+    <row r="186" spans="1:10">
       <c r="A186" s="5">
         <v>2035</v>
       </c>
@@ -35679,7 +35668,7 @@
       </c>
       <c r="J186" s="7"/>
     </row>
-    <row r="187" spans="1:10" hidden="1">
+    <row r="187" spans="1:10">
       <c r="A187" s="5">
         <v>2036</v>
       </c>
@@ -35711,7 +35700,7 @@
       </c>
       <c r="J187" s="7"/>
     </row>
-    <row r="188" spans="1:10" hidden="1">
+    <row r="188" spans="1:10">
       <c r="A188" s="5">
         <v>2037</v>
       </c>
@@ -35743,7 +35732,7 @@
       </c>
       <c r="J188" s="7"/>
     </row>
-    <row r="189" spans="1:10" hidden="1">
+    <row r="189" spans="1:10">
       <c r="A189" s="5">
         <v>2038</v>
       </c>
@@ -35775,7 +35764,7 @@
       </c>
       <c r="J189" s="7"/>
     </row>
-    <row r="190" spans="1:10" hidden="1">
+    <row r="190" spans="1:10">
       <c r="A190" s="5">
         <v>2039</v>
       </c>
@@ -35807,7 +35796,7 @@
       </c>
       <c r="J190" s="7"/>
     </row>
-    <row r="191" spans="1:10" hidden="1">
+    <row r="191" spans="1:10">
       <c r="A191" s="5">
         <v>2040</v>
       </c>
@@ -35839,7 +35828,7 @@
       </c>
       <c r="J191" s="7"/>
     </row>
-    <row r="192" spans="1:10" hidden="1">
+    <row r="192" spans="1:10">
       <c r="A192" s="5">
         <v>2030</v>
       </c>
@@ -35871,7 +35860,7 @@
       </c>
       <c r="J192" s="7"/>
     </row>
-    <row r="193" spans="1:10" hidden="1">
+    <row r="193" spans="1:10">
       <c r="A193" s="5">
         <v>2031</v>
       </c>
@@ -35903,7 +35892,7 @@
       </c>
       <c r="J193" s="7"/>
     </row>
-    <row r="194" spans="1:10" hidden="1">
+    <row r="194" spans="1:10">
       <c r="A194" s="5">
         <v>2032</v>
       </c>
@@ -35935,7 +35924,7 @@
       </c>
       <c r="J194" s="7"/>
     </row>
-    <row r="195" spans="1:10" hidden="1">
+    <row r="195" spans="1:10">
       <c r="A195" s="5">
         <v>2033</v>
       </c>
@@ -35967,7 +35956,7 @@
       </c>
       <c r="J195" s="7"/>
     </row>
-    <row r="196" spans="1:10" hidden="1">
+    <row r="196" spans="1:10">
       <c r="A196" s="5">
         <v>2034</v>
       </c>
@@ -35999,7 +35988,7 @@
       </c>
       <c r="J196" s="7"/>
     </row>
-    <row r="197" spans="1:10" hidden="1">
+    <row r="197" spans="1:10">
       <c r="A197" s="5">
         <v>2035</v>
       </c>
@@ -36031,7 +36020,7 @@
       </c>
       <c r="J197" s="7"/>
     </row>
-    <row r="198" spans="1:10" hidden="1">
+    <row r="198" spans="1:10">
       <c r="A198" s="5">
         <v>2036</v>
       </c>
@@ -36063,7 +36052,7 @@
       </c>
       <c r="J198" s="7"/>
     </row>
-    <row r="199" spans="1:10" hidden="1">
+    <row r="199" spans="1:10">
       <c r="A199" s="5">
         <v>2037</v>
       </c>
@@ -36095,7 +36084,7 @@
       </c>
       <c r="J199" s="7"/>
     </row>
-    <row r="200" spans="1:10" hidden="1">
+    <row r="200" spans="1:10">
       <c r="A200" s="5">
         <v>2038</v>
       </c>
@@ -36127,7 +36116,7 @@
       </c>
       <c r="J200" s="7"/>
     </row>
-    <row r="201" spans="1:10" hidden="1">
+    <row r="201" spans="1:10">
       <c r="A201" s="5">
         <v>2039</v>
       </c>
@@ -36159,7 +36148,7 @@
       </c>
       <c r="J201" s="7"/>
     </row>
-    <row r="202" spans="1:10" hidden="1">
+    <row r="202" spans="1:10">
       <c r="A202" s="5">
         <v>2040</v>
       </c>
@@ -36191,7 +36180,7 @@
       </c>
       <c r="J202" s="7"/>
     </row>
-    <row r="203" spans="1:10" hidden="1">
+    <row r="203" spans="1:10">
       <c r="A203" s="5">
         <v>2030</v>
       </c>
@@ -36223,7 +36212,7 @@
       </c>
       <c r="J203" s="7"/>
     </row>
-    <row r="204" spans="1:10" hidden="1">
+    <row r="204" spans="1:10">
       <c r="A204" s="5">
         <v>2031</v>
       </c>
@@ -36255,7 +36244,7 @@
       </c>
       <c r="J204" s="7"/>
     </row>
-    <row r="205" spans="1:10" hidden="1">
+    <row r="205" spans="1:10">
       <c r="A205" s="5">
         <v>2032</v>
       </c>
@@ -36287,7 +36276,7 @@
       </c>
       <c r="J205" s="7"/>
     </row>
-    <row r="206" spans="1:10" hidden="1">
+    <row r="206" spans="1:10">
       <c r="A206" s="5">
         <v>2033</v>
       </c>
@@ -36319,7 +36308,7 @@
       </c>
       <c r="J206" s="7"/>
     </row>
-    <row r="207" spans="1:10" hidden="1">
+    <row r="207" spans="1:10">
       <c r="A207" s="5">
         <v>2034</v>
       </c>
@@ -36351,7 +36340,7 @@
       </c>
       <c r="J207" s="7"/>
     </row>
-    <row r="208" spans="1:10" hidden="1">
+    <row r="208" spans="1:10">
       <c r="A208" s="5">
         <v>2035</v>
       </c>
@@ -36383,7 +36372,7 @@
       </c>
       <c r="J208" s="7"/>
     </row>
-    <row r="209" spans="1:10" hidden="1">
+    <row r="209" spans="1:10">
       <c r="A209" s="5">
         <v>2036</v>
       </c>
@@ -36415,7 +36404,7 @@
       </c>
       <c r="J209" s="7"/>
     </row>
-    <row r="210" spans="1:10" hidden="1">
+    <row r="210" spans="1:10">
       <c r="A210" s="5">
         <v>2037</v>
       </c>
@@ -36447,7 +36436,7 @@
       </c>
       <c r="J210" s="7"/>
     </row>
-    <row r="211" spans="1:10" hidden="1">
+    <row r="211" spans="1:10">
       <c r="A211" s="5">
         <v>2038</v>
       </c>
@@ -36479,7 +36468,7 @@
       </c>
       <c r="J211" s="7"/>
     </row>
-    <row r="212" spans="1:10" hidden="1">
+    <row r="212" spans="1:10">
       <c r="A212" s="5">
         <v>2039</v>
       </c>
@@ -36511,7 +36500,7 @@
       </c>
       <c r="J212" s="7"/>
     </row>
-    <row r="213" spans="1:10" hidden="1">
+    <row r="213" spans="1:10">
       <c r="A213" s="5">
         <v>2040</v>
       </c>
@@ -36543,7 +36532,7 @@
       </c>
       <c r="J213" s="7"/>
     </row>
-    <row r="214" spans="1:10" hidden="1">
+    <row r="214" spans="1:10">
       <c r="A214" s="5">
         <v>2030</v>
       </c>
@@ -36575,7 +36564,7 @@
       </c>
       <c r="J214" s="7"/>
     </row>
-    <row r="215" spans="1:10" hidden="1">
+    <row r="215" spans="1:10">
       <c r="A215" s="5">
         <v>2031</v>
       </c>
@@ -36607,7 +36596,7 @@
       </c>
       <c r="J215" s="7"/>
     </row>
-    <row r="216" spans="1:10" hidden="1">
+    <row r="216" spans="1:10">
       <c r="A216" s="5">
         <v>2032</v>
       </c>
@@ -36639,7 +36628,7 @@
       </c>
       <c r="J216" s="7"/>
     </row>
-    <row r="217" spans="1:10" hidden="1">
+    <row r="217" spans="1:10">
       <c r="A217" s="5">
         <v>2033</v>
       </c>
@@ -36671,7 +36660,7 @@
       </c>
       <c r="J217" s="7"/>
     </row>
-    <row r="218" spans="1:10" hidden="1">
+    <row r="218" spans="1:10">
       <c r="A218" s="5">
         <v>2034</v>
       </c>
@@ -36703,7 +36692,7 @@
       </c>
       <c r="J218" s="7"/>
     </row>
-    <row r="219" spans="1:10" hidden="1">
+    <row r="219" spans="1:10">
       <c r="A219" s="5">
         <v>2035</v>
       </c>
@@ -36735,7 +36724,7 @@
       </c>
       <c r="J219" s="7"/>
     </row>
-    <row r="220" spans="1:10" hidden="1">
+    <row r="220" spans="1:10">
       <c r="A220" s="5">
         <v>2036</v>
       </c>
@@ -36767,7 +36756,7 @@
       </c>
       <c r="J220" s="7"/>
     </row>
-    <row r="221" spans="1:10" hidden="1">
+    <row r="221" spans="1:10">
       <c r="A221" s="5">
         <v>2037</v>
       </c>
@@ -36799,7 +36788,7 @@
       </c>
       <c r="J221" s="7"/>
     </row>
-    <row r="222" spans="1:10" hidden="1">
+    <row r="222" spans="1:10">
       <c r="A222" s="5">
         <v>2038</v>
       </c>
@@ -36831,7 +36820,7 @@
       </c>
       <c r="J222" s="7"/>
     </row>
-    <row r="223" spans="1:10" hidden="1">
+    <row r="223" spans="1:10">
       <c r="A223" s="5">
         <v>2039</v>
       </c>
@@ -36863,7 +36852,7 @@
       </c>
       <c r="J223" s="7"/>
     </row>
-    <row r="224" spans="1:10" hidden="1">
+    <row r="224" spans="1:10">
       <c r="A224" s="5">
         <v>2040</v>
       </c>
@@ -36895,7 +36884,7 @@
       </c>
       <c r="J224" s="7"/>
     </row>
-    <row r="225" spans="1:10" hidden="1">
+    <row r="225" spans="1:10">
       <c r="A225" s="5">
         <v>2030</v>
       </c>
@@ -36927,7 +36916,7 @@
       </c>
       <c r="J225" s="7"/>
     </row>
-    <row r="226" spans="1:10" hidden="1">
+    <row r="226" spans="1:10">
       <c r="A226" s="5">
         <v>2031</v>
       </c>
@@ -36959,7 +36948,7 @@
       </c>
       <c r="J226" s="7"/>
     </row>
-    <row r="227" spans="1:10" hidden="1">
+    <row r="227" spans="1:10">
       <c r="A227" s="5">
         <v>2032</v>
       </c>
@@ -36991,7 +36980,7 @@
       </c>
       <c r="J227" s="7"/>
     </row>
-    <row r="228" spans="1:10" hidden="1">
+    <row r="228" spans="1:10">
       <c r="A228" s="5">
         <v>2033</v>
       </c>
@@ -37023,7 +37012,7 @@
       </c>
       <c r="J228" s="7"/>
     </row>
-    <row r="229" spans="1:10" hidden="1">
+    <row r="229" spans="1:10">
       <c r="A229" s="5">
         <v>2034</v>
       </c>
@@ -37055,7 +37044,7 @@
       </c>
       <c r="J229" s="7"/>
     </row>
-    <row r="230" spans="1:10" hidden="1">
+    <row r="230" spans="1:10">
       <c r="A230" s="5">
         <v>2035</v>
       </c>
@@ -37087,7 +37076,7 @@
       </c>
       <c r="J230" s="7"/>
     </row>
-    <row r="231" spans="1:10" hidden="1">
+    <row r="231" spans="1:10">
       <c r="A231" s="5">
         <v>2036</v>
       </c>
@@ -37119,7 +37108,7 @@
       </c>
       <c r="J231" s="7"/>
     </row>
-    <row r="232" spans="1:10" hidden="1">
+    <row r="232" spans="1:10">
       <c r="A232" s="5">
         <v>2037</v>
       </c>
@@ -37151,7 +37140,7 @@
       </c>
       <c r="J232" s="7"/>
     </row>
-    <row r="233" spans="1:10" hidden="1">
+    <row r="233" spans="1:10">
       <c r="A233" s="5">
         <v>2038</v>
       </c>
@@ -37183,7 +37172,7 @@
       </c>
       <c r="J233" s="7"/>
     </row>
-    <row r="234" spans="1:10" hidden="1">
+    <row r="234" spans="1:10">
       <c r="A234" s="5">
         <v>2039</v>
       </c>
@@ -37215,7 +37204,7 @@
       </c>
       <c r="J234" s="7"/>
     </row>
-    <row r="235" spans="1:10" hidden="1">
+    <row r="235" spans="1:10">
       <c r="A235" s="5">
         <v>2040</v>
       </c>
@@ -37247,7 +37236,7 @@
       </c>
       <c r="J235" s="7"/>
     </row>
-    <row r="236" spans="1:10" hidden="1">
+    <row r="236" spans="1:10">
       <c r="A236" s="5">
         <v>2030</v>
       </c>
@@ -37279,7 +37268,7 @@
       </c>
       <c r="J236" s="7"/>
     </row>
-    <row r="237" spans="1:10" hidden="1">
+    <row r="237" spans="1:10">
       <c r="A237" s="5">
         <v>2031</v>
       </c>
@@ -37311,7 +37300,7 @@
       </c>
       <c r="J237" s="7"/>
     </row>
-    <row r="238" spans="1:10" hidden="1">
+    <row r="238" spans="1:10">
       <c r="A238" s="5">
         <v>2032</v>
       </c>
@@ -37343,7 +37332,7 @@
       </c>
       <c r="J238" s="7"/>
     </row>
-    <row r="239" spans="1:10" hidden="1">
+    <row r="239" spans="1:10">
       <c r="A239" s="5">
         <v>2033</v>
       </c>
@@ -37375,7 +37364,7 @@
       </c>
       <c r="J239" s="7"/>
     </row>
-    <row r="240" spans="1:10" hidden="1">
+    <row r="240" spans="1:10">
       <c r="A240" s="5">
         <v>2034</v>
       </c>
@@ -37407,7 +37396,7 @@
       </c>
       <c r="J240" s="7"/>
     </row>
-    <row r="241" spans="1:10" hidden="1">
+    <row r="241" spans="1:10">
       <c r="A241" s="5">
         <v>2035</v>
       </c>
@@ -37439,7 +37428,7 @@
       </c>
       <c r="J241" s="7"/>
     </row>
-    <row r="242" spans="1:10" hidden="1">
+    <row r="242" spans="1:10">
       <c r="A242" s="5">
         <v>2036</v>
       </c>
@@ -37471,7 +37460,7 @@
       </c>
       <c r="J242" s="7"/>
     </row>
-    <row r="243" spans="1:10" hidden="1">
+    <row r="243" spans="1:10">
       <c r="A243" s="5">
         <v>2037</v>
       </c>
@@ -37503,7 +37492,7 @@
       </c>
       <c r="J243" s="7"/>
     </row>
-    <row r="244" spans="1:10" hidden="1">
+    <row r="244" spans="1:10">
       <c r="A244" s="5">
         <v>2038</v>
       </c>
@@ -37535,7 +37524,7 @@
       </c>
       <c r="J244" s="7"/>
     </row>
-    <row r="245" spans="1:10" hidden="1">
+    <row r="245" spans="1:10">
       <c r="A245" s="5">
         <v>2039</v>
       </c>
@@ -37567,7 +37556,7 @@
       </c>
       <c r="J245" s="7"/>
     </row>
-    <row r="246" spans="1:10" hidden="1">
+    <row r="246" spans="1:10">
       <c r="A246" s="5">
         <v>2040</v>
       </c>
@@ -37599,7 +37588,7 @@
       </c>
       <c r="J246" s="7"/>
     </row>
-    <row r="247" spans="1:10" hidden="1">
+    <row r="247" spans="1:10">
       <c r="A247" s="5">
         <v>2030</v>
       </c>
@@ -37631,7 +37620,7 @@
       </c>
       <c r="J247" s="7"/>
     </row>
-    <row r="248" spans="1:10" hidden="1">
+    <row r="248" spans="1:10">
       <c r="A248" s="5">
         <v>2031</v>
       </c>
@@ -37663,7 +37652,7 @@
       </c>
       <c r="J248" s="7"/>
     </row>
-    <row r="249" spans="1:10" hidden="1">
+    <row r="249" spans="1:10">
       <c r="A249" s="5">
         <v>2032</v>
       </c>
@@ -37695,7 +37684,7 @@
       </c>
       <c r="J249" s="7"/>
     </row>
-    <row r="250" spans="1:10" hidden="1">
+    <row r="250" spans="1:10">
       <c r="A250" s="5">
         <v>2033</v>
       </c>
@@ -37727,7 +37716,7 @@
       </c>
       <c r="J250" s="7"/>
     </row>
-    <row r="251" spans="1:10" hidden="1">
+    <row r="251" spans="1:10">
       <c r="A251" s="5">
         <v>2034</v>
       </c>
@@ -37759,7 +37748,7 @@
       </c>
       <c r="J251" s="7"/>
     </row>
-    <row r="252" spans="1:10" hidden="1">
+    <row r="252" spans="1:10">
       <c r="A252" s="5">
         <v>2035</v>
       </c>
@@ -37791,7 +37780,7 @@
       </c>
       <c r="J252" s="7"/>
     </row>
-    <row r="253" spans="1:10" hidden="1">
+    <row r="253" spans="1:10">
       <c r="A253" s="5">
         <v>2036</v>
       </c>
@@ -37823,7 +37812,7 @@
       </c>
       <c r="J253" s="7"/>
     </row>
-    <row r="254" spans="1:10" hidden="1">
+    <row r="254" spans="1:10">
       <c r="A254" s="5">
         <v>2037</v>
       </c>
@@ -37855,7 +37844,7 @@
       </c>
       <c r="J254" s="7"/>
     </row>
-    <row r="255" spans="1:10" hidden="1">
+    <row r="255" spans="1:10">
       <c r="A255" s="5">
         <v>2038</v>
       </c>
@@ -37887,7 +37876,7 @@
       </c>
       <c r="J255" s="7"/>
     </row>
-    <row r="256" spans="1:10" hidden="1">
+    <row r="256" spans="1:10">
       <c r="A256" s="5">
         <v>2039</v>
       </c>
@@ -37919,7 +37908,7 @@
       </c>
       <c r="J256" s="7"/>
     </row>
-    <row r="257" spans="1:10" hidden="1">
+    <row r="257" spans="1:10">
       <c r="A257" s="5">
         <v>2040</v>
       </c>
@@ -37951,7 +37940,7 @@
       </c>
       <c r="J257" s="7"/>
     </row>
-    <row r="258" spans="1:10" hidden="1">
+    <row r="258" spans="1:10">
       <c r="A258" s="5">
         <v>2030</v>
       </c>
@@ -37983,7 +37972,7 @@
       </c>
       <c r="J258" s="7"/>
     </row>
-    <row r="259" spans="1:10" hidden="1">
+    <row r="259" spans="1:10">
       <c r="A259" s="5">
         <v>2031</v>
       </c>
@@ -38015,7 +38004,7 @@
       </c>
       <c r="J259" s="7"/>
     </row>
-    <row r="260" spans="1:10" hidden="1">
+    <row r="260" spans="1:10">
       <c r="A260" s="5">
         <v>2032</v>
       </c>
@@ -38047,7 +38036,7 @@
       </c>
       <c r="J260" s="7"/>
     </row>
-    <row r="261" spans="1:10" hidden="1">
+    <row r="261" spans="1:10">
       <c r="A261" s="5">
         <v>2033</v>
       </c>
@@ -38079,7 +38068,7 @@
       </c>
       <c r="J261" s="7"/>
     </row>
-    <row r="262" spans="1:10" hidden="1">
+    <row r="262" spans="1:10">
       <c r="A262" s="5">
         <v>2034</v>
       </c>
@@ -38111,7 +38100,7 @@
       </c>
       <c r="J262" s="7"/>
     </row>
-    <row r="263" spans="1:10" hidden="1">
+    <row r="263" spans="1:10">
       <c r="A263" s="5">
         <v>2035</v>
       </c>
@@ -38143,7 +38132,7 @@
       </c>
       <c r="J263" s="7"/>
     </row>
-    <row r="264" spans="1:10" hidden="1">
+    <row r="264" spans="1:10">
       <c r="A264" s="5">
         <v>2036</v>
       </c>
@@ -38175,7 +38164,7 @@
       </c>
       <c r="J264" s="7"/>
     </row>
-    <row r="265" spans="1:10" hidden="1">
+    <row r="265" spans="1:10">
       <c r="A265" s="5">
         <v>2037</v>
       </c>
@@ -38207,7 +38196,7 @@
       </c>
       <c r="J265" s="7"/>
     </row>
-    <row r="266" spans="1:10" hidden="1">
+    <row r="266" spans="1:10">
       <c r="A266" s="5">
         <v>2038</v>
       </c>
@@ -38239,7 +38228,7 @@
       </c>
       <c r="J266" s="7"/>
     </row>
-    <row r="267" spans="1:10" hidden="1">
+    <row r="267" spans="1:10">
       <c r="A267" s="5">
         <v>2039</v>
       </c>
@@ -38271,7 +38260,7 @@
       </c>
       <c r="J267" s="7"/>
     </row>
-    <row r="268" spans="1:10" hidden="1">
+    <row r="268" spans="1:10">
       <c r="A268" s="5">
         <v>2040</v>
       </c>
@@ -38303,7 +38292,7 @@
       </c>
       <c r="J268" s="7"/>
     </row>
-    <row r="269" spans="1:10" hidden="1">
+    <row r="269" spans="1:10">
       <c r="A269" s="5">
         <v>2030</v>
       </c>
@@ -38335,7 +38324,7 @@
       </c>
       <c r="J269" s="7"/>
     </row>
-    <row r="270" spans="1:10" hidden="1">
+    <row r="270" spans="1:10">
       <c r="A270" s="5">
         <v>2031</v>
       </c>
@@ -38367,7 +38356,7 @@
       </c>
       <c r="J270" s="7"/>
     </row>
-    <row r="271" spans="1:10" hidden="1">
+    <row r="271" spans="1:10">
       <c r="A271" s="5">
         <v>2032</v>
       </c>
@@ -38399,7 +38388,7 @@
       </c>
       <c r="J271" s="7"/>
     </row>
-    <row r="272" spans="1:10" hidden="1">
+    <row r="272" spans="1:10">
       <c r="A272" s="5">
         <v>2033</v>
       </c>
@@ -38431,7 +38420,7 @@
       </c>
       <c r="J272" s="7"/>
     </row>
-    <row r="273" spans="1:10" hidden="1">
+    <row r="273" spans="1:10">
       <c r="A273" s="5">
         <v>2034</v>
       </c>
@@ -38463,7 +38452,7 @@
       </c>
       <c r="J273" s="7"/>
     </row>
-    <row r="274" spans="1:10" hidden="1">
+    <row r="274" spans="1:10">
       <c r="A274" s="5">
         <v>2035</v>
       </c>
@@ -38495,7 +38484,7 @@
       </c>
       <c r="J274" s="7"/>
     </row>
-    <row r="275" spans="1:10" hidden="1">
+    <row r="275" spans="1:10">
       <c r="A275" s="5">
         <v>2036</v>
       </c>
@@ -38527,7 +38516,7 @@
       </c>
       <c r="J275" s="7"/>
     </row>
-    <row r="276" spans="1:10" hidden="1">
+    <row r="276" spans="1:10">
       <c r="A276" s="5">
         <v>2037</v>
       </c>
@@ -38559,7 +38548,7 @@
       </c>
       <c r="J276" s="7"/>
     </row>
-    <row r="277" spans="1:10" hidden="1">
+    <row r="277" spans="1:10">
       <c r="A277" s="5">
         <v>2038</v>
       </c>
@@ -38591,7 +38580,7 @@
       </c>
       <c r="J277" s="7"/>
     </row>
-    <row r="278" spans="1:10" hidden="1">
+    <row r="278" spans="1:10">
       <c r="A278" s="5">
         <v>2039</v>
       </c>
@@ -38623,7 +38612,7 @@
       </c>
       <c r="J278" s="7"/>
     </row>
-    <row r="279" spans="1:10" hidden="1">
+    <row r="279" spans="1:10">
       <c r="A279" s="5">
         <v>2040</v>
       </c>
@@ -38655,7 +38644,7 @@
       </c>
       <c r="J279" s="7"/>
     </row>
-    <row r="280" spans="1:10" hidden="1">
+    <row r="280" spans="1:10">
       <c r="A280" s="5">
         <v>2030</v>
       </c>
@@ -38687,7 +38676,7 @@
       </c>
       <c r="J280" s="7"/>
     </row>
-    <row r="281" spans="1:10" hidden="1">
+    <row r="281" spans="1:10">
       <c r="A281" s="5">
         <v>2031</v>
       </c>
@@ -38719,7 +38708,7 @@
       </c>
       <c r="J281" s="7"/>
     </row>
-    <row r="282" spans="1:10" hidden="1">
+    <row r="282" spans="1:10">
       <c r="A282" s="5">
         <v>2032</v>
       </c>
@@ -38751,7 +38740,7 @@
       </c>
       <c r="J282" s="7"/>
     </row>
-    <row r="283" spans="1:10" hidden="1">
+    <row r="283" spans="1:10">
       <c r="A283" s="5">
         <v>2033</v>
       </c>
@@ -38783,7 +38772,7 @@
       </c>
       <c r="J283" s="7"/>
     </row>
-    <row r="284" spans="1:10" hidden="1">
+    <row r="284" spans="1:10">
       <c r="A284" s="5">
         <v>2034</v>
       </c>
@@ -38815,7 +38804,7 @@
       </c>
       <c r="J284" s="7"/>
     </row>
-    <row r="285" spans="1:10" hidden="1">
+    <row r="285" spans="1:10">
       <c r="A285" s="5">
         <v>2035</v>
       </c>
@@ -38847,7 +38836,7 @@
       </c>
       <c r="J285" s="7"/>
     </row>
-    <row r="286" spans="1:10" hidden="1">
+    <row r="286" spans="1:10">
       <c r="A286" s="5">
         <v>2036</v>
       </c>
@@ -38879,7 +38868,7 @@
       </c>
       <c r="J286" s="7"/>
     </row>
-    <row r="287" spans="1:10" hidden="1">
+    <row r="287" spans="1:10">
       <c r="A287" s="5">
         <v>2037</v>
       </c>
@@ -38911,7 +38900,7 @@
       </c>
       <c r="J287" s="7"/>
     </row>
-    <row r="288" spans="1:10" hidden="1">
+    <row r="288" spans="1:10">
       <c r="A288" s="5">
         <v>2038</v>
       </c>
@@ -38943,7 +38932,7 @@
       </c>
       <c r="J288" s="7"/>
     </row>
-    <row r="289" spans="1:10" hidden="1">
+    <row r="289" spans="1:10">
       <c r="A289" s="5">
         <v>2039</v>
       </c>
@@ -38975,7 +38964,7 @@
       </c>
       <c r="J289" s="7"/>
     </row>
-    <row r="290" spans="1:10" hidden="1">
+    <row r="290" spans="1:10">
       <c r="A290" s="5">
         <v>2040</v>
       </c>
@@ -39007,7 +38996,7 @@
       </c>
       <c r="J290" s="7"/>
     </row>
-    <row r="291" spans="1:10" hidden="1">
+    <row r="291" spans="1:10">
       <c r="A291" s="5">
         <v>2030</v>
       </c>
@@ -39039,7 +39028,7 @@
       </c>
       <c r="J291" s="7"/>
     </row>
-    <row r="292" spans="1:10" hidden="1">
+    <row r="292" spans="1:10">
       <c r="A292" s="5">
         <v>2031</v>
       </c>
@@ -39071,7 +39060,7 @@
       </c>
       <c r="J292" s="7"/>
     </row>
-    <row r="293" spans="1:10" hidden="1">
+    <row r="293" spans="1:10">
       <c r="A293" s="5">
         <v>2032</v>
       </c>
@@ -39103,7 +39092,7 @@
       </c>
       <c r="J293" s="7"/>
     </row>
-    <row r="294" spans="1:10" hidden="1">
+    <row r="294" spans="1:10">
       <c r="A294" s="5">
         <v>2033</v>
       </c>
@@ -39135,7 +39124,7 @@
       </c>
       <c r="J294" s="7"/>
     </row>
-    <row r="295" spans="1:10" hidden="1">
+    <row r="295" spans="1:10">
       <c r="A295" s="5">
         <v>2034</v>
       </c>
@@ -39167,7 +39156,7 @@
       </c>
       <c r="J295" s="7"/>
     </row>
-    <row r="296" spans="1:10" hidden="1">
+    <row r="296" spans="1:10">
       <c r="A296" s="5">
         <v>2035</v>
       </c>
@@ -39199,7 +39188,7 @@
       </c>
       <c r="J296" s="7"/>
     </row>
-    <row r="297" spans="1:10" hidden="1">
+    <row r="297" spans="1:10">
       <c r="A297" s="5">
         <v>2036</v>
       </c>
@@ -39231,7 +39220,7 @@
       </c>
       <c r="J297" s="7"/>
     </row>
-    <row r="298" spans="1:10" hidden="1">
+    <row r="298" spans="1:10">
       <c r="A298" s="5">
         <v>2037</v>
       </c>
@@ -39263,7 +39252,7 @@
       </c>
       <c r="J298" s="7"/>
     </row>
-    <row r="299" spans="1:10" hidden="1">
+    <row r="299" spans="1:10">
       <c r="A299" s="5">
         <v>2038</v>
       </c>
@@ -39295,7 +39284,7 @@
       </c>
       <c r="J299" s="7"/>
     </row>
-    <row r="300" spans="1:10" hidden="1">
+    <row r="300" spans="1:10">
       <c r="A300" s="5">
         <v>2039</v>
       </c>
@@ -39327,7 +39316,7 @@
       </c>
       <c r="J300" s="7"/>
     </row>
-    <row r="301" spans="1:10" hidden="1">
+    <row r="301" spans="1:10">
       <c r="A301" s="5">
         <v>2040</v>
       </c>
@@ -39359,7 +39348,7 @@
       </c>
       <c r="J301" s="7"/>
     </row>
-    <row r="302" spans="1:10" hidden="1">
+    <row r="302" spans="1:10">
       <c r="A302" s="5">
         <v>2030</v>
       </c>
@@ -39391,7 +39380,7 @@
       </c>
       <c r="J302" s="7"/>
     </row>
-    <row r="303" spans="1:10" hidden="1">
+    <row r="303" spans="1:10">
       <c r="A303" s="5">
         <v>2031</v>
       </c>
@@ -39423,7 +39412,7 @@
       </c>
       <c r="J303" s="7"/>
     </row>
-    <row r="304" spans="1:10" hidden="1">
+    <row r="304" spans="1:10">
       <c r="A304" s="5">
         <v>2032</v>
       </c>
@@ -39455,7 +39444,7 @@
       </c>
       <c r="J304" s="7"/>
     </row>
-    <row r="305" spans="1:10" hidden="1">
+    <row r="305" spans="1:10">
       <c r="A305" s="5">
         <v>2033</v>
       </c>
@@ -39487,7 +39476,7 @@
       </c>
       <c r="J305" s="7"/>
     </row>
-    <row r="306" spans="1:10" hidden="1">
+    <row r="306" spans="1:10">
       <c r="A306" s="5">
         <v>2034</v>
       </c>
@@ -39519,7 +39508,7 @@
       </c>
       <c r="J306" s="7"/>
     </row>
-    <row r="307" spans="1:10" hidden="1">
+    <row r="307" spans="1:10">
       <c r="A307" s="5">
         <v>2035</v>
       </c>
@@ -39551,7 +39540,7 @@
       </c>
       <c r="J307" s="7"/>
     </row>
-    <row r="308" spans="1:10" hidden="1">
+    <row r="308" spans="1:10">
       <c r="A308" s="5">
         <v>2036</v>
       </c>
@@ -39583,7 +39572,7 @@
       </c>
       <c r="J308" s="7"/>
     </row>
-    <row r="309" spans="1:10" hidden="1">
+    <row r="309" spans="1:10">
       <c r="A309" s="5">
         <v>2037</v>
       </c>
@@ -39615,7 +39604,7 @@
       </c>
       <c r="J309" s="7"/>
     </row>
-    <row r="310" spans="1:10" hidden="1">
+    <row r="310" spans="1:10">
       <c r="A310" s="5">
         <v>2038</v>
       </c>
@@ -39647,7 +39636,7 @@
       </c>
       <c r="J310" s="7"/>
     </row>
-    <row r="311" spans="1:10" hidden="1">
+    <row r="311" spans="1:10">
       <c r="A311" s="5">
         <v>2039</v>
       </c>
@@ -39679,7 +39668,7 @@
       </c>
       <c r="J311" s="7"/>
     </row>
-    <row r="312" spans="1:10" hidden="1">
+    <row r="312" spans="1:10">
       <c r="A312" s="5">
         <v>2040</v>
       </c>
@@ -39711,7 +39700,7 @@
       </c>
       <c r="J312" s="7"/>
     </row>
-    <row r="313" spans="1:10" hidden="1">
+    <row r="313" spans="1:10">
       <c r="A313" s="5">
         <v>2030</v>
       </c>
@@ -39743,7 +39732,7 @@
       </c>
       <c r="J313" s="7"/>
     </row>
-    <row r="314" spans="1:10" hidden="1">
+    <row r="314" spans="1:10">
       <c r="A314" s="5">
         <v>2031</v>
       </c>
@@ -39775,7 +39764,7 @@
       </c>
       <c r="J314" s="7"/>
     </row>
-    <row r="315" spans="1:10" hidden="1">
+    <row r="315" spans="1:10">
       <c r="A315" s="5">
         <v>2032</v>
       </c>
@@ -39807,7 +39796,7 @@
       </c>
       <c r="J315" s="7"/>
     </row>
-    <row r="316" spans="1:10" hidden="1">
+    <row r="316" spans="1:10">
       <c r="A316" s="5">
         <v>2033</v>
       </c>
@@ -39839,7 +39828,7 @@
       </c>
       <c r="J316" s="7"/>
     </row>
-    <row r="317" spans="1:10" hidden="1">
+    <row r="317" spans="1:10">
       <c r="A317" s="5">
         <v>2034</v>
       </c>
@@ -39871,7 +39860,7 @@
       </c>
       <c r="J317" s="7"/>
     </row>
-    <row r="318" spans="1:10" hidden="1">
+    <row r="318" spans="1:10">
       <c r="A318" s="5">
         <v>2035</v>
       </c>
@@ -39903,7 +39892,7 @@
       </c>
       <c r="J318" s="7"/>
     </row>
-    <row r="319" spans="1:10" hidden="1">
+    <row r="319" spans="1:10">
       <c r="A319" s="5">
         <v>2036</v>
       </c>
@@ -39935,7 +39924,7 @@
       </c>
       <c r="J319" s="7"/>
     </row>
-    <row r="320" spans="1:10" hidden="1">
+    <row r="320" spans="1:10">
       <c r="A320" s="5">
         <v>2037</v>
       </c>
@@ -39967,7 +39956,7 @@
       </c>
       <c r="J320" s="7"/>
     </row>
-    <row r="321" spans="1:10" hidden="1">
+    <row r="321" spans="1:10">
       <c r="A321" s="5">
         <v>2038</v>
       </c>
@@ -39999,7 +39988,7 @@
       </c>
       <c r="J321" s="7"/>
     </row>
-    <row r="322" spans="1:10" hidden="1">
+    <row r="322" spans="1:10">
       <c r="A322" s="5">
         <v>2039</v>
       </c>
@@ -40031,7 +40020,7 @@
       </c>
       <c r="J322" s="7"/>
     </row>
-    <row r="323" spans="1:10" hidden="1">
+    <row r="323" spans="1:10">
       <c r="A323" s="5">
         <v>2040</v>
       </c>
@@ -40063,7 +40052,7 @@
       </c>
       <c r="J323" s="7"/>
     </row>
-    <row r="324" spans="1:10" hidden="1">
+    <row r="324" spans="1:10">
       <c r="A324" s="5">
         <v>2030</v>
       </c>
@@ -40095,7 +40084,7 @@
       </c>
       <c r="J324" s="7"/>
     </row>
-    <row r="325" spans="1:10" hidden="1">
+    <row r="325" spans="1:10">
       <c r="A325" s="5">
         <v>2031</v>
       </c>
@@ -40127,7 +40116,7 @@
       </c>
       <c r="J325" s="7"/>
     </row>
-    <row r="326" spans="1:10" hidden="1">
+    <row r="326" spans="1:10">
       <c r="A326" s="5">
         <v>2032</v>
       </c>
@@ -40159,7 +40148,7 @@
       </c>
       <c r="J326" s="7"/>
     </row>
-    <row r="327" spans="1:10" hidden="1">
+    <row r="327" spans="1:10">
       <c r="A327" s="5">
         <v>2033</v>
       </c>
@@ -40191,7 +40180,7 @@
       </c>
       <c r="J327" s="7"/>
     </row>
-    <row r="328" spans="1:10" hidden="1">
+    <row r="328" spans="1:10">
       <c r="A328" s="5">
         <v>2034</v>
       </c>
@@ -40223,7 +40212,7 @@
       </c>
       <c r="J328" s="7"/>
     </row>
-    <row r="329" spans="1:10" hidden="1">
+    <row r="329" spans="1:10">
       <c r="A329" s="5">
         <v>2035</v>
       </c>
@@ -40255,7 +40244,7 @@
       </c>
       <c r="J329" s="7"/>
     </row>
-    <row r="330" spans="1:10" hidden="1">
+    <row r="330" spans="1:10">
       <c r="A330" s="5">
         <v>2036</v>
       </c>
@@ -40287,7 +40276,7 @@
       </c>
       <c r="J330" s="7"/>
     </row>
-    <row r="331" spans="1:10" hidden="1">
+    <row r="331" spans="1:10">
       <c r="A331" s="5">
         <v>2037</v>
       </c>
@@ -40319,7 +40308,7 @@
       </c>
       <c r="J331" s="7"/>
     </row>
-    <row r="332" spans="1:10" hidden="1">
+    <row r="332" spans="1:10">
       <c r="A332" s="5">
         <v>2038</v>
       </c>
@@ -40351,7 +40340,7 @@
       </c>
       <c r="J332" s="7"/>
     </row>
-    <row r="333" spans="1:10" hidden="1">
+    <row r="333" spans="1:10">
       <c r="A333" s="5">
         <v>2039</v>
       </c>
@@ -40383,7 +40372,7 @@
       </c>
       <c r="J333" s="7"/>
     </row>
-    <row r="334" spans="1:10" hidden="1">
+    <row r="334" spans="1:10">
       <c r="A334" s="5">
         <v>2040</v>
       </c>
@@ -40415,7 +40404,7 @@
       </c>
       <c r="J334" s="7"/>
     </row>
-    <row r="335" spans="1:10" hidden="1">
+    <row r="335" spans="1:10">
       <c r="A335" s="5">
         <v>2030</v>
       </c>
@@ -40447,7 +40436,7 @@
       </c>
       <c r="J335" s="7"/>
     </row>
-    <row r="336" spans="1:10" hidden="1">
+    <row r="336" spans="1:10">
       <c r="A336" s="5">
         <v>2031</v>
       </c>
@@ -40479,7 +40468,7 @@
       </c>
       <c r="J336" s="7"/>
     </row>
-    <row r="337" spans="1:10" hidden="1">
+    <row r="337" spans="1:10">
       <c r="A337" s="5">
         <v>2032</v>
       </c>
@@ -40511,7 +40500,7 @@
       </c>
       <c r="J337" s="7"/>
     </row>
-    <row r="338" spans="1:10" hidden="1">
+    <row r="338" spans="1:10">
       <c r="A338" s="5">
         <v>2033</v>
       </c>
@@ -40543,7 +40532,7 @@
       </c>
       <c r="J338" s="7"/>
     </row>
-    <row r="339" spans="1:10" hidden="1">
+    <row r="339" spans="1:10">
       <c r="A339" s="5">
         <v>2034</v>
       </c>
@@ -40575,7 +40564,7 @@
       </c>
       <c r="J339" s="7"/>
     </row>
-    <row r="340" spans="1:10" hidden="1">
+    <row r="340" spans="1:10">
       <c r="A340" s="5">
         <v>2035</v>
       </c>
@@ -40607,7 +40596,7 @@
       </c>
       <c r="J340" s="7"/>
     </row>
-    <row r="341" spans="1:10" hidden="1">
+    <row r="341" spans="1:10">
       <c r="A341" s="5">
         <v>2036</v>
       </c>
@@ -40639,7 +40628,7 @@
       </c>
       <c r="J341" s="7"/>
     </row>
-    <row r="342" spans="1:10" hidden="1">
+    <row r="342" spans="1:10">
       <c r="A342" s="5">
         <v>2037</v>
       </c>
@@ -40671,7 +40660,7 @@
       </c>
       <c r="J342" s="7"/>
     </row>
-    <row r="343" spans="1:10" hidden="1">
+    <row r="343" spans="1:10">
       <c r="A343" s="5">
         <v>2038</v>
       </c>
@@ -40703,7 +40692,7 @@
       </c>
       <c r="J343" s="7"/>
     </row>
-    <row r="344" spans="1:10" hidden="1">
+    <row r="344" spans="1:10">
       <c r="A344" s="5">
         <v>2039</v>
       </c>
@@ -40735,7 +40724,7 @@
       </c>
       <c r="J344" s="7"/>
     </row>
-    <row r="345" spans="1:10" hidden="1">
+    <row r="345" spans="1:10">
       <c r="A345" s="5">
         <v>2040</v>
       </c>
@@ -40767,7 +40756,7 @@
       </c>
       <c r="J345" s="7"/>
     </row>
-    <row r="346" spans="1:10" hidden="1">
+    <row r="346" spans="1:10">
       <c r="A346" s="5">
         <v>2030</v>
       </c>
@@ -40799,7 +40788,7 @@
       </c>
       <c r="J346" s="7"/>
     </row>
-    <row r="347" spans="1:10" hidden="1">
+    <row r="347" spans="1:10">
       <c r="A347" s="5">
         <v>2031</v>
       </c>
@@ -40831,7 +40820,7 @@
       </c>
       <c r="J347" s="7"/>
     </row>
-    <row r="348" spans="1:10" hidden="1">
+    <row r="348" spans="1:10">
       <c r="A348" s="5">
         <v>2032</v>
       </c>
@@ -40863,7 +40852,7 @@
       </c>
       <c r="J348" s="7"/>
     </row>
-    <row r="349" spans="1:10" hidden="1">
+    <row r="349" spans="1:10">
       <c r="A349" s="5">
         <v>2033</v>
       </c>
@@ -40895,7 +40884,7 @@
       </c>
       <c r="J349" s="7"/>
     </row>
-    <row r="350" spans="1:10" hidden="1">
+    <row r="350" spans="1:10">
       <c r="A350" s="5">
         <v>2034</v>
       </c>
@@ -40927,7 +40916,7 @@
       </c>
       <c r="J350" s="7"/>
     </row>
-    <row r="351" spans="1:10" hidden="1">
+    <row r="351" spans="1:10">
       <c r="A351" s="5">
         <v>2035</v>
       </c>
@@ -40959,7 +40948,7 @@
       </c>
       <c r="J351" s="7"/>
     </row>
-    <row r="352" spans="1:10" hidden="1">
+    <row r="352" spans="1:10">
       <c r="A352" s="5">
         <v>2036</v>
       </c>
@@ -40991,7 +40980,7 @@
       </c>
       <c r="J352" s="7"/>
     </row>
-    <row r="353" spans="1:10" hidden="1">
+    <row r="353" spans="1:10">
       <c r="A353" s="5">
         <v>2037</v>
       </c>
@@ -41023,7 +41012,7 @@
       </c>
       <c r="J353" s="7"/>
     </row>
-    <row r="354" spans="1:10" hidden="1">
+    <row r="354" spans="1:10">
       <c r="A354" s="5">
         <v>2038</v>
       </c>
@@ -41055,7 +41044,7 @@
       </c>
       <c r="J354" s="7"/>
     </row>
-    <row r="355" spans="1:10" hidden="1">
+    <row r="355" spans="1:10">
       <c r="A355" s="5">
         <v>2039</v>
       </c>
@@ -41087,7 +41076,7 @@
       </c>
       <c r="J355" s="7"/>
     </row>
-    <row r="356" spans="1:10" hidden="1">
+    <row r="356" spans="1:10">
       <c r="A356" s="5">
         <v>2040</v>
       </c>
@@ -41119,7 +41108,7 @@
       </c>
       <c r="J356" s="7"/>
     </row>
-    <row r="357" spans="1:10" hidden="1">
+    <row r="357" spans="1:10">
       <c r="A357">
         <v>2030</v>
       </c>
@@ -41151,7 +41140,7 @@
       </c>
       <c r="J357" s="7"/>
     </row>
-    <row r="358" spans="1:10" hidden="1">
+    <row r="358" spans="1:10">
       <c r="A358">
         <v>2031</v>
       </c>
@@ -41183,7 +41172,7 @@
       </c>
       <c r="J358" s="7"/>
     </row>
-    <row r="359" spans="1:10" hidden="1">
+    <row r="359" spans="1:10">
       <c r="A359">
         <v>2032</v>
       </c>
@@ -41215,7 +41204,7 @@
       </c>
       <c r="J359" s="7"/>
     </row>
-    <row r="360" spans="1:10" hidden="1">
+    <row r="360" spans="1:10">
       <c r="A360">
         <v>2033</v>
       </c>
@@ -41247,7 +41236,7 @@
       </c>
       <c r="J360" s="7"/>
     </row>
-    <row r="361" spans="1:10" hidden="1">
+    <row r="361" spans="1:10">
       <c r="A361">
         <v>2034</v>
       </c>
@@ -41279,7 +41268,7 @@
       </c>
       <c r="J361" s="7"/>
     </row>
-    <row r="362" spans="1:10" hidden="1">
+    <row r="362" spans="1:10">
       <c r="A362">
         <v>2035</v>
       </c>
@@ -41311,7 +41300,7 @@
       </c>
       <c r="J362" s="7"/>
     </row>
-    <row r="363" spans="1:10" hidden="1">
+    <row r="363" spans="1:10">
       <c r="A363">
         <v>2036</v>
       </c>
@@ -41343,7 +41332,7 @@
       </c>
       <c r="J363" s="7"/>
     </row>
-    <row r="364" spans="1:10" hidden="1">
+    <row r="364" spans="1:10">
       <c r="A364">
         <v>2037</v>
       </c>
@@ -41375,7 +41364,7 @@
       </c>
       <c r="J364" s="7"/>
     </row>
-    <row r="365" spans="1:10" hidden="1">
+    <row r="365" spans="1:10">
       <c r="A365">
         <v>2038</v>
       </c>
@@ -41407,7 +41396,7 @@
       </c>
       <c r="J365" s="7"/>
     </row>
-    <row r="366" spans="1:10" hidden="1">
+    <row r="366" spans="1:10">
       <c r="A366">
         <v>2039</v>
       </c>
@@ -41439,7 +41428,7 @@
       </c>
       <c r="J366" s="7"/>
     </row>
-    <row r="367" spans="1:10" hidden="1">
+    <row r="367" spans="1:10">
       <c r="A367">
         <v>2040</v>
       </c>
@@ -41471,7 +41460,7 @@
       </c>
       <c r="J367" s="7"/>
     </row>
-    <row r="368" spans="1:10" hidden="1">
+    <row r="368" spans="1:10">
       <c r="A368">
         <v>2030</v>
       </c>
@@ -41503,7 +41492,7 @@
       </c>
       <c r="J368" s="7"/>
     </row>
-    <row r="369" spans="1:10" hidden="1">
+    <row r="369" spans="1:10">
       <c r="A369">
         <v>2031</v>
       </c>
@@ -41535,7 +41524,7 @@
       </c>
       <c r="J369" s="7"/>
     </row>
-    <row r="370" spans="1:10" hidden="1">
+    <row r="370" spans="1:10">
       <c r="A370">
         <v>2032</v>
       </c>
@@ -41567,7 +41556,7 @@
       </c>
       <c r="J370" s="7"/>
     </row>
-    <row r="371" spans="1:10" hidden="1">
+    <row r="371" spans="1:10">
       <c r="A371">
         <v>2033</v>
       </c>
@@ -41599,7 +41588,7 @@
       </c>
       <c r="J371" s="7"/>
     </row>
-    <row r="372" spans="1:10" hidden="1">
+    <row r="372" spans="1:10">
       <c r="A372">
         <v>2034</v>
       </c>
@@ -41631,7 +41620,7 @@
       </c>
       <c r="J372" s="7"/>
     </row>
-    <row r="373" spans="1:10" hidden="1">
+    <row r="373" spans="1:10">
       <c r="A373">
         <v>2035</v>
       </c>
@@ -41663,7 +41652,7 @@
       </c>
       <c r="J373" s="7"/>
     </row>
-    <row r="374" spans="1:10" hidden="1">
+    <row r="374" spans="1:10">
       <c r="A374">
         <v>2036</v>
       </c>
@@ -41695,7 +41684,7 @@
       </c>
       <c r="J374" s="7"/>
     </row>
-    <row r="375" spans="1:10" hidden="1">
+    <row r="375" spans="1:10">
       <c r="A375">
         <v>2037</v>
       </c>
@@ -41727,7 +41716,7 @@
       </c>
       <c r="J375" s="7"/>
     </row>
-    <row r="376" spans="1:10" hidden="1">
+    <row r="376" spans="1:10">
       <c r="A376">
         <v>2038</v>
       </c>
@@ -41759,7 +41748,7 @@
       </c>
       <c r="J376" s="7"/>
     </row>
-    <row r="377" spans="1:10" hidden="1">
+    <row r="377" spans="1:10">
       <c r="A377">
         <v>2039</v>
       </c>
@@ -41791,7 +41780,7 @@
       </c>
       <c r="J377" s="7"/>
     </row>
-    <row r="378" spans="1:10" hidden="1">
+    <row r="378" spans="1:10">
       <c r="A378">
         <v>2040</v>
       </c>
@@ -41823,7 +41812,7 @@
       </c>
       <c r="J378" s="7"/>
     </row>
-    <row r="379" spans="1:10" hidden="1">
+    <row r="379" spans="1:10">
       <c r="A379">
         <v>2030</v>
       </c>
@@ -41855,7 +41844,7 @@
       </c>
       <c r="J379" s="7"/>
     </row>
-    <row r="380" spans="1:10" hidden="1">
+    <row r="380" spans="1:10">
       <c r="A380">
         <v>2031</v>
       </c>
@@ -41887,7 +41876,7 @@
       </c>
       <c r="J380" s="7"/>
     </row>
-    <row r="381" spans="1:10" hidden="1">
+    <row r="381" spans="1:10">
       <c r="A381">
         <v>2032</v>
       </c>
@@ -41919,7 +41908,7 @@
       </c>
       <c r="J381" s="7"/>
     </row>
-    <row r="382" spans="1:10" hidden="1">
+    <row r="382" spans="1:10">
       <c r="A382">
         <v>2033</v>
       </c>
@@ -41951,7 +41940,7 @@
       </c>
       <c r="J382" s="7"/>
     </row>
-    <row r="383" spans="1:10" hidden="1">
+    <row r="383" spans="1:10">
       <c r="A383">
         <v>2034</v>
       </c>
@@ -41983,7 +41972,7 @@
       </c>
       <c r="J383" s="7"/>
     </row>
-    <row r="384" spans="1:10" hidden="1">
+    <row r="384" spans="1:10">
       <c r="A384">
         <v>2035</v>
       </c>
@@ -42015,7 +42004,7 @@
       </c>
       <c r="J384" s="7"/>
     </row>
-    <row r="385" spans="1:10" hidden="1">
+    <row r="385" spans="1:10">
       <c r="A385">
         <v>2036</v>
       </c>
@@ -42047,7 +42036,7 @@
       </c>
       <c r="J385" s="7"/>
     </row>
-    <row r="386" spans="1:10" hidden="1">
+    <row r="386" spans="1:10">
       <c r="A386">
         <v>2037</v>
       </c>
@@ -42079,7 +42068,7 @@
       </c>
       <c r="J386" s="7"/>
     </row>
-    <row r="387" spans="1:10" hidden="1">
+    <row r="387" spans="1:10">
       <c r="A387">
         <v>2038</v>
       </c>
@@ -42111,7 +42100,7 @@
       </c>
       <c r="J387" s="7"/>
     </row>
-    <row r="388" spans="1:10" hidden="1">
+    <row r="388" spans="1:10">
       <c r="A388">
         <v>2039</v>
       </c>
@@ -42143,7 +42132,7 @@
       </c>
       <c r="J388" s="7"/>
     </row>
-    <row r="389" spans="1:10" hidden="1">
+    <row r="389" spans="1:10">
       <c r="A389">
         <v>2040</v>
       </c>
@@ -42175,7 +42164,7 @@
       </c>
       <c r="J389" s="7"/>
     </row>
-    <row r="390" spans="1:10" hidden="1">
+    <row r="390" spans="1:10">
       <c r="A390">
         <v>2030</v>
       </c>
@@ -42207,7 +42196,7 @@
       </c>
       <c r="J390" s="7"/>
     </row>
-    <row r="391" spans="1:10" hidden="1">
+    <row r="391" spans="1:10">
       <c r="A391">
         <v>2031</v>
       </c>
@@ -42239,7 +42228,7 @@
       </c>
       <c r="J391" s="7"/>
     </row>
-    <row r="392" spans="1:10" hidden="1">
+    <row r="392" spans="1:10">
       <c r="A392">
         <v>2032</v>
       </c>
@@ -42271,7 +42260,7 @@
       </c>
       <c r="J392" s="7"/>
     </row>
-    <row r="393" spans="1:10" hidden="1">
+    <row r="393" spans="1:10">
       <c r="A393">
         <v>2033</v>
       </c>
@@ -42303,7 +42292,7 @@
       </c>
       <c r="J393" s="7"/>
     </row>
-    <row r="394" spans="1:10" hidden="1">
+    <row r="394" spans="1:10">
       <c r="A394">
         <v>2034</v>
       </c>
@@ -42335,7 +42324,7 @@
       </c>
       <c r="J394" s="7"/>
     </row>
-    <row r="395" spans="1:10" hidden="1">
+    <row r="395" spans="1:10">
       <c r="A395">
         <v>2035</v>
       </c>
@@ -42367,7 +42356,7 @@
       </c>
       <c r="J395" s="7"/>
     </row>
-    <row r="396" spans="1:10" hidden="1">
+    <row r="396" spans="1:10">
       <c r="A396">
         <v>2036</v>
       </c>
@@ -42399,7 +42388,7 @@
       </c>
       <c r="J396" s="7"/>
     </row>
-    <row r="397" spans="1:10" hidden="1">
+    <row r="397" spans="1:10">
       <c r="A397">
         <v>2037</v>
       </c>
@@ -42431,7 +42420,7 @@
       </c>
       <c r="J397" s="7"/>
     </row>
-    <row r="398" spans="1:10" hidden="1">
+    <row r="398" spans="1:10">
       <c r="A398">
         <v>2038</v>
       </c>
@@ -42463,7 +42452,7 @@
       </c>
       <c r="J398" s="7"/>
     </row>
-    <row r="399" spans="1:10" hidden="1">
+    <row r="399" spans="1:10">
       <c r="A399">
         <v>2039</v>
       </c>
@@ -42495,7 +42484,7 @@
       </c>
       <c r="J399" s="7"/>
     </row>
-    <row r="400" spans="1:10" hidden="1">
+    <row r="400" spans="1:10">
       <c r="A400">
         <v>2040</v>
       </c>
@@ -42527,7 +42516,7 @@
       </c>
       <c r="J400" s="7"/>
     </row>
-    <row r="401" spans="1:10" hidden="1">
+    <row r="401" spans="1:10">
       <c r="A401">
         <v>2030</v>
       </c>
@@ -42559,7 +42548,7 @@
       </c>
       <c r="J401" s="7"/>
     </row>
-    <row r="402" spans="1:10" hidden="1">
+    <row r="402" spans="1:10">
       <c r="A402">
         <v>2031</v>
       </c>
@@ -42591,7 +42580,7 @@
       </c>
       <c r="J402" s="7"/>
     </row>
-    <row r="403" spans="1:10" hidden="1">
+    <row r="403" spans="1:10">
       <c r="A403">
         <v>2032</v>
       </c>
@@ -42623,7 +42612,7 @@
       </c>
       <c r="J403" s="7"/>
     </row>
-    <row r="404" spans="1:10" hidden="1">
+    <row r="404" spans="1:10">
       <c r="A404">
         <v>2033</v>
       </c>
@@ -42655,7 +42644,7 @@
       </c>
       <c r="J404" s="7"/>
     </row>
-    <row r="405" spans="1:10" hidden="1">
+    <row r="405" spans="1:10">
       <c r="A405">
         <v>2034</v>
       </c>
@@ -42687,7 +42676,7 @@
       </c>
       <c r="J405" s="7"/>
     </row>
-    <row r="406" spans="1:10" hidden="1">
+    <row r="406" spans="1:10">
       <c r="A406">
         <v>2035</v>
       </c>
@@ -42719,7 +42708,7 @@
       </c>
       <c r="J406" s="7"/>
     </row>
-    <row r="407" spans="1:10" hidden="1">
+    <row r="407" spans="1:10">
       <c r="A407">
         <v>2036</v>
       </c>
@@ -42751,7 +42740,7 @@
       </c>
       <c r="J407" s="7"/>
     </row>
-    <row r="408" spans="1:10" hidden="1">
+    <row r="408" spans="1:10">
       <c r="A408">
         <v>2037</v>
       </c>
@@ -42783,7 +42772,7 @@
       </c>
       <c r="J408" s="7"/>
     </row>
-    <row r="409" spans="1:10" hidden="1">
+    <row r="409" spans="1:10">
       <c r="A409">
         <v>2038</v>
       </c>
@@ -42815,7 +42804,7 @@
       </c>
       <c r="J409" s="7"/>
     </row>
-    <row r="410" spans="1:10" hidden="1">
+    <row r="410" spans="1:10">
       <c r="A410">
         <v>2039</v>
       </c>
@@ -42847,7 +42836,7 @@
       </c>
       <c r="J410" s="7"/>
     </row>
-    <row r="411" spans="1:10" hidden="1">
+    <row r="411" spans="1:10">
       <c r="A411">
         <v>2040</v>
       </c>
@@ -42879,7 +42868,7 @@
       </c>
       <c r="J411" s="7"/>
     </row>
-    <row r="412" spans="1:10" hidden="1">
+    <row r="412" spans="1:10">
       <c r="A412">
         <v>2030</v>
       </c>
@@ -42911,7 +42900,7 @@
       </c>
       <c r="J412" s="7"/>
     </row>
-    <row r="413" spans="1:10" hidden="1">
+    <row r="413" spans="1:10">
       <c r="A413">
         <v>2031</v>
       </c>
@@ -42943,7 +42932,7 @@
       </c>
       <c r="J413" s="7"/>
     </row>
-    <row r="414" spans="1:10" hidden="1">
+    <row r="414" spans="1:10">
       <c r="A414">
         <v>2032</v>
       </c>
@@ -42975,7 +42964,7 @@
       </c>
       <c r="J414" s="7"/>
     </row>
-    <row r="415" spans="1:10" hidden="1">
+    <row r="415" spans="1:10">
       <c r="A415">
         <v>2033</v>
       </c>
@@ -43007,7 +42996,7 @@
       </c>
       <c r="J415" s="7"/>
     </row>
-    <row r="416" spans="1:10" hidden="1">
+    <row r="416" spans="1:10">
       <c r="A416">
         <v>2034</v>
       </c>
@@ -43039,7 +43028,7 @@
       </c>
       <c r="J416" s="7"/>
     </row>
-    <row r="417" spans="1:10" hidden="1">
+    <row r="417" spans="1:10">
       <c r="A417">
         <v>2035</v>
       </c>
@@ -43071,7 +43060,7 @@
       </c>
       <c r="J417" s="7"/>
     </row>
-    <row r="418" spans="1:10" hidden="1">
+    <row r="418" spans="1:10">
       <c r="A418">
         <v>2036</v>
       </c>
@@ -43103,7 +43092,7 @@
       </c>
       <c r="J418" s="7"/>
     </row>
-    <row r="419" spans="1:10" hidden="1">
+    <row r="419" spans="1:10">
       <c r="A419">
         <v>2037</v>
       </c>
@@ -43135,7 +43124,7 @@
       </c>
       <c r="J419" s="7"/>
     </row>
-    <row r="420" spans="1:10" hidden="1">
+    <row r="420" spans="1:10">
       <c r="A420">
         <v>2038</v>
       </c>
@@ -43167,7 +43156,7 @@
       </c>
       <c r="J420" s="7"/>
     </row>
-    <row r="421" spans="1:10" hidden="1">
+    <row r="421" spans="1:10">
       <c r="A421">
         <v>2039</v>
       </c>
@@ -43199,7 +43188,7 @@
       </c>
       <c r="J421" s="7"/>
     </row>
-    <row r="422" spans="1:10" hidden="1">
+    <row r="422" spans="1:10">
       <c r="A422">
         <v>2040</v>
       </c>
@@ -43231,7 +43220,7 @@
       </c>
       <c r="J422" s="7"/>
     </row>
-    <row r="423" spans="1:10" hidden="1">
+    <row r="423" spans="1:10">
       <c r="A423">
         <v>2030</v>
       </c>
@@ -43263,7 +43252,7 @@
       </c>
       <c r="J423" s="7"/>
     </row>
-    <row r="424" spans="1:10" hidden="1">
+    <row r="424" spans="1:10">
       <c r="A424">
         <v>2031</v>
       </c>
@@ -43295,7 +43284,7 @@
       </c>
       <c r="J424" s="7"/>
     </row>
-    <row r="425" spans="1:10" hidden="1">
+    <row r="425" spans="1:10">
       <c r="A425">
         <v>2032</v>
       </c>
@@ -43327,7 +43316,7 @@
       </c>
       <c r="J425" s="7"/>
     </row>
-    <row r="426" spans="1:10" hidden="1">
+    <row r="426" spans="1:10">
       <c r="A426">
         <v>2033</v>
       </c>
@@ -43359,7 +43348,7 @@
       </c>
       <c r="J426" s="7"/>
     </row>
-    <row r="427" spans="1:10" hidden="1">
+    <row r="427" spans="1:10">
       <c r="A427">
         <v>2034</v>
       </c>
@@ -43391,7 +43380,7 @@
       </c>
       <c r="J427" s="7"/>
     </row>
-    <row r="428" spans="1:10" hidden="1">
+    <row r="428" spans="1:10">
       <c r="A428">
         <v>2035</v>
       </c>
@@ -43423,7 +43412,7 @@
       </c>
       <c r="J428" s="7"/>
     </row>
-    <row r="429" spans="1:10" hidden="1">
+    <row r="429" spans="1:10">
       <c r="A429">
         <v>2036</v>
       </c>
@@ -43455,7 +43444,7 @@
       </c>
       <c r="J429" s="7"/>
     </row>
-    <row r="430" spans="1:10" hidden="1">
+    <row r="430" spans="1:10">
       <c r="A430">
         <v>2037</v>
       </c>
@@ -43487,7 +43476,7 @@
       </c>
       <c r="J430" s="7"/>
     </row>
-    <row r="431" spans="1:10" hidden="1">
+    <row r="431" spans="1:10">
       <c r="A431">
         <v>2038</v>
       </c>
@@ -43519,7 +43508,7 @@
       </c>
       <c r="J431" s="7"/>
     </row>
-    <row r="432" spans="1:10" hidden="1">
+    <row r="432" spans="1:10">
       <c r="A432">
         <v>2039</v>
       </c>
@@ -43551,7 +43540,7 @@
       </c>
       <c r="J432" s="7"/>
     </row>
-    <row r="433" spans="1:10" hidden="1">
+    <row r="433" spans="1:10">
       <c r="A433">
         <v>2040</v>
       </c>
@@ -43583,7 +43572,7 @@
       </c>
       <c r="J433" s="7"/>
     </row>
-    <row r="434" spans="1:10" hidden="1">
+    <row r="434" spans="1:10">
       <c r="A434">
         <v>2030</v>
       </c>
@@ -43615,7 +43604,7 @@
       </c>
       <c r="J434" s="7"/>
     </row>
-    <row r="435" spans="1:10" hidden="1">
+    <row r="435" spans="1:10">
       <c r="A435">
         <v>2031</v>
       </c>
@@ -43647,7 +43636,7 @@
       </c>
       <c r="J435" s="7"/>
     </row>
-    <row r="436" spans="1:10" hidden="1">
+    <row r="436" spans="1:10">
       <c r="A436">
         <v>2032</v>
       </c>
@@ -43679,7 +43668,7 @@
       </c>
       <c r="J436" s="7"/>
     </row>
-    <row r="437" spans="1:10" hidden="1">
+    <row r="437" spans="1:10">
       <c r="A437">
         <v>2033</v>
       </c>
@@ -43711,7 +43700,7 @@
       </c>
       <c r="J437" s="7"/>
     </row>
-    <row r="438" spans="1:10" hidden="1">
+    <row r="438" spans="1:10">
       <c r="A438">
         <v>2034</v>
       </c>
@@ -43743,7 +43732,7 @@
       </c>
       <c r="J438" s="7"/>
     </row>
-    <row r="439" spans="1:10" hidden="1">
+    <row r="439" spans="1:10">
       <c r="A439">
         <v>2035</v>
       </c>
@@ -43775,7 +43764,7 @@
       </c>
       <c r="J439" s="7"/>
     </row>
-    <row r="440" spans="1:10" hidden="1">
+    <row r="440" spans="1:10">
       <c r="A440">
         <v>2036</v>
       </c>
@@ -43807,7 +43796,7 @@
       </c>
       <c r="J440" s="7"/>
     </row>
-    <row r="441" spans="1:10" hidden="1">
+    <row r="441" spans="1:10">
       <c r="A441">
         <v>2037</v>
       </c>
@@ -43839,7 +43828,7 @@
       </c>
       <c r="J441" s="7"/>
     </row>
-    <row r="442" spans="1:10" hidden="1">
+    <row r="442" spans="1:10">
       <c r="A442">
         <v>2038</v>
       </c>
@@ -43871,7 +43860,7 @@
       </c>
       <c r="J442" s="7"/>
     </row>
-    <row r="443" spans="1:10" hidden="1">
+    <row r="443" spans="1:10">
       <c r="A443">
         <v>2039</v>
       </c>
@@ -43903,7 +43892,7 @@
       </c>
       <c r="J443" s="7"/>
     </row>
-    <row r="444" spans="1:10" hidden="1">
+    <row r="444" spans="1:10">
       <c r="A444">
         <v>2040</v>
       </c>
@@ -43935,7 +43924,7 @@
       </c>
       <c r="J444" s="7"/>
     </row>
-    <row r="445" spans="1:10" hidden="1">
+    <row r="445" spans="1:10">
       <c r="A445">
         <v>2030</v>
       </c>
@@ -43967,7 +43956,7 @@
       </c>
       <c r="J445" s="7"/>
     </row>
-    <row r="446" spans="1:10" hidden="1">
+    <row r="446" spans="1:10">
       <c r="A446">
         <v>2031</v>
       </c>
@@ -43999,7 +43988,7 @@
       </c>
       <c r="J446" s="7"/>
     </row>
-    <row r="447" spans="1:10" hidden="1">
+    <row r="447" spans="1:10">
       <c r="A447">
         <v>2032</v>
       </c>
@@ -44031,7 +44020,7 @@
       </c>
       <c r="J447" s="7"/>
     </row>
-    <row r="448" spans="1:10" hidden="1">
+    <row r="448" spans="1:10">
       <c r="A448">
         <v>2033</v>
       </c>
@@ -44063,7 +44052,7 @@
       </c>
       <c r="J448" s="7"/>
     </row>
-    <row r="449" spans="1:10" hidden="1">
+    <row r="449" spans="1:10">
       <c r="A449">
         <v>2034</v>
       </c>
@@ -44095,7 +44084,7 @@
       </c>
       <c r="J449" s="7"/>
     </row>
-    <row r="450" spans="1:10" hidden="1">
+    <row r="450" spans="1:10">
       <c r="A450">
         <v>2035</v>
       </c>
@@ -44127,7 +44116,7 @@
       </c>
       <c r="J450" s="7"/>
     </row>
-    <row r="451" spans="1:10" hidden="1">
+    <row r="451" spans="1:10">
       <c r="A451">
         <v>2036</v>
       </c>
@@ -44159,7 +44148,7 @@
       </c>
       <c r="J451" s="7"/>
     </row>
-    <row r="452" spans="1:10" hidden="1">
+    <row r="452" spans="1:10">
       <c r="A452">
         <v>2037</v>
       </c>
@@ -44191,7 +44180,7 @@
       </c>
       <c r="J452" s="7"/>
     </row>
-    <row r="453" spans="1:10" hidden="1">
+    <row r="453" spans="1:10">
       <c r="A453">
         <v>2038</v>
       </c>
@@ -44223,7 +44212,7 @@
       </c>
       <c r="J453" s="7"/>
     </row>
-    <row r="454" spans="1:10" hidden="1">
+    <row r="454" spans="1:10">
       <c r="A454">
         <v>2039</v>
       </c>
@@ -44255,7 +44244,7 @@
       </c>
       <c r="J454" s="7"/>
     </row>
-    <row r="455" spans="1:10" hidden="1">
+    <row r="455" spans="1:10">
       <c r="A455">
         <v>2040</v>
       </c>
@@ -44287,7 +44276,7 @@
       </c>
       <c r="J455" s="7"/>
     </row>
-    <row r="456" spans="1:10" hidden="1">
+    <row r="456" spans="1:10">
       <c r="A456">
         <v>2030</v>
       </c>
@@ -44319,7 +44308,7 @@
       </c>
       <c r="J456" s="7"/>
     </row>
-    <row r="457" spans="1:10" hidden="1">
+    <row r="457" spans="1:10">
       <c r="A457">
         <v>2031</v>
       </c>
@@ -44351,7 +44340,7 @@
       </c>
       <c r="J457" s="7"/>
     </row>
-    <row r="458" spans="1:10" hidden="1">
+    <row r="458" spans="1:10">
       <c r="A458">
         <v>2032</v>
       </c>
@@ -44383,7 +44372,7 @@
       </c>
       <c r="J458" s="7"/>
     </row>
-    <row r="459" spans="1:10" hidden="1">
+    <row r="459" spans="1:10">
       <c r="A459">
         <v>2033</v>
       </c>
@@ -44415,7 +44404,7 @@
       </c>
       <c r="J459" s="7"/>
     </row>
-    <row r="460" spans="1:10" hidden="1">
+    <row r="460" spans="1:10">
       <c r="A460">
         <v>2034</v>
       </c>
@@ -44447,7 +44436,7 @@
       </c>
       <c r="J460" s="7"/>
     </row>
-    <row r="461" spans="1:10" hidden="1">
+    <row r="461" spans="1:10">
       <c r="A461">
         <v>2035</v>
       </c>
@@ -44479,7 +44468,7 @@
       </c>
       <c r="J461" s="7"/>
     </row>
-    <row r="462" spans="1:10" hidden="1">
+    <row r="462" spans="1:10">
       <c r="A462">
         <v>2036</v>
       </c>
@@ -44511,7 +44500,7 @@
       </c>
       <c r="J462" s="7"/>
     </row>
-    <row r="463" spans="1:10" hidden="1">
+    <row r="463" spans="1:10">
       <c r="A463">
         <v>2037</v>
       </c>
@@ -44543,7 +44532,7 @@
       </c>
       <c r="J463" s="7"/>
     </row>
-    <row r="464" spans="1:10" hidden="1">
+    <row r="464" spans="1:10">
       <c r="A464">
         <v>2038</v>
       </c>
@@ -44575,7 +44564,7 @@
       </c>
       <c r="J464" s="7"/>
     </row>
-    <row r="465" spans="1:10" hidden="1">
+    <row r="465" spans="1:10">
       <c r="A465">
         <v>2039</v>
       </c>
@@ -44607,7 +44596,7 @@
       </c>
       <c r="J465" s="7"/>
     </row>
-    <row r="466" spans="1:10" hidden="1">
+    <row r="466" spans="1:10">
       <c r="A466">
         <v>2040</v>
       </c>
@@ -44639,7 +44628,7 @@
       </c>
       <c r="J466" s="7"/>
     </row>
-    <row r="467" spans="1:10" hidden="1">
+    <row r="467" spans="1:10">
       <c r="A467">
         <v>2030</v>
       </c>
@@ -44671,7 +44660,7 @@
       </c>
       <c r="J467" s="7"/>
     </row>
-    <row r="468" spans="1:10" hidden="1">
+    <row r="468" spans="1:10">
       <c r="A468">
         <v>2031</v>
       </c>
@@ -44703,7 +44692,7 @@
       </c>
       <c r="J468" s="7"/>
     </row>
-    <row r="469" spans="1:10" hidden="1">
+    <row r="469" spans="1:10">
       <c r="A469">
         <v>2032</v>
       </c>
@@ -44735,7 +44724,7 @@
       </c>
       <c r="J469" s="7"/>
     </row>
-    <row r="470" spans="1:10" hidden="1">
+    <row r="470" spans="1:10">
       <c r="A470">
         <v>2033</v>
       </c>
@@ -44767,7 +44756,7 @@
       </c>
       <c r="J470" s="7"/>
     </row>
-    <row r="471" spans="1:10" hidden="1">
+    <row r="471" spans="1:10">
       <c r="A471">
         <v>2034</v>
       </c>
@@ -44799,7 +44788,7 @@
       </c>
       <c r="J471" s="7"/>
     </row>
-    <row r="472" spans="1:10" hidden="1">
+    <row r="472" spans="1:10">
       <c r="A472">
         <v>2035</v>
       </c>
@@ -44831,7 +44820,7 @@
       </c>
       <c r="J472" s="7"/>
     </row>
-    <row r="473" spans="1:10" hidden="1">
+    <row r="473" spans="1:10">
       <c r="A473">
         <v>2036</v>
       </c>
@@ -44863,7 +44852,7 @@
       </c>
       <c r="J473" s="7"/>
     </row>
-    <row r="474" spans="1:10" hidden="1">
+    <row r="474" spans="1:10">
       <c r="A474">
         <v>2037</v>
       </c>
@@ -44895,7 +44884,7 @@
       </c>
       <c r="J474" s="7"/>
     </row>
-    <row r="475" spans="1:10" hidden="1">
+    <row r="475" spans="1:10">
       <c r="A475">
         <v>2038</v>
       </c>
@@ -44927,7 +44916,7 @@
       </c>
       <c r="J475" s="7"/>
     </row>
-    <row r="476" spans="1:10" hidden="1">
+    <row r="476" spans="1:10">
       <c r="A476">
         <v>2039</v>
       </c>
@@ -44959,7 +44948,7 @@
       </c>
       <c r="J476" s="7"/>
     </row>
-    <row r="477" spans="1:10" hidden="1">
+    <row r="477" spans="1:10">
       <c r="A477">
         <v>2040</v>
       </c>
@@ -44991,7 +44980,7 @@
       </c>
       <c r="J477" s="7"/>
     </row>
-    <row r="478" spans="1:10" hidden="1">
+    <row r="478" spans="1:10">
       <c r="A478">
         <v>2030</v>
       </c>
@@ -45023,7 +45012,7 @@
       </c>
       <c r="J478" s="7"/>
     </row>
-    <row r="479" spans="1:10" hidden="1">
+    <row r="479" spans="1:10">
       <c r="A479">
         <v>2031</v>
       </c>
@@ -45055,7 +45044,7 @@
       </c>
       <c r="J479" s="7"/>
     </row>
-    <row r="480" spans="1:10" hidden="1">
+    <row r="480" spans="1:10">
       <c r="A480">
         <v>2032</v>
       </c>
@@ -45087,7 +45076,7 @@
       </c>
       <c r="J480" s="7"/>
     </row>
-    <row r="481" spans="1:10" hidden="1">
+    <row r="481" spans="1:10">
       <c r="A481">
         <v>2033</v>
       </c>
@@ -45119,7 +45108,7 @@
       </c>
       <c r="J481" s="7"/>
     </row>
-    <row r="482" spans="1:10" hidden="1">
+    <row r="482" spans="1:10">
       <c r="A482">
         <v>2034</v>
       </c>
@@ -45151,7 +45140,7 @@
       </c>
       <c r="J482" s="7"/>
     </row>
-    <row r="483" spans="1:10" hidden="1">
+    <row r="483" spans="1:10">
       <c r="A483">
         <v>2035</v>
       </c>
@@ -45183,7 +45172,7 @@
       </c>
       <c r="J483" s="7"/>
     </row>
-    <row r="484" spans="1:10" hidden="1">
+    <row r="484" spans="1:10">
       <c r="A484">
         <v>2036</v>
       </c>
@@ -45215,7 +45204,7 @@
       </c>
       <c r="J484" s="7"/>
     </row>
-    <row r="485" spans="1:10" hidden="1">
+    <row r="485" spans="1:10">
       <c r="A485">
         <v>2037</v>
       </c>
@@ -45247,7 +45236,7 @@
       </c>
       <c r="J485" s="7"/>
     </row>
-    <row r="486" spans="1:10" hidden="1">
+    <row r="486" spans="1:10">
       <c r="A486">
         <v>2038</v>
       </c>
@@ -45279,7 +45268,7 @@
       </c>
       <c r="J486" s="7"/>
     </row>
-    <row r="487" spans="1:10" hidden="1">
+    <row r="487" spans="1:10">
       <c r="A487">
         <v>2039</v>
       </c>
@@ -45311,7 +45300,7 @@
       </c>
       <c r="J487" s="7"/>
     </row>
-    <row r="488" spans="1:10" hidden="1">
+    <row r="488" spans="1:10">
       <c r="A488">
         <v>2040</v>
       </c>
@@ -45343,7 +45332,7 @@
       </c>
       <c r="J488" s="7"/>
     </row>
-    <row r="489" spans="1:10" hidden="1">
+    <row r="489" spans="1:10">
       <c r="A489">
         <v>2030</v>
       </c>
@@ -45375,7 +45364,7 @@
       </c>
       <c r="J489" s="7"/>
     </row>
-    <row r="490" spans="1:10" hidden="1">
+    <row r="490" spans="1:10">
       <c r="A490">
         <v>2031</v>
       </c>
@@ -45407,7 +45396,7 @@
       </c>
       <c r="J490" s="7"/>
     </row>
-    <row r="491" spans="1:10" hidden="1">
+    <row r="491" spans="1:10">
       <c r="A491">
         <v>2032</v>
       </c>
@@ -45439,7 +45428,7 @@
       </c>
       <c r="J491" s="7"/>
     </row>
-    <row r="492" spans="1:10" hidden="1">
+    <row r="492" spans="1:10">
       <c r="A492">
         <v>2033</v>
       </c>
@@ -45471,7 +45460,7 @@
       </c>
       <c r="J492" s="7"/>
     </row>
-    <row r="493" spans="1:10" hidden="1">
+    <row r="493" spans="1:10">
       <c r="A493">
         <v>2034</v>
       </c>
@@ -45503,7 +45492,7 @@
       </c>
       <c r="J493" s="7"/>
     </row>
-    <row r="494" spans="1:10" hidden="1">
+    <row r="494" spans="1:10">
       <c r="A494">
         <v>2035</v>
       </c>
@@ -45535,7 +45524,7 @@
       </c>
       <c r="J494" s="7"/>
     </row>
-    <row r="495" spans="1:10" hidden="1">
+    <row r="495" spans="1:10">
       <c r="A495">
         <v>2036</v>
       </c>
@@ -45567,7 +45556,7 @@
       </c>
       <c r="J495" s="7"/>
     </row>
-    <row r="496" spans="1:10" hidden="1">
+    <row r="496" spans="1:10">
       <c r="A496">
         <v>2037</v>
       </c>
@@ -45599,7 +45588,7 @@
       </c>
       <c r="J496" s="7"/>
     </row>
-    <row r="497" spans="1:10" hidden="1">
+    <row r="497" spans="1:10">
       <c r="A497">
         <v>2038</v>
       </c>
@@ -45631,7 +45620,7 @@
       </c>
       <c r="J497" s="7"/>
     </row>
-    <row r="498" spans="1:10" hidden="1">
+    <row r="498" spans="1:10">
       <c r="A498">
         <v>2039</v>
       </c>
@@ -45663,7 +45652,7 @@
       </c>
       <c r="J498" s="7"/>
     </row>
-    <row r="499" spans="1:10" hidden="1">
+    <row r="499" spans="1:10">
       <c r="A499">
         <v>2040</v>
       </c>
@@ -45695,7 +45684,7 @@
       </c>
       <c r="J499" s="7"/>
     </row>
-    <row r="500" spans="1:10" hidden="1">
+    <row r="500" spans="1:10">
       <c r="A500">
         <v>2030</v>
       </c>
@@ -45727,7 +45716,7 @@
       </c>
       <c r="J500" s="7"/>
     </row>
-    <row r="501" spans="1:10" hidden="1">
+    <row r="501" spans="1:10">
       <c r="A501">
         <v>2031</v>
       </c>
@@ -45759,7 +45748,7 @@
       </c>
       <c r="J501" s="7"/>
     </row>
-    <row r="502" spans="1:10" hidden="1">
+    <row r="502" spans="1:10">
       <c r="A502">
         <v>2032</v>
       </c>
@@ -45791,7 +45780,7 @@
       </c>
       <c r="J502" s="7"/>
     </row>
-    <row r="503" spans="1:10" hidden="1">
+    <row r="503" spans="1:10">
       <c r="A503">
         <v>2033</v>
       </c>
@@ -45823,7 +45812,7 @@
       </c>
       <c r="J503" s="7"/>
     </row>
-    <row r="504" spans="1:10" hidden="1">
+    <row r="504" spans="1:10">
       <c r="A504">
         <v>2034</v>
       </c>
@@ -45855,7 +45844,7 @@
       </c>
       <c r="J504" s="7"/>
     </row>
-    <row r="505" spans="1:10" hidden="1">
+    <row r="505" spans="1:10">
       <c r="A505">
         <v>2035</v>
       </c>
@@ -45887,7 +45876,7 @@
       </c>
       <c r="J505" s="7"/>
     </row>
-    <row r="506" spans="1:10" hidden="1">
+    <row r="506" spans="1:10">
       <c r="A506">
         <v>2036</v>
       </c>
@@ -45919,7 +45908,7 @@
       </c>
       <c r="J506" s="7"/>
     </row>
-    <row r="507" spans="1:10" hidden="1">
+    <row r="507" spans="1:10">
       <c r="A507">
         <v>2037</v>
       </c>
@@ -45951,7 +45940,7 @@
       </c>
       <c r="J507" s="7"/>
     </row>
-    <row r="508" spans="1:10" hidden="1">
+    <row r="508" spans="1:10">
       <c r="A508">
         <v>2038</v>
       </c>
@@ -45983,7 +45972,7 @@
       </c>
       <c r="J508" s="7"/>
     </row>
-    <row r="509" spans="1:10" hidden="1">
+    <row r="509" spans="1:10">
       <c r="A509">
         <v>2039</v>
       </c>
@@ -46015,7 +46004,7 @@
       </c>
       <c r="J509" s="7"/>
     </row>
-    <row r="510" spans="1:10" hidden="1">
+    <row r="510" spans="1:10">
       <c r="A510">
         <v>2040</v>
       </c>
@@ -46047,7 +46036,7 @@
       </c>
       <c r="J510" s="7"/>
     </row>
-    <row r="511" spans="1:10" hidden="1">
+    <row r="511" spans="1:10">
       <c r="A511">
         <v>2030</v>
       </c>
@@ -46079,7 +46068,7 @@
       </c>
       <c r="J511" s="7"/>
     </row>
-    <row r="512" spans="1:10" hidden="1">
+    <row r="512" spans="1:10">
       <c r="A512">
         <v>2031</v>
       </c>
@@ -46111,7 +46100,7 @@
       </c>
       <c r="J512" s="7"/>
     </row>
-    <row r="513" spans="1:10" hidden="1">
+    <row r="513" spans="1:10">
       <c r="A513">
         <v>2032</v>
       </c>
@@ -46143,7 +46132,7 @@
       </c>
       <c r="J513" s="7"/>
     </row>
-    <row r="514" spans="1:10" hidden="1">
+    <row r="514" spans="1:10">
       <c r="A514">
         <v>2033</v>
       </c>
@@ -46175,7 +46164,7 @@
       </c>
       <c r="J514" s="7"/>
     </row>
-    <row r="515" spans="1:10" hidden="1">
+    <row r="515" spans="1:10">
       <c r="A515">
         <v>2034</v>
       </c>
@@ -46207,7 +46196,7 @@
       </c>
       <c r="J515" s="7"/>
     </row>
-    <row r="516" spans="1:10" hidden="1">
+    <row r="516" spans="1:10">
       <c r="A516">
         <v>2035</v>
       </c>
@@ -46239,7 +46228,7 @@
       </c>
       <c r="J516" s="7"/>
     </row>
-    <row r="517" spans="1:10" hidden="1">
+    <row r="517" spans="1:10">
       <c r="A517">
         <v>2036</v>
       </c>
@@ -46271,7 +46260,7 @@
       </c>
       <c r="J517" s="7"/>
     </row>
-    <row r="518" spans="1:10" hidden="1">
+    <row r="518" spans="1:10">
       <c r="A518">
         <v>2037</v>
       </c>
@@ -46303,7 +46292,7 @@
       </c>
       <c r="J518" s="7"/>
     </row>
-    <row r="519" spans="1:10" hidden="1">
+    <row r="519" spans="1:10">
       <c r="A519">
         <v>2038</v>
       </c>
@@ -46335,7 +46324,7 @@
       </c>
       <c r="J519" s="7"/>
     </row>
-    <row r="520" spans="1:10" hidden="1">
+    <row r="520" spans="1:10">
       <c r="A520">
         <v>2039</v>
       </c>
@@ -46367,7 +46356,7 @@
       </c>
       <c r="J520" s="7"/>
     </row>
-    <row r="521" spans="1:10" hidden="1">
+    <row r="521" spans="1:10">
       <c r="A521">
         <v>2040</v>
       </c>
@@ -46399,7 +46388,7 @@
       </c>
       <c r="J521" s="7"/>
     </row>
-    <row r="522" spans="1:10" hidden="1">
+    <row r="522" spans="1:10">
       <c r="A522">
         <v>2030</v>
       </c>
@@ -46431,7 +46420,7 @@
       </c>
       <c r="J522" s="7"/>
     </row>
-    <row r="523" spans="1:10" hidden="1">
+    <row r="523" spans="1:10">
       <c r="A523">
         <v>2031</v>
       </c>
@@ -46463,7 +46452,7 @@
       </c>
       <c r="J523" s="7"/>
     </row>
-    <row r="524" spans="1:10" hidden="1">
+    <row r="524" spans="1:10">
       <c r="A524">
         <v>2032</v>
       </c>
@@ -46495,7 +46484,7 @@
       </c>
       <c r="J524" s="7"/>
     </row>
-    <row r="525" spans="1:10" hidden="1">
+    <row r="525" spans="1:10">
       <c r="A525">
         <v>2033</v>
       </c>
@@ -46527,7 +46516,7 @@
       </c>
       <c r="J525" s="7"/>
     </row>
-    <row r="526" spans="1:10" hidden="1">
+    <row r="526" spans="1:10">
       <c r="A526">
         <v>2034</v>
       </c>
@@ -46559,7 +46548,7 @@
       </c>
       <c r="J526" s="7"/>
     </row>
-    <row r="527" spans="1:10" hidden="1">
+    <row r="527" spans="1:10">
       <c r="A527">
         <v>2035</v>
       </c>
@@ -46591,7 +46580,7 @@
       </c>
       <c r="J527" s="7"/>
     </row>
-    <row r="528" spans="1:10" hidden="1">
+    <row r="528" spans="1:10">
       <c r="A528">
         <v>2036</v>
       </c>
@@ -46623,7 +46612,7 @@
       </c>
       <c r="J528" s="7"/>
     </row>
-    <row r="529" spans="1:10" hidden="1">
+    <row r="529" spans="1:10">
       <c r="A529">
         <v>2037</v>
       </c>
@@ -46655,7 +46644,7 @@
       </c>
       <c r="J529" s="7"/>
     </row>
-    <row r="530" spans="1:10" hidden="1">
+    <row r="530" spans="1:10">
       <c r="A530">
         <v>2038</v>
       </c>
@@ -46687,7 +46676,7 @@
       </c>
       <c r="J530" s="7"/>
     </row>
-    <row r="531" spans="1:10" hidden="1">
+    <row r="531" spans="1:10">
       <c r="A531">
         <v>2039</v>
       </c>
@@ -46719,7 +46708,7 @@
       </c>
       <c r="J531" s="7"/>
     </row>
-    <row r="532" spans="1:10" hidden="1">
+    <row r="532" spans="1:10">
       <c r="A532">
         <v>2040</v>
       </c>
@@ -46751,7 +46740,7 @@
       </c>
       <c r="J532" s="7"/>
     </row>
-    <row r="533" spans="1:10" hidden="1">
+    <row r="533" spans="1:10">
       <c r="A533">
         <v>2030</v>
       </c>
@@ -46783,7 +46772,7 @@
       </c>
       <c r="J533" s="7"/>
     </row>
-    <row r="534" spans="1:10" hidden="1">
+    <row r="534" spans="1:10">
       <c r="A534">
         <v>2031</v>
       </c>
@@ -46815,7 +46804,7 @@
       </c>
       <c r="J534" s="7"/>
     </row>
-    <row r="535" spans="1:10" hidden="1">
+    <row r="535" spans="1:10">
       <c r="A535">
         <v>2032</v>
       </c>
@@ -46847,7 +46836,7 @@
       </c>
       <c r="J535" s="7"/>
     </row>
-    <row r="536" spans="1:10" hidden="1">
+    <row r="536" spans="1:10">
       <c r="A536">
         <v>2033</v>
       </c>
@@ -46879,7 +46868,7 @@
       </c>
       <c r="J536" s="7"/>
     </row>
-    <row r="537" spans="1:10" hidden="1">
+    <row r="537" spans="1:10">
       <c r="A537">
         <v>2034</v>
       </c>
@@ -46911,7 +46900,7 @@
       </c>
       <c r="J537" s="7"/>
     </row>
-    <row r="538" spans="1:10" hidden="1">
+    <row r="538" spans="1:10">
       <c r="A538">
         <v>2035</v>
       </c>
@@ -46943,7 +46932,7 @@
       </c>
       <c r="J538" s="7"/>
     </row>
-    <row r="539" spans="1:10" hidden="1">
+    <row r="539" spans="1:10">
       <c r="A539">
         <v>2036</v>
       </c>
@@ -46975,7 +46964,7 @@
       </c>
       <c r="J539" s="7"/>
     </row>
-    <row r="540" spans="1:10" hidden="1">
+    <row r="540" spans="1:10">
       <c r="A540">
         <v>2037</v>
       </c>
@@ -47007,7 +46996,7 @@
       </c>
       <c r="J540" s="7"/>
     </row>
-    <row r="541" spans="1:10" hidden="1">
+    <row r="541" spans="1:10">
       <c r="A541">
         <v>2038</v>
       </c>
@@ -47039,7 +47028,7 @@
       </c>
       <c r="J541" s="7"/>
     </row>
-    <row r="542" spans="1:10" hidden="1">
+    <row r="542" spans="1:10">
       <c r="A542">
         <v>2039</v>
       </c>
@@ -47071,7 +47060,7 @@
       </c>
       <c r="J542" s="7"/>
     </row>
-    <row r="543" spans="1:10" hidden="1">
+    <row r="543" spans="1:10">
       <c r="A543">
         <v>2040</v>
       </c>
@@ -47103,7 +47092,7 @@
       </c>
       <c r="J543" s="7"/>
     </row>
-    <row r="544" spans="1:10" hidden="1">
+    <row r="544" spans="1:10">
       <c r="A544">
         <v>2030</v>
       </c>
@@ -47135,7 +47124,7 @@
       </c>
       <c r="J544" s="7"/>
     </row>
-    <row r="545" spans="1:10" hidden="1">
+    <row r="545" spans="1:10">
       <c r="A545">
         <v>2031</v>
       </c>
@@ -47167,7 +47156,7 @@
       </c>
       <c r="J545" s="7"/>
     </row>
-    <row r="546" spans="1:10" hidden="1">
+    <row r="546" spans="1:10">
       <c r="A546">
         <v>2032</v>
       </c>
@@ -47199,7 +47188,7 @@
       </c>
       <c r="J546" s="7"/>
     </row>
-    <row r="547" spans="1:10" hidden="1">
+    <row r="547" spans="1:10">
       <c r="A547">
         <v>2033</v>
       </c>
@@ -47231,7 +47220,7 @@
       </c>
       <c r="J547" s="7"/>
     </row>
-    <row r="548" spans="1:10" hidden="1">
+    <row r="548" spans="1:10">
       <c r="A548">
         <v>2034</v>
       </c>
@@ -47263,7 +47252,7 @@
       </c>
       <c r="J548" s="7"/>
     </row>
-    <row r="549" spans="1:10" hidden="1">
+    <row r="549" spans="1:10">
       <c r="A549">
         <v>2035</v>
       </c>
@@ -47295,7 +47284,7 @@
       </c>
       <c r="J549" s="7"/>
     </row>
-    <row r="550" spans="1:10" hidden="1">
+    <row r="550" spans="1:10">
       <c r="A550">
         <v>2036</v>
       </c>
@@ -47327,7 +47316,7 @@
       </c>
       <c r="J550" s="7"/>
     </row>
-    <row r="551" spans="1:10" hidden="1">
+    <row r="551" spans="1:10">
       <c r="A551">
         <v>2037</v>
       </c>
@@ -47359,7 +47348,7 @@
       </c>
       <c r="J551" s="7"/>
     </row>
-    <row r="552" spans="1:10" hidden="1">
+    <row r="552" spans="1:10">
       <c r="A552">
         <v>2038</v>
       </c>
@@ -47391,7 +47380,7 @@
       </c>
       <c r="J552" s="7"/>
     </row>
-    <row r="553" spans="1:10" hidden="1">
+    <row r="553" spans="1:10">
       <c r="A553">
         <v>2039</v>
       </c>
@@ -47423,7 +47412,7 @@
       </c>
       <c r="J553" s="7"/>
     </row>
-    <row r="554" spans="1:10" hidden="1">
+    <row r="554" spans="1:10">
       <c r="A554">
         <v>2040</v>
       </c>
@@ -47455,7 +47444,7 @@
       </c>
       <c r="J554" s="7"/>
     </row>
-    <row r="555" spans="1:10" hidden="1">
+    <row r="555" spans="1:10">
       <c r="A555">
         <v>2030</v>
       </c>
@@ -47487,7 +47476,7 @@
       </c>
       <c r="J555" s="7"/>
     </row>
-    <row r="556" spans="1:10" hidden="1">
+    <row r="556" spans="1:10">
       <c r="A556">
         <v>2031</v>
       </c>
@@ -47519,7 +47508,7 @@
       </c>
       <c r="J556" s="7"/>
     </row>
-    <row r="557" spans="1:10" hidden="1">
+    <row r="557" spans="1:10">
       <c r="A557">
         <v>2032</v>
       </c>
@@ -47551,7 +47540,7 @@
       </c>
       <c r="J557" s="7"/>
     </row>
-    <row r="558" spans="1:10" hidden="1">
+    <row r="558" spans="1:10">
       <c r="A558">
         <v>2033</v>
       </c>
@@ -47583,7 +47572,7 @@
       </c>
       <c r="J558" s="7"/>
     </row>
-    <row r="559" spans="1:10" hidden="1">
+    <row r="559" spans="1:10">
       <c r="A559">
         <v>2034</v>
       </c>
@@ -47615,7 +47604,7 @@
       </c>
       <c r="J559" s="7"/>
     </row>
-    <row r="560" spans="1:10" hidden="1">
+    <row r="560" spans="1:10">
       <c r="A560">
         <v>2035</v>
       </c>
@@ -47647,7 +47636,7 @@
       </c>
       <c r="J560" s="7"/>
     </row>
-    <row r="561" spans="1:10" hidden="1">
+    <row r="561" spans="1:10">
       <c r="A561">
         <v>2036</v>
       </c>
@@ -47679,7 +47668,7 @@
       </c>
       <c r="J561" s="7"/>
     </row>
-    <row r="562" spans="1:10" hidden="1">
+    <row r="562" spans="1:10">
       <c r="A562">
         <v>2037</v>
       </c>
@@ -47711,7 +47700,7 @@
       </c>
       <c r="J562" s="7"/>
     </row>
-    <row r="563" spans="1:10" hidden="1">
+    <row r="563" spans="1:10">
       <c r="A563">
         <v>2038</v>
       </c>
@@ -47743,7 +47732,7 @@
       </c>
       <c r="J563" s="7"/>
     </row>
-    <row r="564" spans="1:10" hidden="1">
+    <row r="564" spans="1:10">
       <c r="A564">
         <v>2039</v>
       </c>
@@ -47775,7 +47764,7 @@
       </c>
       <c r="J564" s="7"/>
     </row>
-    <row r="565" spans="1:10" hidden="1">
+    <row r="565" spans="1:10">
       <c r="A565">
         <v>2040</v>
       </c>
@@ -47807,7 +47796,7 @@
       </c>
       <c r="J565" s="7"/>
     </row>
-    <row r="566" spans="1:10" hidden="1">
+    <row r="566" spans="1:10">
       <c r="A566">
         <v>2030</v>
       </c>
@@ -47839,7 +47828,7 @@
       </c>
       <c r="J566" s="7"/>
     </row>
-    <row r="567" spans="1:10" hidden="1">
+    <row r="567" spans="1:10">
       <c r="A567">
         <v>2031</v>
       </c>
@@ -47871,7 +47860,7 @@
       </c>
       <c r="J567" s="7"/>
     </row>
-    <row r="568" spans="1:10" hidden="1">
+    <row r="568" spans="1:10">
       <c r="A568">
         <v>2032</v>
       </c>
@@ -47903,7 +47892,7 @@
       </c>
       <c r="J568" s="7"/>
     </row>
-    <row r="569" spans="1:10" hidden="1">
+    <row r="569" spans="1:10">
       <c r="A569">
         <v>2033</v>
       </c>
@@ -47935,7 +47924,7 @@
       </c>
       <c r="J569" s="7"/>
     </row>
-    <row r="570" spans="1:10" hidden="1">
+    <row r="570" spans="1:10">
       <c r="A570">
         <v>2034</v>
       </c>
@@ -47967,7 +47956,7 @@
       </c>
       <c r="J570" s="7"/>
     </row>
-    <row r="571" spans="1:10" hidden="1">
+    <row r="571" spans="1:10">
       <c r="A571">
         <v>2035</v>
       </c>
@@ -47999,7 +47988,7 @@
       </c>
       <c r="J571" s="7"/>
     </row>
-    <row r="572" spans="1:10" hidden="1">
+    <row r="572" spans="1:10">
       <c r="A572">
         <v>2036</v>
       </c>
@@ -48031,7 +48020,7 @@
       </c>
       <c r="J572" s="7"/>
     </row>
-    <row r="573" spans="1:10" hidden="1">
+    <row r="573" spans="1:10">
       <c r="A573">
         <v>2037</v>
       </c>
@@ -48063,7 +48052,7 @@
       </c>
       <c r="J573" s="7"/>
     </row>
-    <row r="574" spans="1:10" hidden="1">
+    <row r="574" spans="1:10">
       <c r="A574">
         <v>2038</v>
       </c>
@@ -48095,7 +48084,7 @@
       </c>
       <c r="J574" s="7"/>
     </row>
-    <row r="575" spans="1:10" hidden="1">
+    <row r="575" spans="1:10">
       <c r="A575">
         <v>2039</v>
       </c>
@@ -48127,7 +48116,7 @@
       </c>
       <c r="J575" s="7"/>
     </row>
-    <row r="576" spans="1:10" hidden="1">
+    <row r="576" spans="1:10">
       <c r="A576">
         <v>2040</v>
       </c>
@@ -48159,7 +48148,7 @@
       </c>
       <c r="J576" s="7"/>
     </row>
-    <row r="577" spans="1:10" hidden="1">
+    <row r="577" spans="1:10">
       <c r="A577">
         <v>2030</v>
       </c>
@@ -48191,7 +48180,7 @@
       </c>
       <c r="J577" s="7"/>
     </row>
-    <row r="578" spans="1:10" hidden="1">
+    <row r="578" spans="1:10">
       <c r="A578">
         <v>2031</v>
       </c>
@@ -48223,7 +48212,7 @@
       </c>
       <c r="J578" s="7"/>
     </row>
-    <row r="579" spans="1:10" hidden="1">
+    <row r="579" spans="1:10">
       <c r="A579">
         <v>2032</v>
       </c>
@@ -48255,7 +48244,7 @@
       </c>
       <c r="J579" s="7"/>
     </row>
-    <row r="580" spans="1:10" hidden="1">
+    <row r="580" spans="1:10">
       <c r="A580">
         <v>2033</v>
       </c>
@@ -48287,7 +48276,7 @@
       </c>
       <c r="J580" s="7"/>
     </row>
-    <row r="581" spans="1:10" hidden="1">
+    <row r="581" spans="1:10">
       <c r="A581">
         <v>2034</v>
       </c>
@@ -48319,7 +48308,7 @@
       </c>
       <c r="J581" s="7"/>
     </row>
-    <row r="582" spans="1:10" hidden="1">
+    <row r="582" spans="1:10">
       <c r="A582">
         <v>2035</v>
       </c>
@@ -48351,7 +48340,7 @@
       </c>
       <c r="J582" s="7"/>
     </row>
-    <row r="583" spans="1:10" hidden="1">
+    <row r="583" spans="1:10">
       <c r="A583">
         <v>2036</v>
       </c>
@@ -48383,7 +48372,7 @@
       </c>
       <c r="J583" s="7"/>
     </row>
-    <row r="584" spans="1:10" hidden="1">
+    <row r="584" spans="1:10">
       <c r="A584">
         <v>2037</v>
       </c>
@@ -48415,7 +48404,7 @@
       </c>
       <c r="J584" s="7"/>
     </row>
-    <row r="585" spans="1:10" hidden="1">
+    <row r="585" spans="1:10">
       <c r="A585">
         <v>2038</v>
       </c>
@@ -48447,7 +48436,7 @@
       </c>
       <c r="J585" s="7"/>
     </row>
-    <row r="586" spans="1:10" hidden="1">
+    <row r="586" spans="1:10">
       <c r="A586">
         <v>2039</v>
       </c>
@@ -48479,7 +48468,7 @@
       </c>
       <c r="J586" s="7"/>
     </row>
-    <row r="587" spans="1:10" hidden="1">
+    <row r="587" spans="1:10">
       <c r="A587">
         <v>2040</v>
       </c>
@@ -48511,7 +48500,7 @@
       </c>
       <c r="J587" s="7"/>
     </row>
-    <row r="588" spans="1:10" hidden="1">
+    <row r="588" spans="1:10">
       <c r="A588">
         <v>2030</v>
       </c>
@@ -48543,7 +48532,7 @@
       </c>
       <c r="J588" s="7"/>
     </row>
-    <row r="589" spans="1:10" hidden="1">
+    <row r="589" spans="1:10">
       <c r="A589">
         <v>2031</v>
       </c>
@@ -48575,7 +48564,7 @@
       </c>
       <c r="J589" s="7"/>
     </row>
-    <row r="590" spans="1:10" hidden="1">
+    <row r="590" spans="1:10">
       <c r="A590">
         <v>2032</v>
       </c>
@@ -48607,7 +48596,7 @@
       </c>
       <c r="J590" s="7"/>
     </row>
-    <row r="591" spans="1:10" hidden="1">
+    <row r="591" spans="1:10">
       <c r="A591">
         <v>2033</v>
       </c>
@@ -48639,7 +48628,7 @@
       </c>
       <c r="J591" s="7"/>
     </row>
-    <row r="592" spans="1:10" hidden="1">
+    <row r="592" spans="1:10">
       <c r="A592">
         <v>2034</v>
       </c>
@@ -48671,7 +48660,7 @@
       </c>
       <c r="J592" s="7"/>
     </row>
-    <row r="593" spans="1:10" hidden="1">
+    <row r="593" spans="1:10">
       <c r="A593">
         <v>2035</v>
       </c>
@@ -48703,7 +48692,7 @@
       </c>
       <c r="J593" s="7"/>
     </row>
-    <row r="594" spans="1:10" hidden="1">
+    <row r="594" spans="1:10">
       <c r="A594">
         <v>2036</v>
       </c>
@@ -48735,7 +48724,7 @@
       </c>
       <c r="J594" s="7"/>
     </row>
-    <row r="595" spans="1:10" hidden="1">
+    <row r="595" spans="1:10">
       <c r="A595">
         <v>2037</v>
       </c>
@@ -48767,7 +48756,7 @@
       </c>
       <c r="J595" s="7"/>
     </row>
-    <row r="596" spans="1:10" hidden="1">
+    <row r="596" spans="1:10">
       <c r="A596">
         <v>2038</v>
       </c>
@@ -48799,7 +48788,7 @@
       </c>
       <c r="J596" s="7"/>
     </row>
-    <row r="597" spans="1:10" hidden="1">
+    <row r="597" spans="1:10">
       <c r="A597">
         <v>2039</v>
       </c>
@@ -48831,7 +48820,7 @@
       </c>
       <c r="J597" s="7"/>
     </row>
-    <row r="598" spans="1:10" hidden="1">
+    <row r="598" spans="1:10">
       <c r="A598">
         <v>2040</v>
       </c>
@@ -48863,7 +48852,7 @@
       </c>
       <c r="J598" s="7"/>
     </row>
-    <row r="599" spans="1:10" hidden="1">
+    <row r="599" spans="1:10">
       <c r="A599">
         <v>2030</v>
       </c>
@@ -48895,7 +48884,7 @@
       </c>
       <c r="J599" s="7"/>
     </row>
-    <row r="600" spans="1:10" hidden="1">
+    <row r="600" spans="1:10">
       <c r="A600">
         <v>2031</v>
       </c>
@@ -48927,7 +48916,7 @@
       </c>
       <c r="J600" s="7"/>
     </row>
-    <row r="601" spans="1:10" hidden="1">
+    <row r="601" spans="1:10">
       <c r="A601">
         <v>2032</v>
       </c>
@@ -48959,7 +48948,7 @@
       </c>
       <c r="J601" s="7"/>
     </row>
-    <row r="602" spans="1:10" hidden="1">
+    <row r="602" spans="1:10">
       <c r="A602">
         <v>2033</v>
       </c>
@@ -48991,7 +48980,7 @@
       </c>
       <c r="J602" s="7"/>
     </row>
-    <row r="603" spans="1:10" hidden="1">
+    <row r="603" spans="1:10">
       <c r="A603">
         <v>2034</v>
       </c>
@@ -49023,7 +49012,7 @@
       </c>
       <c r="J603" s="7"/>
     </row>
-    <row r="604" spans="1:10" hidden="1">
+    <row r="604" spans="1:10">
       <c r="A604">
         <v>2035</v>
       </c>
@@ -49055,7 +49044,7 @@
       </c>
       <c r="J604" s="7"/>
     </row>
-    <row r="605" spans="1:10" hidden="1">
+    <row r="605" spans="1:10">
       <c r="A605">
         <v>2036</v>
       </c>
@@ -49087,7 +49076,7 @@
       </c>
       <c r="J605" s="7"/>
     </row>
-    <row r="606" spans="1:10" hidden="1">
+    <row r="606" spans="1:10">
       <c r="A606">
         <v>2037</v>
       </c>
@@ -49119,7 +49108,7 @@
       </c>
       <c r="J606" s="7"/>
     </row>
-    <row r="607" spans="1:10" hidden="1">
+    <row r="607" spans="1:10">
       <c r="A607">
         <v>2038</v>
       </c>
@@ -49151,7 +49140,7 @@
       </c>
       <c r="J607" s="7"/>
     </row>
-    <row r="608" spans="1:10" hidden="1">
+    <row r="608" spans="1:10">
       <c r="A608">
         <v>2039</v>
       </c>
@@ -49183,7 +49172,7 @@
       </c>
       <c r="J608" s="7"/>
     </row>
-    <row r="609" spans="1:10" hidden="1">
+    <row r="609" spans="1:10">
       <c r="A609">
         <v>2040</v>
       </c>
@@ -49215,7 +49204,7 @@
       </c>
       <c r="J609" s="7"/>
     </row>
-    <row r="610" spans="1:10" hidden="1">
+    <row r="610" spans="1:10">
       <c r="A610">
         <v>2030</v>
       </c>
@@ -49247,7 +49236,7 @@
       </c>
       <c r="J610" s="7"/>
     </row>
-    <row r="611" spans="1:10" hidden="1">
+    <row r="611" spans="1:10">
       <c r="A611">
         <v>2031</v>
       </c>
@@ -49279,7 +49268,7 @@
       </c>
       <c r="J611" s="7"/>
     </row>
-    <row r="612" spans="1:10" hidden="1">
+    <row r="612" spans="1:10">
       <c r="A612">
         <v>2032</v>
       </c>
@@ -49311,7 +49300,7 @@
       </c>
       <c r="J612" s="7"/>
     </row>
-    <row r="613" spans="1:10" hidden="1">
+    <row r="613" spans="1:10">
       <c r="A613">
         <v>2033</v>
       </c>
@@ -49343,7 +49332,7 @@
       </c>
       <c r="J613" s="7"/>
     </row>
-    <row r="614" spans="1:10" hidden="1">
+    <row r="614" spans="1:10">
       <c r="A614">
         <v>2034</v>
       </c>
@@ -49375,7 +49364,7 @@
       </c>
       <c r="J614" s="7"/>
     </row>
-    <row r="615" spans="1:10" hidden="1">
+    <row r="615" spans="1:10">
       <c r="A615">
         <v>2035</v>
       </c>
@@ -49407,7 +49396,7 @@
       </c>
       <c r="J615" s="7"/>
     </row>
-    <row r="616" spans="1:10" hidden="1">
+    <row r="616" spans="1:10">
       <c r="A616">
         <v>2036</v>
       </c>
@@ -49439,7 +49428,7 @@
       </c>
       <c r="J616" s="7"/>
     </row>
-    <row r="617" spans="1:10" hidden="1">
+    <row r="617" spans="1:10">
       <c r="A617">
         <v>2037</v>
       </c>
@@ -49471,7 +49460,7 @@
       </c>
       <c r="J617" s="7"/>
     </row>
-    <row r="618" spans="1:10" hidden="1">
+    <row r="618" spans="1:10">
       <c r="A618">
         <v>2038</v>
       </c>
@@ -49503,7 +49492,7 @@
       </c>
       <c r="J618" s="7"/>
     </row>
-    <row r="619" spans="1:10" hidden="1">
+    <row r="619" spans="1:10">
       <c r="A619">
         <v>2039</v>
       </c>
@@ -49535,7 +49524,7 @@
       </c>
       <c r="J619" s="7"/>
     </row>
-    <row r="620" spans="1:10" hidden="1">
+    <row r="620" spans="1:10">
       <c r="A620">
         <v>2040</v>
       </c>
@@ -49567,7 +49556,7 @@
       </c>
       <c r="J620" s="7"/>
     </row>
-    <row r="621" spans="1:10" hidden="1">
+    <row r="621" spans="1:10">
       <c r="A621">
         <v>2030</v>
       </c>
@@ -49599,7 +49588,7 @@
       </c>
       <c r="J621" s="7"/>
     </row>
-    <row r="622" spans="1:10" hidden="1">
+    <row r="622" spans="1:10">
       <c r="A622">
         <v>2031</v>
       </c>
@@ -49631,7 +49620,7 @@
       </c>
       <c r="J622" s="7"/>
     </row>
-    <row r="623" spans="1:10" hidden="1">
+    <row r="623" spans="1:10">
       <c r="A623">
         <v>2032</v>
       </c>
@@ -49663,7 +49652,7 @@
       </c>
       <c r="J623" s="7"/>
     </row>
-    <row r="624" spans="1:10" hidden="1">
+    <row r="624" spans="1:10">
       <c r="A624">
         <v>2033</v>
       </c>
@@ -49695,7 +49684,7 @@
       </c>
       <c r="J624" s="7"/>
     </row>
-    <row r="625" spans="1:10" hidden="1">
+    <row r="625" spans="1:10">
       <c r="A625">
         <v>2034</v>
       </c>
@@ -49727,7 +49716,7 @@
       </c>
       <c r="J625" s="7"/>
     </row>
-    <row r="626" spans="1:10" hidden="1">
+    <row r="626" spans="1:10">
       <c r="A626">
         <v>2035</v>
       </c>
@@ -49759,7 +49748,7 @@
       </c>
       <c r="J626" s="7"/>
     </row>
-    <row r="627" spans="1:10" hidden="1">
+    <row r="627" spans="1:10">
       <c r="A627">
         <v>2036</v>
       </c>
@@ -49791,7 +49780,7 @@
       </c>
       <c r="J627" s="7"/>
     </row>
-    <row r="628" spans="1:10" hidden="1">
+    <row r="628" spans="1:10">
       <c r="A628">
         <v>2037</v>
       </c>
@@ -49823,7 +49812,7 @@
       </c>
       <c r="J628" s="7"/>
     </row>
-    <row r="629" spans="1:10" hidden="1">
+    <row r="629" spans="1:10">
       <c r="A629">
         <v>2038</v>
       </c>
@@ -49855,7 +49844,7 @@
       </c>
       <c r="J629" s="7"/>
     </row>
-    <row r="630" spans="1:10" hidden="1">
+    <row r="630" spans="1:10">
       <c r="A630">
         <v>2039</v>
       </c>
@@ -49887,7 +49876,7 @@
       </c>
       <c r="J630" s="7"/>
     </row>
-    <row r="631" spans="1:10" hidden="1">
+    <row r="631" spans="1:10">
       <c r="A631">
         <v>2040</v>
       </c>
@@ -49919,7 +49908,7 @@
       </c>
       <c r="J631" s="7"/>
     </row>
-    <row r="632" spans="1:10" hidden="1">
+    <row r="632" spans="1:10">
       <c r="A632">
         <v>2030</v>
       </c>
@@ -49951,7 +49940,7 @@
       </c>
       <c r="J632" s="7"/>
     </row>
-    <row r="633" spans="1:10" hidden="1">
+    <row r="633" spans="1:10">
       <c r="A633">
         <v>2031</v>
       </c>
@@ -49983,7 +49972,7 @@
       </c>
       <c r="J633" s="7"/>
     </row>
-    <row r="634" spans="1:10" hidden="1">
+    <row r="634" spans="1:10">
       <c r="A634">
         <v>2032</v>
       </c>
@@ -50015,7 +50004,7 @@
       </c>
       <c r="J634" s="7"/>
     </row>
-    <row r="635" spans="1:10" hidden="1">
+    <row r="635" spans="1:10">
       <c r="A635">
         <v>2033</v>
       </c>
@@ -50047,7 +50036,7 @@
       </c>
       <c r="J635" s="7"/>
     </row>
-    <row r="636" spans="1:10" hidden="1">
+    <row r="636" spans="1:10">
       <c r="A636">
         <v>2034</v>
       </c>
@@ -50079,7 +50068,7 @@
       </c>
       <c r="J636" s="7"/>
     </row>
-    <row r="637" spans="1:10" hidden="1">
+    <row r="637" spans="1:10">
       <c r="A637">
         <v>2035</v>
       </c>
@@ -50111,7 +50100,7 @@
       </c>
       <c r="J637" s="7"/>
     </row>
-    <row r="638" spans="1:10" hidden="1">
+    <row r="638" spans="1:10">
       <c r="A638">
         <v>2036</v>
       </c>
@@ -50143,7 +50132,7 @@
       </c>
       <c r="J638" s="7"/>
     </row>
-    <row r="639" spans="1:10" hidden="1">
+    <row r="639" spans="1:10">
       <c r="A639">
         <v>2037</v>
       </c>
@@ -50175,7 +50164,7 @@
       </c>
       <c r="J639" s="7"/>
     </row>
-    <row r="640" spans="1:10" hidden="1">
+    <row r="640" spans="1:10">
       <c r="A640">
         <v>2038</v>
       </c>
@@ -50207,7 +50196,7 @@
       </c>
       <c r="J640" s="7"/>
     </row>
-    <row r="641" spans="1:10" hidden="1">
+    <row r="641" spans="1:10">
       <c r="A641">
         <v>2039</v>
       </c>
@@ -50239,7 +50228,7 @@
       </c>
       <c r="J641" s="7"/>
     </row>
-    <row r="642" spans="1:10" hidden="1">
+    <row r="642" spans="1:10">
       <c r="A642">
         <v>2040</v>
       </c>
@@ -50271,7 +50260,7 @@
       </c>
       <c r="J642" s="7"/>
     </row>
-    <row r="643" spans="1:10" hidden="1">
+    <row r="643" spans="1:10">
       <c r="A643">
         <v>2030</v>
       </c>
@@ -50303,7 +50292,7 @@
       </c>
       <c r="J643" s="7"/>
     </row>
-    <row r="644" spans="1:10" hidden="1">
+    <row r="644" spans="1:10">
       <c r="A644">
         <v>2031</v>
       </c>
@@ -50335,7 +50324,7 @@
       </c>
       <c r="J644" s="7"/>
     </row>
-    <row r="645" spans="1:10" hidden="1">
+    <row r="645" spans="1:10">
       <c r="A645">
         <v>2032</v>
       </c>
@@ -50367,7 +50356,7 @@
       </c>
       <c r="J645" s="7"/>
     </row>
-    <row r="646" spans="1:10" hidden="1">
+    <row r="646" spans="1:10">
       <c r="A646">
         <v>2033</v>
       </c>
@@ -50399,7 +50388,7 @@
       </c>
       <c r="J646" s="7"/>
     </row>
-    <row r="647" spans="1:10" hidden="1">
+    <row r="647" spans="1:10">
       <c r="A647">
         <v>2034</v>
       </c>
@@ -50431,7 +50420,7 @@
       </c>
       <c r="J647" s="7"/>
     </row>
-    <row r="648" spans="1:10" hidden="1">
+    <row r="648" spans="1:10">
       <c r="A648">
         <v>2035</v>
       </c>
@@ -50463,7 +50452,7 @@
       </c>
       <c r="J648" s="7"/>
     </row>
-    <row r="649" spans="1:10" hidden="1">
+    <row r="649" spans="1:10">
       <c r="A649">
         <v>2036</v>
       </c>
@@ -50495,7 +50484,7 @@
       </c>
       <c r="J649" s="7"/>
     </row>
-    <row r="650" spans="1:10" hidden="1">
+    <row r="650" spans="1:10">
       <c r="A650">
         <v>2037</v>
       </c>
@@ -50527,7 +50516,7 @@
       </c>
       <c r="J650" s="7"/>
     </row>
-    <row r="651" spans="1:10" hidden="1">
+    <row r="651" spans="1:10">
       <c r="A651">
         <v>2038</v>
       </c>
@@ -50559,7 +50548,7 @@
       </c>
       <c r="J651" s="7"/>
     </row>
-    <row r="652" spans="1:10" hidden="1">
+    <row r="652" spans="1:10">
       <c r="A652">
         <v>2039</v>
       </c>
@@ -50591,7 +50580,7 @@
       </c>
       <c r="J652" s="7"/>
     </row>
-    <row r="653" spans="1:10" hidden="1">
+    <row r="653" spans="1:10">
       <c r="A653">
         <v>2040</v>
       </c>
@@ -50623,7 +50612,7 @@
       </c>
       <c r="J653" s="7"/>
     </row>
-    <row r="654" spans="1:10" hidden="1">
+    <row r="654" spans="1:10">
       <c r="A654">
         <v>2030</v>
       </c>
@@ -50655,7 +50644,7 @@
       </c>
       <c r="J654" s="7"/>
     </row>
-    <row r="655" spans="1:10" hidden="1">
+    <row r="655" spans="1:10">
       <c r="A655">
         <v>2031</v>
       </c>
@@ -50687,7 +50676,7 @@
       </c>
       <c r="J655" s="7"/>
     </row>
-    <row r="656" spans="1:10" hidden="1">
+    <row r="656" spans="1:10">
       <c r="A656">
         <v>2032</v>
       </c>
@@ -50719,7 +50708,7 @@
       </c>
       <c r="J656" s="7"/>
     </row>
-    <row r="657" spans="1:10" hidden="1">
+    <row r="657" spans="1:10">
       <c r="A657">
         <v>2033</v>
       </c>
@@ -50751,7 +50740,7 @@
       </c>
       <c r="J657" s="7"/>
     </row>
-    <row r="658" spans="1:10" hidden="1">
+    <row r="658" spans="1:10">
       <c r="A658">
         <v>2034</v>
       </c>
@@ -50783,7 +50772,7 @@
       </c>
       <c r="J658" s="7"/>
     </row>
-    <row r="659" spans="1:10" hidden="1">
+    <row r="659" spans="1:10">
       <c r="A659">
         <v>2035</v>
       </c>
@@ -50815,7 +50804,7 @@
       </c>
       <c r="J659" s="7"/>
     </row>
-    <row r="660" spans="1:10" hidden="1">
+    <row r="660" spans="1:10">
       <c r="A660">
         <v>2036</v>
       </c>
@@ -50847,7 +50836,7 @@
       </c>
       <c r="J660" s="7"/>
     </row>
-    <row r="661" spans="1:10" hidden="1">
+    <row r="661" spans="1:10">
       <c r="A661">
         <v>2037</v>
       </c>
@@ -50879,7 +50868,7 @@
       </c>
       <c r="J661" s="7"/>
     </row>
-    <row r="662" spans="1:10" hidden="1">
+    <row r="662" spans="1:10">
       <c r="A662">
         <v>2038</v>
       </c>
@@ -50911,7 +50900,7 @@
       </c>
       <c r="J662" s="7"/>
     </row>
-    <row r="663" spans="1:10" hidden="1">
+    <row r="663" spans="1:10">
       <c r="A663">
         <v>2039</v>
       </c>
@@ -50943,7 +50932,7 @@
       </c>
       <c r="J663" s="7"/>
     </row>
-    <row r="664" spans="1:10" hidden="1">
+    <row r="664" spans="1:10">
       <c r="A664">
         <v>2040</v>
       </c>
@@ -50975,7 +50964,7 @@
       </c>
       <c r="J664" s="7"/>
     </row>
-    <row r="665" spans="1:10" hidden="1">
+    <row r="665" spans="1:10">
       <c r="A665">
         <v>2030</v>
       </c>
@@ -51007,7 +50996,7 @@
       </c>
       <c r="J665" s="7"/>
     </row>
-    <row r="666" spans="1:10" hidden="1">
+    <row r="666" spans="1:10">
       <c r="A666">
         <v>2031</v>
       </c>
@@ -51039,7 +51028,7 @@
       </c>
       <c r="J666" s="7"/>
     </row>
-    <row r="667" spans="1:10" hidden="1">
+    <row r="667" spans="1:10">
       <c r="A667">
         <v>2032</v>
       </c>
@@ -51071,7 +51060,7 @@
       </c>
       <c r="J667" s="7"/>
     </row>
-    <row r="668" spans="1:10" hidden="1">
+    <row r="668" spans="1:10">
       <c r="A668">
         <v>2033</v>
       </c>
@@ -51103,7 +51092,7 @@
       </c>
       <c r="J668" s="7"/>
     </row>
-    <row r="669" spans="1:10" hidden="1">
+    <row r="669" spans="1:10">
       <c r="A669">
         <v>2034</v>
       </c>
@@ -51135,7 +51124,7 @@
       </c>
       <c r="J669" s="7"/>
     </row>
-    <row r="670" spans="1:10" hidden="1">
+    <row r="670" spans="1:10">
       <c r="A670">
         <v>2035</v>
       </c>
@@ -51167,7 +51156,7 @@
       </c>
       <c r="J670" s="7"/>
     </row>
-    <row r="671" spans="1:10" hidden="1">
+    <row r="671" spans="1:10">
       <c r="A671">
         <v>2036</v>
       </c>
@@ -51199,7 +51188,7 @@
       </c>
       <c r="J671" s="7"/>
     </row>
-    <row r="672" spans="1:10" hidden="1">
+    <row r="672" spans="1:10">
       <c r="A672">
         <v>2037</v>
       </c>
@@ -51231,7 +51220,7 @@
       </c>
       <c r="J672" s="7"/>
     </row>
-    <row r="673" spans="1:10" hidden="1">
+    <row r="673" spans="1:10">
       <c r="A673">
         <v>2038</v>
       </c>
@@ -51263,7 +51252,7 @@
       </c>
       <c r="J673" s="7"/>
     </row>
-    <row r="674" spans="1:10" hidden="1">
+    <row r="674" spans="1:10">
       <c r="A674">
         <v>2039</v>
       </c>
@@ -51295,7 +51284,7 @@
       </c>
       <c r="J674" s="7"/>
     </row>
-    <row r="675" spans="1:10" hidden="1">
+    <row r="675" spans="1:10">
       <c r="A675">
         <v>2040</v>
       </c>
@@ -51327,7 +51316,7 @@
       </c>
       <c r="J675" s="7"/>
     </row>
-    <row r="676" spans="1:10" hidden="1">
+    <row r="676" spans="1:10">
       <c r="A676">
         <v>2030</v>
       </c>
@@ -51359,7 +51348,7 @@
       </c>
       <c r="J676" s="7"/>
     </row>
-    <row r="677" spans="1:10" hidden="1">
+    <row r="677" spans="1:10">
       <c r="A677">
         <v>2031</v>
       </c>
@@ -51391,7 +51380,7 @@
       </c>
       <c r="J677" s="7"/>
     </row>
-    <row r="678" spans="1:10" hidden="1">
+    <row r="678" spans="1:10">
       <c r="A678">
         <v>2032</v>
       </c>
@@ -51423,7 +51412,7 @@
       </c>
       <c r="J678" s="7"/>
     </row>
-    <row r="679" spans="1:10" hidden="1">
+    <row r="679" spans="1:10">
       <c r="A679">
         <v>2033</v>
       </c>
@@ -51455,7 +51444,7 @@
       </c>
       <c r="J679" s="7"/>
     </row>
-    <row r="680" spans="1:10" hidden="1">
+    <row r="680" spans="1:10">
       <c r="A680">
         <v>2034</v>
       </c>
@@ -51487,7 +51476,7 @@
       </c>
       <c r="J680" s="7"/>
     </row>
-    <row r="681" spans="1:10" hidden="1">
+    <row r="681" spans="1:10">
       <c r="A681">
         <v>2035</v>
       </c>
@@ -51519,7 +51508,7 @@
       </c>
       <c r="J681" s="7"/>
     </row>
-    <row r="682" spans="1:10" hidden="1">
+    <row r="682" spans="1:10">
       <c r="A682">
         <v>2036</v>
       </c>
@@ -51551,7 +51540,7 @@
       </c>
       <c r="J682" s="7"/>
     </row>
-    <row r="683" spans="1:10" hidden="1">
+    <row r="683" spans="1:10">
       <c r="A683">
         <v>2037</v>
       </c>
@@ -51583,7 +51572,7 @@
       </c>
       <c r="J683" s="7"/>
     </row>
-    <row r="684" spans="1:10" hidden="1">
+    <row r="684" spans="1:10">
       <c r="A684">
         <v>2038</v>
       </c>
@@ -51615,7 +51604,7 @@
       </c>
       <c r="J684" s="7"/>
     </row>
-    <row r="685" spans="1:10" hidden="1">
+    <row r="685" spans="1:10">
       <c r="A685">
         <v>2039</v>
       </c>
@@ -51647,7 +51636,7 @@
       </c>
       <c r="J685" s="7"/>
     </row>
-    <row r="686" spans="1:10" hidden="1">
+    <row r="686" spans="1:10">
       <c r="A686">
         <v>2040</v>
       </c>
@@ -51679,7 +51668,7 @@
       </c>
       <c r="J686" s="7"/>
     </row>
-    <row r="687" spans="1:10" hidden="1">
+    <row r="687" spans="1:10">
       <c r="A687">
         <v>2030</v>
       </c>
@@ -51711,7 +51700,7 @@
       </c>
       <c r="J687" s="7"/>
     </row>
-    <row r="688" spans="1:10" hidden="1">
+    <row r="688" spans="1:10">
       <c r="A688">
         <v>2031</v>
       </c>
@@ -51743,7 +51732,7 @@
       </c>
       <c r="J688" s="7"/>
     </row>
-    <row r="689" spans="1:10" hidden="1">
+    <row r="689" spans="1:10">
       <c r="A689">
         <v>2032</v>
       </c>
@@ -51775,7 +51764,7 @@
       </c>
       <c r="J689" s="7"/>
     </row>
-    <row r="690" spans="1:10" hidden="1">
+    <row r="690" spans="1:10">
       <c r="A690">
         <v>2033</v>
       </c>
@@ -51807,7 +51796,7 @@
       </c>
       <c r="J690" s="7"/>
     </row>
-    <row r="691" spans="1:10" hidden="1">
+    <row r="691" spans="1:10">
       <c r="A691">
         <v>2034</v>
       </c>
@@ -51839,7 +51828,7 @@
       </c>
       <c r="J691" s="7"/>
     </row>
-    <row r="692" spans="1:10" hidden="1">
+    <row r="692" spans="1:10">
       <c r="A692">
         <v>2035</v>
       </c>
@@ -51871,7 +51860,7 @@
       </c>
       <c r="J692" s="7"/>
     </row>
-    <row r="693" spans="1:10" hidden="1">
+    <row r="693" spans="1:10">
       <c r="A693">
         <v>2036</v>
       </c>
@@ -51903,7 +51892,7 @@
       </c>
       <c r="J693" s="7"/>
     </row>
-    <row r="694" spans="1:10" hidden="1">
+    <row r="694" spans="1:10">
       <c r="A694">
         <v>2037</v>
       </c>
@@ -51935,7 +51924,7 @@
       </c>
       <c r="J694" s="7"/>
     </row>
-    <row r="695" spans="1:10" hidden="1">
+    <row r="695" spans="1:10">
       <c r="A695">
         <v>2038</v>
       </c>
@@ -51967,7 +51956,7 @@
       </c>
       <c r="J695" s="7"/>
     </row>
-    <row r="696" spans="1:10" hidden="1">
+    <row r="696" spans="1:10">
       <c r="A696">
         <v>2039</v>
       </c>
@@ -51999,7 +51988,7 @@
       </c>
       <c r="J696" s="7"/>
     </row>
-    <row r="697" spans="1:10" hidden="1">
+    <row r="697" spans="1:10">
       <c r="A697">
         <v>2040</v>
       </c>
@@ -52031,7 +52020,7 @@
       </c>
       <c r="J697" s="7"/>
     </row>
-    <row r="698" spans="1:10" hidden="1">
+    <row r="698" spans="1:10">
       <c r="A698">
         <v>2030</v>
       </c>
@@ -52059,7 +52048,7 @@
       </c>
       <c r="J698" s="7"/>
     </row>
-    <row r="699" spans="1:10" hidden="1">
+    <row r="699" spans="1:10">
       <c r="A699">
         <v>2031</v>
       </c>
@@ -52087,7 +52076,7 @@
       </c>
       <c r="J699" s="7"/>
     </row>
-    <row r="700" spans="1:10" hidden="1">
+    <row r="700" spans="1:10">
       <c r="A700">
         <v>2032</v>
       </c>
@@ -52115,7 +52104,7 @@
       </c>
       <c r="J700" s="7"/>
     </row>
-    <row r="701" spans="1:10" hidden="1">
+    <row r="701" spans="1:10">
       <c r="A701">
         <v>2033</v>
       </c>
@@ -52143,7 +52132,7 @@
       </c>
       <c r="J701" s="7"/>
     </row>
-    <row r="702" spans="1:10" hidden="1">
+    <row r="702" spans="1:10">
       <c r="A702">
         <v>2034</v>
       </c>
@@ -52171,7 +52160,7 @@
       </c>
       <c r="J702" s="7"/>
     </row>
-    <row r="703" spans="1:10" hidden="1">
+    <row r="703" spans="1:10">
       <c r="A703">
         <v>2035</v>
       </c>
@@ -52199,7 +52188,7 @@
       </c>
       <c r="J703" s="7"/>
     </row>
-    <row r="704" spans="1:10" hidden="1">
+    <row r="704" spans="1:10">
       <c r="A704">
         <v>2036</v>
       </c>
@@ -52227,7 +52216,7 @@
       </c>
       <c r="J704" s="7"/>
     </row>
-    <row r="705" spans="1:10" hidden="1">
+    <row r="705" spans="1:10">
       <c r="A705">
         <v>2037</v>
       </c>
@@ -52255,7 +52244,7 @@
       </c>
       <c r="J705" s="7"/>
     </row>
-    <row r="706" spans="1:10" hidden="1">
+    <row r="706" spans="1:10">
       <c r="A706">
         <v>2038</v>
       </c>
@@ -52283,7 +52272,7 @@
       </c>
       <c r="J706" s="7"/>
     </row>
-    <row r="707" spans="1:10" hidden="1">
+    <row r="707" spans="1:10">
       <c r="A707">
         <v>2039</v>
       </c>
@@ -52311,7 +52300,7 @@
       </c>
       <c r="J707" s="7"/>
     </row>
-    <row r="708" spans="1:10" hidden="1">
+    <row r="708" spans="1:10">
       <c r="A708">
         <v>2040</v>
       </c>
@@ -52339,7 +52328,7 @@
       </c>
       <c r="J708" s="7"/>
     </row>
-    <row r="709" spans="1:10" hidden="1">
+    <row r="709" spans="1:10">
       <c r="A709">
         <v>2030</v>
       </c>
@@ -52367,7 +52356,7 @@
       </c>
       <c r="J709" s="7"/>
     </row>
-    <row r="710" spans="1:10" hidden="1">
+    <row r="710" spans="1:10">
       <c r="A710">
         <v>2031</v>
       </c>
@@ -52395,7 +52384,7 @@
       </c>
       <c r="J710" s="7"/>
     </row>
-    <row r="711" spans="1:10" hidden="1">
+    <row r="711" spans="1:10">
       <c r="A711">
         <v>2032</v>
       </c>
@@ -52423,7 +52412,7 @@
       </c>
       <c r="J711" s="7"/>
     </row>
-    <row r="712" spans="1:10" hidden="1">
+    <row r="712" spans="1:10">
       <c r="A712">
         <v>2033</v>
       </c>
@@ -52451,7 +52440,7 @@
       </c>
       <c r="J712" s="7"/>
     </row>
-    <row r="713" spans="1:10" hidden="1">
+    <row r="713" spans="1:10">
       <c r="A713">
         <v>2034</v>
       </c>
@@ -52479,7 +52468,7 @@
       </c>
       <c r="J713" s="7"/>
     </row>
-    <row r="714" spans="1:10" hidden="1">
+    <row r="714" spans="1:10">
       <c r="A714">
         <v>2035</v>
       </c>
@@ -52507,7 +52496,7 @@
       </c>
       <c r="J714" s="7"/>
     </row>
-    <row r="715" spans="1:10" hidden="1">
+    <row r="715" spans="1:10">
       <c r="A715">
         <v>2036</v>
       </c>
@@ -52535,7 +52524,7 @@
       </c>
       <c r="J715" s="7"/>
     </row>
-    <row r="716" spans="1:10" hidden="1">
+    <row r="716" spans="1:10">
       <c r="A716">
         <v>2037</v>
       </c>
@@ -52563,7 +52552,7 @@
       </c>
       <c r="J716" s="7"/>
     </row>
-    <row r="717" spans="1:10" hidden="1">
+    <row r="717" spans="1:10">
       <c r="A717">
         <v>2038</v>
       </c>
@@ -52591,7 +52580,7 @@
       </c>
       <c r="J717" s="7"/>
     </row>
-    <row r="718" spans="1:10" hidden="1">
+    <row r="718" spans="1:10">
       <c r="A718">
         <v>2039</v>
       </c>
@@ -52619,7 +52608,7 @@
       </c>
       <c r="J718" s="7"/>
     </row>
-    <row r="719" spans="1:10" hidden="1">
+    <row r="719" spans="1:10">
       <c r="A719">
         <v>2040</v>
       </c>
@@ -52647,7 +52636,7 @@
       </c>
       <c r="J719" s="7"/>
     </row>
-    <row r="720" spans="1:10" hidden="1">
+    <row r="720" spans="1:10">
       <c r="A720" s="15">
         <v>2026</v>
       </c>
@@ -52675,7 +52664,7 @@
       </c>
       <c r="J720" s="7"/>
     </row>
-    <row r="721" spans="1:10" hidden="1">
+    <row r="721" spans="1:10">
       <c r="A721" s="15">
         <v>2027</v>
       </c>
@@ -52703,7 +52692,7 @@
       </c>
       <c r="J721" s="7"/>
     </row>
-    <row r="722" spans="1:10" hidden="1">
+    <row r="722" spans="1:10">
       <c r="A722" s="15">
         <v>2028</v>
       </c>
@@ -52731,7 +52720,7 @@
       </c>
       <c r="J722" s="7"/>
     </row>
-    <row r="723" spans="1:10" hidden="1">
+    <row r="723" spans="1:10">
       <c r="A723" s="15">
         <v>2029</v>
       </c>
@@ -52759,7 +52748,7 @@
       </c>
       <c r="J723" s="7"/>
     </row>
-    <row r="724" spans="1:10" hidden="1">
+    <row r="724" spans="1:10">
       <c r="A724" s="15">
         <v>2026</v>
       </c>
@@ -52787,7 +52776,7 @@
       </c>
       <c r="J724" s="7"/>
     </row>
-    <row r="725" spans="1:10" hidden="1">
+    <row r="725" spans="1:10">
       <c r="A725" s="15">
         <v>2027</v>
       </c>
@@ -52815,7 +52804,7 @@
       </c>
       <c r="J725" s="7"/>
     </row>
-    <row r="726" spans="1:10" hidden="1">
+    <row r="726" spans="1:10">
       <c r="A726" s="15">
         <v>2028</v>
       </c>
@@ -52843,7 +52832,7 @@
       </c>
       <c r="J726" s="7"/>
     </row>
-    <row r="727" spans="1:10" hidden="1">
+    <row r="727" spans="1:10">
       <c r="A727" s="15">
         <v>2029</v>
       </c>
@@ -52871,7 +52860,7 @@
       </c>
       <c r="J727" s="7"/>
     </row>
-    <row r="728" spans="1:10" hidden="1">
+    <row r="728" spans="1:10">
       <c r="A728" s="15">
         <v>2026</v>
       </c>
@@ -52899,7 +52888,7 @@
       </c>
       <c r="J728" s="7"/>
     </row>
-    <row r="729" spans="1:10" hidden="1">
+    <row r="729" spans="1:10">
       <c r="A729" s="15">
         <v>2027</v>
       </c>
@@ -52927,7 +52916,7 @@
       </c>
       <c r="J729" s="7"/>
     </row>
-    <row r="730" spans="1:10" hidden="1">
+    <row r="730" spans="1:10">
       <c r="A730" s="15">
         <v>2028</v>
       </c>
@@ -52955,7 +52944,7 @@
       </c>
       <c r="J730" s="7"/>
     </row>
-    <row r="731" spans="1:10" hidden="1">
+    <row r="731" spans="1:10">
       <c r="A731" s="15">
         <v>2029</v>
       </c>
@@ -52983,7 +52972,7 @@
       </c>
       <c r="J731" s="7"/>
     </row>
-    <row r="732" spans="1:10" hidden="1">
+    <row r="732" spans="1:10">
       <c r="A732" s="15">
         <v>2026</v>
       </c>
@@ -53011,7 +53000,7 @@
       </c>
       <c r="J732" s="7"/>
     </row>
-    <row r="733" spans="1:10" hidden="1">
+    <row r="733" spans="1:10">
       <c r="A733" s="15">
         <v>2027</v>
       </c>
@@ -53039,7 +53028,7 @@
       </c>
       <c r="J733" s="7"/>
     </row>
-    <row r="734" spans="1:10" hidden="1">
+    <row r="734" spans="1:10">
       <c r="A734" s="15">
         <v>2028</v>
       </c>
@@ -53067,7 +53056,7 @@
       </c>
       <c r="J734" s="7"/>
     </row>
-    <row r="735" spans="1:10" hidden="1">
+    <row r="735" spans="1:10">
       <c r="A735" s="15">
         <v>2029</v>
       </c>
@@ -53095,7 +53084,7 @@
       </c>
       <c r="J735" s="7"/>
     </row>
-    <row r="736" spans="1:10" hidden="1">
+    <row r="736" spans="1:10">
       <c r="A736" s="15">
         <v>2026</v>
       </c>
@@ -53123,7 +53112,7 @@
       </c>
       <c r="J736" s="7"/>
     </row>
-    <row r="737" spans="1:10" hidden="1">
+    <row r="737" spans="1:10">
       <c r="A737" s="15">
         <v>2027</v>
       </c>
@@ -53151,7 +53140,7 @@
       </c>
       <c r="J737" s="7"/>
     </row>
-    <row r="738" spans="1:10" hidden="1">
+    <row r="738" spans="1:10">
       <c r="A738" s="15">
         <v>2028</v>
       </c>
@@ -53179,7 +53168,7 @@
       </c>
       <c r="J738" s="7"/>
     </row>
-    <row r="739" spans="1:10" hidden="1">
+    <row r="739" spans="1:10">
       <c r="A739" s="15">
         <v>2029</v>
       </c>
@@ -53207,7 +53196,7 @@
       </c>
       <c r="J739" s="7"/>
     </row>
-    <row r="740" spans="1:10" hidden="1">
+    <row r="740" spans="1:10">
       <c r="A740" s="15">
         <v>2026</v>
       </c>
@@ -53235,7 +53224,7 @@
       </c>
       <c r="J740" s="7"/>
     </row>
-    <row r="741" spans="1:10" hidden="1">
+    <row r="741" spans="1:10">
       <c r="A741" s="15">
         <v>2027</v>
       </c>
@@ -53263,7 +53252,7 @@
       </c>
       <c r="J741" s="7"/>
     </row>
-    <row r="742" spans="1:10" hidden="1">
+    <row r="742" spans="1:10">
       <c r="A742" s="15">
         <v>2028</v>
       </c>
@@ -53291,7 +53280,7 @@
       </c>
       <c r="J742" s="7"/>
     </row>
-    <row r="743" spans="1:10" hidden="1">
+    <row r="743" spans="1:10">
       <c r="A743" s="15">
         <v>2029</v>
       </c>
@@ -53319,7 +53308,7 @@
       </c>
       <c r="J743" s="7"/>
     </row>
-    <row r="744" spans="1:10" hidden="1">
+    <row r="744" spans="1:10">
       <c r="A744" s="15">
         <v>2026</v>
       </c>
@@ -53347,7 +53336,7 @@
       </c>
       <c r="J744" s="7"/>
     </row>
-    <row r="745" spans="1:10" hidden="1">
+    <row r="745" spans="1:10">
       <c r="A745" s="15">
         <v>2027</v>
       </c>
@@ -53375,7 +53364,7 @@
       </c>
       <c r="J745" s="7"/>
     </row>
-    <row r="746" spans="1:10" hidden="1">
+    <row r="746" spans="1:10">
       <c r="A746" s="15">
         <v>2028</v>
       </c>
@@ -53403,7 +53392,7 @@
       </c>
       <c r="J746" s="7"/>
     </row>
-    <row r="747" spans="1:10" hidden="1">
+    <row r="747" spans="1:10">
       <c r="A747" s="15">
         <v>2029</v>
       </c>
@@ -53431,7 +53420,7 @@
       </c>
       <c r="J747" s="7"/>
     </row>
-    <row r="748" spans="1:10" hidden="1">
+    <row r="748" spans="1:10">
       <c r="A748" s="15">
         <v>2026</v>
       </c>
@@ -53459,7 +53448,7 @@
       </c>
       <c r="J748" s="7"/>
     </row>
-    <row r="749" spans="1:10" hidden="1">
+    <row r="749" spans="1:10">
       <c r="A749" s="15">
         <v>2027</v>
       </c>
@@ -53487,7 +53476,7 @@
       </c>
       <c r="J749" s="7"/>
     </row>
-    <row r="750" spans="1:10" hidden="1">
+    <row r="750" spans="1:10">
       <c r="A750" s="16">
         <v>2028</v>
       </c>
@@ -53515,7 +53504,7 @@
       </c>
       <c r="J750" s="7"/>
     </row>
-    <row r="751" spans="1:10" hidden="1">
+    <row r="751" spans="1:10">
       <c r="A751" s="16">
         <v>2029</v>
       </c>
@@ -53543,7 +53532,7 @@
       </c>
       <c r="J751" s="7"/>
     </row>
-    <row r="752" spans="1:10" hidden="1">
+    <row r="752" spans="1:10">
       <c r="A752" s="16">
         <v>2026</v>
       </c>
@@ -53571,7 +53560,7 @@
       </c>
       <c r="J752" s="7"/>
     </row>
-    <row r="753" spans="1:10" hidden="1">
+    <row r="753" spans="1:10">
       <c r="A753" s="16">
         <v>2027</v>
       </c>
@@ -53599,7 +53588,7 @@
       </c>
       <c r="J753" s="7"/>
     </row>
-    <row r="754" spans="1:10" hidden="1">
+    <row r="754" spans="1:10">
       <c r="A754" s="16">
         <v>2028</v>
       </c>
@@ -53627,7 +53616,7 @@
       </c>
       <c r="J754" s="7"/>
     </row>
-    <row r="755" spans="1:10" hidden="1">
+    <row r="755" spans="1:10">
       <c r="A755" s="16">
         <v>2029</v>
       </c>
@@ -53655,7 +53644,7 @@
       </c>
       <c r="J755" s="7"/>
     </row>
-    <row r="756" spans="1:10" hidden="1">
+    <row r="756" spans="1:10">
       <c r="A756" s="16">
         <v>2026</v>
       </c>
@@ -53683,7 +53672,7 @@
       </c>
       <c r="J756" s="7"/>
     </row>
-    <row r="757" spans="1:10" hidden="1">
+    <row r="757" spans="1:10">
       <c r="A757" s="16">
         <v>2027</v>
       </c>
@@ -53711,7 +53700,7 @@
       </c>
       <c r="J757" s="7"/>
     </row>
-    <row r="758" spans="1:10" hidden="1">
+    <row r="758" spans="1:10">
       <c r="A758" s="16">
         <v>2028</v>
       </c>
@@ -53739,7 +53728,7 @@
       </c>
       <c r="J758" s="7"/>
     </row>
-    <row r="759" spans="1:10" hidden="1">
+    <row r="759" spans="1:10">
       <c r="A759" s="16">
         <v>2029</v>
       </c>
@@ -53767,7 +53756,7 @@
       </c>
       <c r="J759" s="7"/>
     </row>
-    <row r="760" spans="1:10" hidden="1">
+    <row r="760" spans="1:10">
       <c r="A760" s="16">
         <v>2026</v>
       </c>
@@ -53795,7 +53784,7 @@
       </c>
       <c r="J760" s="7"/>
     </row>
-    <row r="761" spans="1:10" hidden="1">
+    <row r="761" spans="1:10">
       <c r="A761" s="16">
         <v>2027</v>
       </c>
@@ -53823,7 +53812,7 @@
       </c>
       <c r="J761" s="7"/>
     </row>
-    <row r="762" spans="1:10" hidden="1">
+    <row r="762" spans="1:10">
       <c r="A762" s="16">
         <v>2028</v>
       </c>
@@ -53851,7 +53840,7 @@
       </c>
       <c r="J762" s="7"/>
     </row>
-    <row r="763" spans="1:10" hidden="1">
+    <row r="763" spans="1:10">
       <c r="A763" s="16">
         <v>2029</v>
       </c>
@@ -53879,7 +53868,7 @@
       </c>
       <c r="J763" s="7"/>
     </row>
-    <row r="764" spans="1:10" hidden="1">
+    <row r="764" spans="1:10">
       <c r="A764" s="16">
         <v>2026</v>
       </c>
@@ -53907,7 +53896,7 @@
       </c>
       <c r="J764" s="7"/>
     </row>
-    <row r="765" spans="1:10" hidden="1">
+    <row r="765" spans="1:10">
       <c r="A765" s="16">
         <v>2027</v>
       </c>
@@ -53935,7 +53924,7 @@
       </c>
       <c r="J765" s="7"/>
     </row>
-    <row r="766" spans="1:10" hidden="1">
+    <row r="766" spans="1:10">
       <c r="A766" s="16">
         <v>2028</v>
       </c>
@@ -53963,7 +53952,7 @@
       </c>
       <c r="J766" s="7"/>
     </row>
-    <row r="767" spans="1:10" hidden="1">
+    <row r="767" spans="1:10">
       <c r="A767" s="16">
         <v>2029</v>
       </c>
@@ -53991,7 +53980,7 @@
       </c>
       <c r="J767" s="7"/>
     </row>
-    <row r="768" spans="1:10" hidden="1">
+    <row r="768" spans="1:10">
       <c r="A768" s="16">
         <v>2026</v>
       </c>
@@ -54019,7 +54008,7 @@
       </c>
       <c r="J768" s="7"/>
     </row>
-    <row r="769" spans="1:10" hidden="1">
+    <row r="769" spans="1:10">
       <c r="A769" s="16">
         <v>2027</v>
       </c>
@@ -54047,7 +54036,7 @@
       </c>
       <c r="J769" s="7"/>
     </row>
-    <row r="770" spans="1:10" hidden="1">
+    <row r="770" spans="1:10">
       <c r="A770" s="16">
         <v>2028</v>
       </c>
@@ -54075,7 +54064,7 @@
       </c>
       <c r="J770" s="7"/>
     </row>
-    <row r="771" spans="1:10" hidden="1">
+    <row r="771" spans="1:10">
       <c r="A771" s="16">
         <v>2029</v>
       </c>
@@ -54103,7 +54092,7 @@
       </c>
       <c r="J771" s="7"/>
     </row>
-    <row r="772" spans="1:10" hidden="1">
+    <row r="772" spans="1:10">
       <c r="A772" s="16">
         <v>2026</v>
       </c>
@@ -54131,7 +54120,7 @@
       </c>
       <c r="J772" s="7"/>
     </row>
-    <row r="773" spans="1:10" hidden="1">
+    <row r="773" spans="1:10">
       <c r="A773" s="16">
         <v>2027</v>
       </c>
@@ -54159,7 +54148,7 @@
       </c>
       <c r="J773" s="7"/>
     </row>
-    <row r="774" spans="1:10" hidden="1">
+    <row r="774" spans="1:10">
       <c r="A774" s="16">
         <v>2028</v>
       </c>
@@ -54187,7 +54176,7 @@
       </c>
       <c r="J774" s="7"/>
     </row>
-    <row r="775" spans="1:10" hidden="1">
+    <row r="775" spans="1:10">
       <c r="A775" s="16">
         <v>2029</v>
       </c>
@@ -54215,7 +54204,7 @@
       </c>
       <c r="J775" s="7"/>
     </row>
-    <row r="776" spans="1:10" hidden="1">
+    <row r="776" spans="1:10">
       <c r="A776" s="16">
         <v>2026</v>
       </c>
@@ -54243,7 +54232,7 @@
       </c>
       <c r="J776" s="7"/>
     </row>
-    <row r="777" spans="1:10" hidden="1">
+    <row r="777" spans="1:10">
       <c r="A777" s="16">
         <v>2027</v>
       </c>
@@ -54271,7 +54260,7 @@
       </c>
       <c r="J777" s="7"/>
     </row>
-    <row r="778" spans="1:10" hidden="1">
+    <row r="778" spans="1:10">
       <c r="A778" s="16">
         <v>2028</v>
       </c>
@@ -54299,7 +54288,7 @@
       </c>
       <c r="J778" s="7"/>
     </row>
-    <row r="779" spans="1:10" hidden="1">
+    <row r="779" spans="1:10">
       <c r="A779" s="16">
         <v>2029</v>
       </c>
@@ -54327,7 +54316,7 @@
       </c>
       <c r="J779" s="7"/>
     </row>
-    <row r="780" spans="1:10" hidden="1">
+    <row r="780" spans="1:10">
       <c r="A780" s="16">
         <v>2026</v>
       </c>
@@ -54355,7 +54344,7 @@
       </c>
       <c r="J780" s="7"/>
     </row>
-    <row r="781" spans="1:10" hidden="1">
+    <row r="781" spans="1:10">
       <c r="A781" s="16">
         <v>2027</v>
       </c>
@@ -54383,7 +54372,7 @@
       </c>
       <c r="J781" s="7"/>
     </row>
-    <row r="782" spans="1:10" hidden="1">
+    <row r="782" spans="1:10">
       <c r="A782" s="16">
         <v>2028</v>
       </c>
@@ -54411,7 +54400,7 @@
       </c>
       <c r="J782" s="7"/>
     </row>
-    <row r="783" spans="1:10" hidden="1">
+    <row r="783" spans="1:10">
       <c r="A783" s="16">
         <v>2029</v>
       </c>
@@ -54439,7 +54428,7 @@
       </c>
       <c r="J783" s="7"/>
     </row>
-    <row r="784" spans="1:10" hidden="1">
+    <row r="784" spans="1:10">
       <c r="A784" s="16">
         <v>2026</v>
       </c>
@@ -54467,7 +54456,7 @@
       </c>
       <c r="J784" s="7"/>
     </row>
-    <row r="785" spans="1:10" hidden="1">
+    <row r="785" spans="1:10">
       <c r="A785" s="16">
         <v>2027</v>
       </c>
@@ -54495,7 +54484,7 @@
       </c>
       <c r="J785" s="7"/>
     </row>
-    <row r="786" spans="1:10" hidden="1">
+    <row r="786" spans="1:10">
       <c r="A786" s="16">
         <v>2028</v>
       </c>
@@ -54523,7 +54512,7 @@
       </c>
       <c r="J786" s="7"/>
     </row>
-    <row r="787" spans="1:10" hidden="1">
+    <row r="787" spans="1:10">
       <c r="A787" s="16">
         <v>2029</v>
       </c>
@@ -54551,7 +54540,7 @@
       </c>
       <c r="J787" s="7"/>
     </row>
-    <row r="788" spans="1:10" hidden="1">
+    <row r="788" spans="1:10">
       <c r="A788" s="16">
         <v>2026</v>
       </c>
@@ -54579,7 +54568,7 @@
       </c>
       <c r="J788" s="7"/>
     </row>
-    <row r="789" spans="1:10" hidden="1">
+    <row r="789" spans="1:10">
       <c r="A789" s="16">
         <v>2027</v>
       </c>
@@ -54607,7 +54596,7 @@
       </c>
       <c r="J789" s="7"/>
     </row>
-    <row r="790" spans="1:10" hidden="1">
+    <row r="790" spans="1:10">
       <c r="A790" s="16">
         <v>2028</v>
       </c>
@@ -54635,7 +54624,7 @@
       </c>
       <c r="J790" s="7"/>
     </row>
-    <row r="791" spans="1:10" hidden="1">
+    <row r="791" spans="1:10">
       <c r="A791" s="16">
         <v>2029</v>
       </c>
@@ -54663,7 +54652,7 @@
       </c>
       <c r="J791" s="7"/>
     </row>
-    <row r="792" spans="1:10" hidden="1">
+    <row r="792" spans="1:10">
       <c r="A792" s="16">
         <v>2026</v>
       </c>
@@ -54691,7 +54680,7 @@
       </c>
       <c r="J792" s="7"/>
     </row>
-    <row r="793" spans="1:10" hidden="1">
+    <row r="793" spans="1:10">
       <c r="A793" s="16">
         <v>2027</v>
       </c>
@@ -54719,7 +54708,7 @@
       </c>
       <c r="J793" s="7"/>
     </row>
-    <row r="794" spans="1:10" hidden="1">
+    <row r="794" spans="1:10">
       <c r="A794" s="16">
         <v>2028</v>
       </c>
@@ -54747,7 +54736,7 @@
       </c>
       <c r="J794" s="7"/>
     </row>
-    <row r="795" spans="1:10" hidden="1">
+    <row r="795" spans="1:10">
       <c r="A795" s="16">
         <v>2029</v>
       </c>
@@ -54775,7 +54764,7 @@
       </c>
       <c r="J795" s="7"/>
     </row>
-    <row r="796" spans="1:10" hidden="1">
+    <row r="796" spans="1:10">
       <c r="A796" s="16">
         <v>2026</v>
       </c>
@@ -54803,7 +54792,7 @@
       </c>
       <c r="J796" s="7"/>
     </row>
-    <row r="797" spans="1:10" hidden="1">
+    <row r="797" spans="1:10">
       <c r="A797" s="16">
         <v>2027</v>
       </c>
@@ -54831,7 +54820,7 @@
       </c>
       <c r="J797" s="7"/>
     </row>
-    <row r="798" spans="1:10" hidden="1">
+    <row r="798" spans="1:10">
       <c r="A798" s="16">
         <v>2028</v>
       </c>
@@ -54859,7 +54848,7 @@
       </c>
       <c r="J798" s="7"/>
     </row>
-    <row r="799" spans="1:10" hidden="1">
+    <row r="799" spans="1:10">
       <c r="A799" s="16">
         <v>2029</v>
       </c>
@@ -54887,7 +54876,7 @@
       </c>
       <c r="J799" s="7"/>
     </row>
-    <row r="800" spans="1:10" hidden="1">
+    <row r="800" spans="1:10">
       <c r="A800" s="16">
         <v>2026</v>
       </c>
@@ -54915,7 +54904,7 @@
       </c>
       <c r="J800" s="7"/>
     </row>
-    <row r="801" spans="1:10" hidden="1">
+    <row r="801" spans="1:10">
       <c r="A801" s="16">
         <v>2027</v>
       </c>
@@ -54943,7 +54932,7 @@
       </c>
       <c r="J801" s="7"/>
     </row>
-    <row r="802" spans="1:10" hidden="1">
+    <row r="802" spans="1:10">
       <c r="A802" s="16">
         <v>2028</v>
       </c>
@@ -54971,7 +54960,7 @@
       </c>
       <c r="J802" s="7"/>
     </row>
-    <row r="803" spans="1:10" hidden="1">
+    <row r="803" spans="1:10">
       <c r="A803" s="16">
         <v>2029</v>
       </c>
@@ -54999,7 +54988,7 @@
       </c>
       <c r="J803" s="7"/>
     </row>
-    <row r="804" spans="1:10" hidden="1">
+    <row r="804" spans="1:10">
       <c r="A804" s="16">
         <v>2026</v>
       </c>
@@ -55027,7 +55016,7 @@
       </c>
       <c r="J804" s="7"/>
     </row>
-    <row r="805" spans="1:10" hidden="1">
+    <row r="805" spans="1:10">
       <c r="A805" s="16">
         <v>2027</v>
       </c>
@@ -55055,7 +55044,7 @@
       </c>
       <c r="J805" s="7"/>
     </row>
-    <row r="806" spans="1:10" hidden="1">
+    <row r="806" spans="1:10">
       <c r="A806" s="16">
         <v>2028</v>
       </c>
@@ -55083,7 +55072,7 @@
       </c>
       <c r="J806" s="7"/>
     </row>
-    <row r="807" spans="1:10" hidden="1">
+    <row r="807" spans="1:10">
       <c r="A807" s="16">
         <v>2029</v>
       </c>
@@ -55111,7 +55100,7 @@
       </c>
       <c r="J807" s="7"/>
     </row>
-    <row r="808" spans="1:10" hidden="1">
+    <row r="808" spans="1:10">
       <c r="A808" s="16">
         <v>2026</v>
       </c>
@@ -55139,7 +55128,7 @@
       </c>
       <c r="J808" s="7"/>
     </row>
-    <row r="809" spans="1:10" hidden="1">
+    <row r="809" spans="1:10">
       <c r="A809" s="16">
         <v>2027</v>
       </c>
@@ -55167,7 +55156,7 @@
       </c>
       <c r="J809" s="7"/>
     </row>
-    <row r="810" spans="1:10" hidden="1">
+    <row r="810" spans="1:10">
       <c r="A810" s="16">
         <v>2028</v>
       </c>
@@ -55195,7 +55184,7 @@
       </c>
       <c r="J810" s="7"/>
     </row>
-    <row r="811" spans="1:10" hidden="1">
+    <row r="811" spans="1:10">
       <c r="A811" s="16">
         <v>2029</v>
       </c>
@@ -55223,7 +55212,7 @@
       </c>
       <c r="J811" s="7"/>
     </row>
-    <row r="812" spans="1:10" hidden="1">
+    <row r="812" spans="1:10">
       <c r="A812" s="16">
         <v>2026</v>
       </c>
@@ -55251,7 +55240,7 @@
       </c>
       <c r="J812" s="7"/>
     </row>
-    <row r="813" spans="1:10" hidden="1">
+    <row r="813" spans="1:10">
       <c r="A813" s="16">
         <v>2027</v>
       </c>
@@ -55279,7 +55268,7 @@
       </c>
       <c r="J813" s="7"/>
     </row>
-    <row r="814" spans="1:10" hidden="1">
+    <row r="814" spans="1:10">
       <c r="A814" s="16">
         <v>2028</v>
       </c>
@@ -55307,7 +55296,7 @@
       </c>
       <c r="J814" s="7"/>
     </row>
-    <row r="815" spans="1:10" hidden="1">
+    <row r="815" spans="1:10">
       <c r="A815" s="16">
         <v>2029</v>
       </c>
@@ -55335,7 +55324,7 @@
       </c>
       <c r="J815" s="7"/>
     </row>
-    <row r="816" spans="1:10" hidden="1">
+    <row r="816" spans="1:10">
       <c r="A816" s="16">
         <v>2026</v>
       </c>
@@ -55363,7 +55352,7 @@
       </c>
       <c r="J816" s="7"/>
     </row>
-    <row r="817" spans="1:10" hidden="1">
+    <row r="817" spans="1:10">
       <c r="A817" s="16">
         <v>2027</v>
       </c>
@@ -55391,7 +55380,7 @@
       </c>
       <c r="J817" s="7"/>
     </row>
-    <row r="818" spans="1:10" hidden="1">
+    <row r="818" spans="1:10">
       <c r="A818" s="16">
         <v>2028</v>
       </c>
@@ -55419,7 +55408,7 @@
       </c>
       <c r="J818" s="7"/>
     </row>
-    <row r="819" spans="1:10" hidden="1">
+    <row r="819" spans="1:10">
       <c r="A819" s="16">
         <v>2029</v>
       </c>
@@ -55447,7 +55436,7 @@
       </c>
       <c r="J819" s="7"/>
     </row>
-    <row r="820" spans="1:10" hidden="1">
+    <row r="820" spans="1:10">
       <c r="A820" s="16">
         <v>2026</v>
       </c>
@@ -55475,7 +55464,7 @@
       </c>
       <c r="J820" s="7"/>
     </row>
-    <row r="821" spans="1:10" hidden="1">
+    <row r="821" spans="1:10">
       <c r="A821" s="16">
         <v>2027</v>
       </c>
@@ -55503,7 +55492,7 @@
       </c>
       <c r="J821" s="7"/>
     </row>
-    <row r="822" spans="1:10" hidden="1">
+    <row r="822" spans="1:10">
       <c r="A822" s="16">
         <v>2028</v>
       </c>
@@ -55531,7 +55520,7 @@
       </c>
       <c r="J822" s="7"/>
     </row>
-    <row r="823" spans="1:10" hidden="1">
+    <row r="823" spans="1:10">
       <c r="A823" s="16">
         <v>2029</v>
       </c>
@@ -55559,7 +55548,7 @@
       </c>
       <c r="J823" s="7"/>
     </row>
-    <row r="824" spans="1:10" hidden="1">
+    <row r="824" spans="1:10">
       <c r="A824" s="16">
         <v>2026</v>
       </c>
@@ -55587,7 +55576,7 @@
       </c>
       <c r="J824" s="7"/>
     </row>
-    <row r="825" spans="1:10" hidden="1">
+    <row r="825" spans="1:10">
       <c r="A825" s="16">
         <v>2027</v>
       </c>
@@ -55615,7 +55604,7 @@
       </c>
       <c r="J825" s="7"/>
     </row>
-    <row r="826" spans="1:10" hidden="1">
+    <row r="826" spans="1:10">
       <c r="A826" s="16">
         <v>2028</v>
       </c>
@@ -55643,7 +55632,7 @@
       </c>
       <c r="J826" s="7"/>
     </row>
-    <row r="827" spans="1:10" hidden="1">
+    <row r="827" spans="1:10">
       <c r="A827" s="16">
         <v>2029</v>
       </c>
@@ -55671,7 +55660,7 @@
       </c>
       <c r="J827" s="7"/>
     </row>
-    <row r="828" spans="1:10" hidden="1">
+    <row r="828" spans="1:10">
       <c r="A828" s="16">
         <v>2026</v>
       </c>
@@ -55699,7 +55688,7 @@
       </c>
       <c r="J828" s="7"/>
     </row>
-    <row r="829" spans="1:10" hidden="1">
+    <row r="829" spans="1:10">
       <c r="A829" s="16">
         <v>2027</v>
       </c>
@@ -55727,7 +55716,7 @@
       </c>
       <c r="J829" s="7"/>
     </row>
-    <row r="830" spans="1:10" hidden="1">
+    <row r="830" spans="1:10">
       <c r="A830" s="16">
         <v>2028</v>
       </c>
@@ -55755,7 +55744,7 @@
       </c>
       <c r="J830" s="7"/>
     </row>
-    <row r="831" spans="1:10" hidden="1">
+    <row r="831" spans="1:10">
       <c r="A831" s="16">
         <v>2029</v>
       </c>
@@ -55783,7 +55772,7 @@
       </c>
       <c r="J831" s="7"/>
     </row>
-    <row r="832" spans="1:10" hidden="1">
+    <row r="832" spans="1:10">
       <c r="A832" s="16">
         <v>2026</v>
       </c>
@@ -55811,7 +55800,7 @@
       </c>
       <c r="J832" s="7"/>
     </row>
-    <row r="833" spans="1:10" hidden="1">
+    <row r="833" spans="1:10">
       <c r="A833" s="16">
         <v>2027</v>
       </c>
@@ -55839,7 +55828,7 @@
       </c>
       <c r="J833" s="7"/>
     </row>
-    <row r="834" spans="1:10" hidden="1">
+    <row r="834" spans="1:10">
       <c r="A834" s="16">
         <v>2028</v>
       </c>
@@ -55867,7 +55856,7 @@
       </c>
       <c r="J834" s="7"/>
     </row>
-    <row r="835" spans="1:10" hidden="1">
+    <row r="835" spans="1:10">
       <c r="A835" s="16">
         <v>2029</v>
       </c>
@@ -55895,7 +55884,7 @@
       </c>
       <c r="J835" s="7"/>
     </row>
-    <row r="836" spans="1:10" hidden="1">
+    <row r="836" spans="1:10">
       <c r="A836" s="16">
         <v>2026</v>
       </c>
@@ -55923,7 +55912,7 @@
       </c>
       <c r="J836" s="7"/>
     </row>
-    <row r="837" spans="1:10" hidden="1">
+    <row r="837" spans="1:10">
       <c r="A837" s="16">
         <v>2027</v>
       </c>
@@ -55951,7 +55940,7 @@
       </c>
       <c r="J837" s="7"/>
     </row>
-    <row r="838" spans="1:10" hidden="1">
+    <row r="838" spans="1:10">
       <c r="A838" s="16">
         <v>2028</v>
       </c>
@@ -55979,7 +55968,7 @@
       </c>
       <c r="J838" s="7"/>
     </row>
-    <row r="839" spans="1:10" hidden="1">
+    <row r="839" spans="1:10">
       <c r="A839" s="16">
         <v>2029</v>
       </c>
@@ -56007,7 +55996,7 @@
       </c>
       <c r="J839" s="7"/>
     </row>
-    <row r="840" spans="1:10" hidden="1">
+    <row r="840" spans="1:10">
       <c r="A840" s="16">
         <v>2026</v>
       </c>
@@ -56035,7 +56024,7 @@
       </c>
       <c r="J840" s="7"/>
     </row>
-    <row r="841" spans="1:10" hidden="1">
+    <row r="841" spans="1:10">
       <c r="A841" s="16">
         <v>2027</v>
       </c>
@@ -56063,7 +56052,7 @@
       </c>
       <c r="J841" s="7"/>
     </row>
-    <row r="842" spans="1:10" hidden="1">
+    <row r="842" spans="1:10">
       <c r="A842" s="16">
         <v>2028</v>
       </c>
@@ -56091,7 +56080,7 @@
       </c>
       <c r="J842" s="7"/>
     </row>
-    <row r="843" spans="1:10" hidden="1">
+    <row r="843" spans="1:10">
       <c r="A843" s="16">
         <v>2029</v>
       </c>
@@ -56119,7 +56108,7 @@
       </c>
       <c r="J843" s="7"/>
     </row>
-    <row r="844" spans="1:10" hidden="1">
+    <row r="844" spans="1:10">
       <c r="A844" s="16">
         <v>2026</v>
       </c>
@@ -56147,7 +56136,7 @@
       </c>
       <c r="J844" s="7"/>
     </row>
-    <row r="845" spans="1:10" hidden="1">
+    <row r="845" spans="1:10">
       <c r="A845" s="16">
         <v>2027</v>
       </c>
@@ -56175,7 +56164,7 @@
       </c>
       <c r="J845" s="7"/>
     </row>
-    <row r="846" spans="1:10" hidden="1">
+    <row r="846" spans="1:10">
       <c r="A846" s="16">
         <v>2028</v>
       </c>
@@ -56203,7 +56192,7 @@
       </c>
       <c r="J846" s="7"/>
     </row>
-    <row r="847" spans="1:10" hidden="1">
+    <row r="847" spans="1:10">
       <c r="A847" s="16">
         <v>2029</v>
       </c>
@@ -56259,7 +56248,7 @@
       </c>
       <c r="J848" s="7"/>
     </row>
-    <row r="849" spans="1:10" hidden="1">
+    <row r="849" spans="1:10">
       <c r="A849" s="16">
         <v>2027</v>
       </c>
@@ -56287,7 +56276,7 @@
       </c>
       <c r="J849" s="7"/>
     </row>
-    <row r="850" spans="1:10" hidden="1">
+    <row r="850" spans="1:10">
       <c r="A850" s="16">
         <v>2028</v>
       </c>
@@ -56315,7 +56304,7 @@
       </c>
       <c r="J850" s="7"/>
     </row>
-    <row r="851" spans="1:10" hidden="1">
+    <row r="851" spans="1:10">
       <c r="A851" s="16">
         <v>2029</v>
       </c>
@@ -56371,7 +56360,7 @@
       </c>
       <c r="J852" s="7"/>
     </row>
-    <row r="853" spans="1:10" hidden="1">
+    <row r="853" spans="1:10">
       <c r="A853" s="16">
         <v>2027</v>
       </c>
@@ -56399,7 +56388,7 @@
       </c>
       <c r="J853" s="7"/>
     </row>
-    <row r="854" spans="1:10" hidden="1">
+    <row r="854" spans="1:10">
       <c r="A854" s="16">
         <v>2028</v>
       </c>
@@ -56427,7 +56416,7 @@
       </c>
       <c r="J854" s="7"/>
     </row>
-    <row r="855" spans="1:10" hidden="1">
+    <row r="855" spans="1:10">
       <c r="A855" s="16">
         <v>2029</v>
       </c>
@@ -56483,7 +56472,7 @@
       </c>
       <c r="J856" s="7"/>
     </row>
-    <row r="857" spans="1:10" hidden="1">
+    <row r="857" spans="1:10">
       <c r="A857" s="16">
         <v>2027</v>
       </c>
@@ -56511,7 +56500,7 @@
       </c>
       <c r="J857" s="7"/>
     </row>
-    <row r="858" spans="1:10" hidden="1">
+    <row r="858" spans="1:10">
       <c r="A858" s="16">
         <v>2028</v>
       </c>
@@ -56539,7 +56528,7 @@
       </c>
       <c r="J858" s="7"/>
     </row>
-    <row r="859" spans="1:10" hidden="1">
+    <row r="859" spans="1:10">
       <c r="A859" s="16">
         <v>2029</v>
       </c>
@@ -56595,7 +56584,7 @@
       </c>
       <c r="J860" s="7"/>
     </row>
-    <row r="861" spans="1:10" hidden="1">
+    <row r="861" spans="1:10">
       <c r="A861" s="16">
         <v>2027</v>
       </c>
@@ -56623,7 +56612,7 @@
       </c>
       <c r="J861" s="7"/>
     </row>
-    <row r="862" spans="1:10" hidden="1">
+    <row r="862" spans="1:10">
       <c r="A862" s="16">
         <v>2028</v>
       </c>
@@ -56651,7 +56640,7 @@
       </c>
       <c r="J862" s="7"/>
     </row>
-    <row r="863" spans="1:10" hidden="1">
+    <row r="863" spans="1:10">
       <c r="A863" s="16">
         <v>2029</v>
       </c>
@@ -56707,7 +56696,7 @@
       </c>
       <c r="J864" s="7"/>
     </row>
-    <row r="865" spans="1:10" hidden="1">
+    <row r="865" spans="1:10">
       <c r="A865" s="16">
         <v>2027</v>
       </c>
@@ -56735,7 +56724,7 @@
       </c>
       <c r="J865" s="7"/>
     </row>
-    <row r="866" spans="1:10" hidden="1">
+    <row r="866" spans="1:10">
       <c r="A866" s="16">
         <v>2028</v>
       </c>
@@ -56763,7 +56752,7 @@
       </c>
       <c r="J866" s="7"/>
     </row>
-    <row r="867" spans="1:10" hidden="1">
+    <row r="867" spans="1:10">
       <c r="A867" s="16">
         <v>2029</v>
       </c>
@@ -56819,7 +56808,7 @@
       </c>
       <c r="J868" s="7"/>
     </row>
-    <row r="869" spans="1:10" hidden="1">
+    <row r="869" spans="1:10">
       <c r="A869" s="16">
         <v>2027</v>
       </c>
@@ -56847,7 +56836,7 @@
       </c>
       <c r="J869" s="7"/>
     </row>
-    <row r="870" spans="1:10" hidden="1">
+    <row r="870" spans="1:10">
       <c r="A870" s="16">
         <v>2028</v>
       </c>
@@ -56875,7 +56864,7 @@
       </c>
       <c r="J870" s="7"/>
     </row>
-    <row r="871" spans="1:10" hidden="1">
+    <row r="871" spans="1:10">
       <c r="A871" s="16">
         <v>2029</v>
       </c>
@@ -56931,7 +56920,7 @@
       </c>
       <c r="J872" s="7"/>
     </row>
-    <row r="873" spans="1:10" hidden="1">
+    <row r="873" spans="1:10">
       <c r="A873" s="16">
         <v>2027</v>
       </c>
@@ -56959,7 +56948,7 @@
       </c>
       <c r="J873" s="7"/>
     </row>
-    <row r="874" spans="1:10" hidden="1">
+    <row r="874" spans="1:10">
       <c r="A874" s="16">
         <v>2028</v>
       </c>
@@ -56987,7 +56976,7 @@
       </c>
       <c r="J874" s="7"/>
     </row>
-    <row r="875" spans="1:10" hidden="1">
+    <row r="875" spans="1:10">
       <c r="A875" s="16">
         <v>2029</v>
       </c>
@@ -57043,7 +57032,7 @@
       </c>
       <c r="J876" s="7"/>
     </row>
-    <row r="877" spans="1:10" hidden="1">
+    <row r="877" spans="1:10">
       <c r="A877" s="16">
         <v>2027</v>
       </c>
@@ -57071,7 +57060,7 @@
       </c>
       <c r="J877" s="7"/>
     </row>
-    <row r="878" spans="1:10" hidden="1">
+    <row r="878" spans="1:10">
       <c r="A878" s="16">
         <v>2028</v>
       </c>
@@ -57099,7 +57088,7 @@
       </c>
       <c r="J878" s="7"/>
     </row>
-    <row r="879" spans="1:10" hidden="1">
+    <row r="879" spans="1:10">
       <c r="A879" s="16">
         <v>2029</v>
       </c>
@@ -57155,7 +57144,7 @@
       </c>
       <c r="J880" s="7"/>
     </row>
-    <row r="881" spans="1:10" hidden="1">
+    <row r="881" spans="1:10">
       <c r="A881" s="16">
         <v>2027</v>
       </c>
@@ -57183,7 +57172,7 @@
       </c>
       <c r="J881" s="7"/>
     </row>
-    <row r="882" spans="1:10" hidden="1">
+    <row r="882" spans="1:10">
       <c r="A882" s="16">
         <v>2028</v>
       </c>
@@ -57211,7 +57200,7 @@
       </c>
       <c r="J882" s="7"/>
     </row>
-    <row r="883" spans="1:10" hidden="1">
+    <row r="883" spans="1:10">
       <c r="A883" s="16">
         <v>2029</v>
       </c>
@@ -57267,7 +57256,7 @@
       </c>
       <c r="J884" s="7"/>
     </row>
-    <row r="885" spans="1:10" hidden="1">
+    <row r="885" spans="1:10">
       <c r="A885" s="16">
         <v>2027</v>
       </c>
@@ -57295,7 +57284,7 @@
       </c>
       <c r="J885" s="7"/>
     </row>
-    <row r="886" spans="1:10" hidden="1">
+    <row r="886" spans="1:10">
       <c r="A886" s="16">
         <v>2028</v>
       </c>
@@ -57323,7 +57312,7 @@
       </c>
       <c r="J886" s="7"/>
     </row>
-    <row r="887" spans="1:10" hidden="1">
+    <row r="887" spans="1:10">
       <c r="A887" s="16">
         <v>2029</v>
       </c>
@@ -57379,7 +57368,7 @@
       </c>
       <c r="J888" s="7"/>
     </row>
-    <row r="889" spans="1:10" hidden="1">
+    <row r="889" spans="1:10">
       <c r="A889" s="16">
         <v>2027</v>
       </c>
@@ -57407,7 +57396,7 @@
       </c>
       <c r="J889" s="7"/>
     </row>
-    <row r="890" spans="1:10" hidden="1">
+    <row r="890" spans="1:10">
       <c r="A890" s="16">
         <v>2028</v>
       </c>
@@ -57435,7 +57424,7 @@
       </c>
       <c r="J890" s="7"/>
     </row>
-    <row r="891" spans="1:10" hidden="1">
+    <row r="891" spans="1:10">
       <c r="A891" s="16">
         <v>2029</v>
       </c>
@@ -57491,7 +57480,7 @@
       </c>
       <c r="J892" s="7"/>
     </row>
-    <row r="893" spans="1:10" hidden="1">
+    <row r="893" spans="1:10">
       <c r="A893" s="16">
         <v>2027</v>
       </c>
@@ -57519,7 +57508,7 @@
       </c>
       <c r="J893" s="7"/>
     </row>
-    <row r="894" spans="1:10" hidden="1">
+    <row r="894" spans="1:10">
       <c r="A894" s="16">
         <v>2028</v>
       </c>
@@ -57547,7 +57536,7 @@
       </c>
       <c r="J894" s="7"/>
     </row>
-    <row r="895" spans="1:10" hidden="1">
+    <row r="895" spans="1:10">
       <c r="A895" s="16">
         <v>2029</v>
       </c>
@@ -57603,7 +57592,7 @@
       </c>
       <c r="J896" s="7"/>
     </row>
-    <row r="897" spans="1:10" hidden="1">
+    <row r="897" spans="1:10">
       <c r="A897" s="16">
         <v>2027</v>
       </c>
@@ -57631,7 +57620,7 @@
       </c>
       <c r="J897" s="7"/>
     </row>
-    <row r="898" spans="1:10" hidden="1">
+    <row r="898" spans="1:10">
       <c r="A898" s="16">
         <v>2028</v>
       </c>
@@ -57659,7 +57648,7 @@
       </c>
       <c r="J898" s="7"/>
     </row>
-    <row r="899" spans="1:10" hidden="1">
+    <row r="899" spans="1:10">
       <c r="A899" s="16">
         <v>2029</v>
       </c>
@@ -57715,7 +57704,7 @@
       </c>
       <c r="J900" s="7"/>
     </row>
-    <row r="901" spans="1:10" hidden="1">
+    <row r="901" spans="1:10">
       <c r="A901" s="16">
         <v>2027</v>
       </c>
@@ -57743,7 +57732,7 @@
       </c>
       <c r="J901" s="7"/>
     </row>
-    <row r="902" spans="1:10" hidden="1">
+    <row r="902" spans="1:10">
       <c r="A902" s="16">
         <v>2028</v>
       </c>
@@ -57771,7 +57760,7 @@
       </c>
       <c r="J902" s="7"/>
     </row>
-    <row r="903" spans="1:10" hidden="1">
+    <row r="903" spans="1:10">
       <c r="A903" s="16">
         <v>2029</v>
       </c>
@@ -57827,7 +57816,7 @@
       </c>
       <c r="J904" s="7"/>
     </row>
-    <row r="905" spans="1:10" hidden="1">
+    <row r="905" spans="1:10">
       <c r="A905" s="16">
         <v>2027</v>
       </c>
@@ -57855,7 +57844,7 @@
       </c>
       <c r="J905" s="7"/>
     </row>
-    <row r="906" spans="1:10" hidden="1">
+    <row r="906" spans="1:10">
       <c r="A906" s="16">
         <v>2028</v>
       </c>
@@ -57883,7 +57872,7 @@
       </c>
       <c r="J906" s="7"/>
     </row>
-    <row r="907" spans="1:10" hidden="1">
+    <row r="907" spans="1:10">
       <c r="A907" s="16">
         <v>2029</v>
       </c>
@@ -57939,7 +57928,7 @@
       </c>
       <c r="J908" s="7"/>
     </row>
-    <row r="909" spans="1:10" hidden="1">
+    <row r="909" spans="1:10">
       <c r="A909" s="16">
         <v>2027</v>
       </c>
@@ -57967,7 +57956,7 @@
       </c>
       <c r="J909" s="7"/>
     </row>
-    <row r="910" spans="1:10" hidden="1">
+    <row r="910" spans="1:10">
       <c r="A910" s="16">
         <v>2028</v>
       </c>
@@ -57995,7 +57984,7 @@
       </c>
       <c r="J910" s="7"/>
     </row>
-    <row r="911" spans="1:10" hidden="1">
+    <row r="911" spans="1:10">
       <c r="A911" s="16">
         <v>2029</v>
       </c>
@@ -58051,7 +58040,7 @@
       </c>
       <c r="J912" s="7"/>
     </row>
-    <row r="913" spans="1:10" hidden="1">
+    <row r="913" spans="1:10">
       <c r="A913" s="16">
         <v>2027</v>
       </c>
@@ -58079,7 +58068,7 @@
       </c>
       <c r="J913" s="7"/>
     </row>
-    <row r="914" spans="1:10" hidden="1">
+    <row r="914" spans="1:10">
       <c r="A914" s="16">
         <v>2028</v>
       </c>
@@ -58107,7 +58096,7 @@
       </c>
       <c r="J914" s="7"/>
     </row>
-    <row r="915" spans="1:10" hidden="1">
+    <row r="915" spans="1:10">
       <c r="A915" s="16">
         <v>2029</v>
       </c>
@@ -58163,7 +58152,7 @@
       </c>
       <c r="J916" s="7"/>
     </row>
-    <row r="917" spans="1:10" hidden="1">
+    <row r="917" spans="1:10">
       <c r="A917" s="16">
         <v>2027</v>
       </c>
@@ -58191,7 +58180,7 @@
       </c>
       <c r="J917" s="7"/>
     </row>
-    <row r="918" spans="1:10" hidden="1">
+    <row r="918" spans="1:10">
       <c r="A918" s="16">
         <v>2028</v>
       </c>
@@ -58219,7 +58208,7 @@
       </c>
       <c r="J918" s="7"/>
     </row>
-    <row r="919" spans="1:10" hidden="1">
+    <row r="919" spans="1:10">
       <c r="A919" s="16">
         <v>2029</v>
       </c>
@@ -58275,7 +58264,7 @@
       </c>
       <c r="J920" s="7"/>
     </row>
-    <row r="921" spans="1:10" hidden="1">
+    <row r="921" spans="1:10">
       <c r="A921" s="16">
         <v>2027</v>
       </c>
@@ -58303,7 +58292,7 @@
       </c>
       <c r="J921" s="7"/>
     </row>
-    <row r="922" spans="1:10" hidden="1">
+    <row r="922" spans="1:10">
       <c r="A922" s="16">
         <v>2028</v>
       </c>
@@ -58331,7 +58320,7 @@
       </c>
       <c r="J922" s="7"/>
     </row>
-    <row r="923" spans="1:10" hidden="1">
+    <row r="923" spans="1:10">
       <c r="A923" s="16">
         <v>2029</v>
       </c>
@@ -58387,7 +58376,7 @@
       </c>
       <c r="J924" s="7"/>
     </row>
-    <row r="925" spans="1:10" hidden="1">
+    <row r="925" spans="1:10">
       <c r="A925" s="16">
         <v>2027</v>
       </c>
@@ -58415,7 +58404,7 @@
       </c>
       <c r="J925" s="7"/>
     </row>
-    <row r="926" spans="1:10" hidden="1">
+    <row r="926" spans="1:10">
       <c r="A926" s="16">
         <v>2028</v>
       </c>
@@ -58443,7 +58432,7 @@
       </c>
       <c r="J926" s="7"/>
     </row>
-    <row r="927" spans="1:10" hidden="1">
+    <row r="927" spans="1:10">
       <c r="A927" s="16">
         <v>2029</v>
       </c>
@@ -58499,7 +58488,7 @@
       </c>
       <c r="J928" s="7"/>
     </row>
-    <row r="929" spans="1:10" hidden="1">
+    <row r="929" spans="1:10">
       <c r="A929" s="16">
         <v>2027</v>
       </c>
@@ -58527,7 +58516,7 @@
       </c>
       <c r="J929" s="7"/>
     </row>
-    <row r="930" spans="1:10" hidden="1">
+    <row r="930" spans="1:10">
       <c r="A930" s="16">
         <v>2028</v>
       </c>
@@ -58555,7 +58544,7 @@
       </c>
       <c r="J930" s="7"/>
     </row>
-    <row r="931" spans="1:10" hidden="1">
+    <row r="931" spans="1:10">
       <c r="A931" s="16">
         <v>2029</v>
       </c>
@@ -58611,7 +58600,7 @@
       </c>
       <c r="J932" s="7"/>
     </row>
-    <row r="933" spans="1:10" hidden="1">
+    <row r="933" spans="1:10">
       <c r="A933" s="16">
         <v>2027</v>
       </c>
@@ -58639,7 +58628,7 @@
       </c>
       <c r="J933" s="7"/>
     </row>
-    <row r="934" spans="1:10" hidden="1">
+    <row r="934" spans="1:10">
       <c r="A934" s="16">
         <v>2028</v>
       </c>
@@ -58667,7 +58656,7 @@
       </c>
       <c r="J934" s="7"/>
     </row>
-    <row r="935" spans="1:10" hidden="1">
+    <row r="935" spans="1:10">
       <c r="A935" s="16">
         <v>2029</v>
       </c>
@@ -58723,7 +58712,7 @@
       </c>
       <c r="J936" s="7"/>
     </row>
-    <row r="937" spans="1:10" hidden="1">
+    <row r="937" spans="1:10">
       <c r="A937" s="16">
         <v>2027</v>
       </c>
@@ -58751,7 +58740,7 @@
       </c>
       <c r="J937" s="7"/>
     </row>
-    <row r="938" spans="1:10" hidden="1">
+    <row r="938" spans="1:10">
       <c r="A938" s="16">
         <v>2028</v>
       </c>
@@ -58779,7 +58768,7 @@
       </c>
       <c r="J938" s="7"/>
     </row>
-    <row r="939" spans="1:10" hidden="1">
+    <row r="939" spans="1:10">
       <c r="A939" s="16">
         <v>2029</v>
       </c>
@@ -58835,7 +58824,7 @@
       </c>
       <c r="J940" s="7"/>
     </row>
-    <row r="941" spans="1:10" hidden="1">
+    <row r="941" spans="1:10">
       <c r="A941" s="16">
         <v>2027</v>
       </c>
@@ -58863,7 +58852,7 @@
       </c>
       <c r="J941" s="7"/>
     </row>
-    <row r="942" spans="1:10" hidden="1">
+    <row r="942" spans="1:10">
       <c r="A942" s="16">
         <v>2028</v>
       </c>
@@ -58891,7 +58880,7 @@
       </c>
       <c r="J942" s="7"/>
     </row>
-    <row r="943" spans="1:10" hidden="1">
+    <row r="943" spans="1:10">
       <c r="A943" s="16">
         <v>2029</v>
       </c>
@@ -58947,7 +58936,7 @@
       </c>
       <c r="J944" s="7"/>
     </row>
-    <row r="945" spans="1:10" hidden="1">
+    <row r="945" spans="1:10">
       <c r="A945" s="16">
         <v>2027</v>
       </c>
@@ -58975,7 +58964,7 @@
       </c>
       <c r="J945" s="7"/>
     </row>
-    <row r="946" spans="1:10" hidden="1">
+    <row r="946" spans="1:10">
       <c r="A946" s="16">
         <v>2028</v>
       </c>
@@ -59003,7 +58992,7 @@
       </c>
       <c r="J946" s="7"/>
     </row>
-    <row r="947" spans="1:10" hidden="1">
+    <row r="947" spans="1:10">
       <c r="A947" s="16">
         <v>2029</v>
       </c>
@@ -59059,7 +59048,7 @@
       </c>
       <c r="J948" s="7"/>
     </row>
-    <row r="949" spans="1:10" hidden="1">
+    <row r="949" spans="1:10">
       <c r="A949" s="16">
         <v>2027</v>
       </c>
@@ -59087,7 +59076,7 @@
       </c>
       <c r="J949" s="7"/>
     </row>
-    <row r="950" spans="1:10" hidden="1">
+    <row r="950" spans="1:10">
       <c r="A950" s="16">
         <v>2028</v>
       </c>
@@ -59115,7 +59104,7 @@
       </c>
       <c r="J950" s="7"/>
     </row>
-    <row r="951" spans="1:10" hidden="1">
+    <row r="951" spans="1:10">
       <c r="A951" s="16">
         <v>2029</v>
       </c>
@@ -59171,7 +59160,7 @@
       </c>
       <c r="J952" s="7"/>
     </row>
-    <row r="953" spans="1:10" hidden="1">
+    <row r="953" spans="1:10">
       <c r="A953" s="16">
         <v>2027</v>
       </c>
@@ -59199,7 +59188,7 @@
       </c>
       <c r="J953" s="7"/>
     </row>
-    <row r="954" spans="1:10" hidden="1">
+    <row r="954" spans="1:10">
       <c r="A954" s="16">
         <v>2028</v>
       </c>
@@ -59227,7 +59216,7 @@
       </c>
       <c r="J954" s="7"/>
     </row>
-    <row r="955" spans="1:10" hidden="1">
+    <row r="955" spans="1:10">
       <c r="A955" s="16">
         <v>2029</v>
       </c>
@@ -59283,7 +59272,7 @@
       </c>
       <c r="J956" s="7"/>
     </row>
-    <row r="957" spans="1:10" hidden="1">
+    <row r="957" spans="1:10">
       <c r="A957" s="16">
         <v>2027</v>
       </c>
@@ -59311,7 +59300,7 @@
       </c>
       <c r="J957" s="7"/>
     </row>
-    <row r="958" spans="1:10" hidden="1">
+    <row r="958" spans="1:10">
       <c r="A958" s="16">
         <v>2028</v>
       </c>
@@ -59339,7 +59328,7 @@
       </c>
       <c r="J958" s="7"/>
     </row>
-    <row r="959" spans="1:10" hidden="1">
+    <row r="959" spans="1:10">
       <c r="A959" s="16">
         <v>2029</v>
       </c>
@@ -59395,7 +59384,7 @@
       </c>
       <c r="J960" s="7"/>
     </row>
-    <row r="961" spans="1:10" hidden="1">
+    <row r="961" spans="1:10">
       <c r="A961" s="16">
         <v>2027</v>
       </c>
@@ -59423,7 +59412,7 @@
       </c>
       <c r="J961" s="7"/>
     </row>
-    <row r="962" spans="1:10" hidden="1">
+    <row r="962" spans="1:10">
       <c r="A962" s="16">
         <v>2028</v>
       </c>
@@ -59451,7 +59440,7 @@
       </c>
       <c r="J962" s="7"/>
     </row>
-    <row r="963" spans="1:10" hidden="1">
+    <row r="963" spans="1:10">
       <c r="A963" s="16">
         <v>2029</v>
       </c>
@@ -59507,7 +59496,7 @@
       </c>
       <c r="J964" s="7"/>
     </row>
-    <row r="965" spans="1:10" hidden="1">
+    <row r="965" spans="1:10">
       <c r="A965" s="16">
         <v>2027</v>
       </c>
@@ -59535,7 +59524,7 @@
       </c>
       <c r="J965" s="7"/>
     </row>
-    <row r="966" spans="1:10" hidden="1">
+    <row r="966" spans="1:10">
       <c r="A966" s="16">
         <v>2028</v>
       </c>
@@ -59563,7 +59552,7 @@
       </c>
       <c r="J966" s="7"/>
     </row>
-    <row r="967" spans="1:10" hidden="1">
+    <row r="967" spans="1:10">
       <c r="A967" s="16">
         <v>2029</v>
       </c>
@@ -59619,7 +59608,7 @@
       </c>
       <c r="J968" s="7"/>
     </row>
-    <row r="969" spans="1:10" hidden="1">
+    <row r="969" spans="1:10">
       <c r="A969" s="16">
         <v>2027</v>
       </c>
@@ -59647,7 +59636,7 @@
       </c>
       <c r="J969" s="7"/>
     </row>
-    <row r="970" spans="1:10" hidden="1">
+    <row r="970" spans="1:10">
       <c r="A970" s="16">
         <v>2028</v>
       </c>
@@ -59675,7 +59664,7 @@
       </c>
       <c r="J970" s="7"/>
     </row>
-    <row r="971" spans="1:10" hidden="1">
+    <row r="971" spans="1:10">
       <c r="A971" s="16">
         <v>2029</v>
       </c>
@@ -59703,7 +59692,7 @@
       </c>
       <c r="J971" s="7"/>
     </row>
-    <row r="972" spans="1:10" hidden="1">
+    <row r="972" spans="1:10">
       <c r="A972" s="5">
         <v>2026</v>
       </c>
@@ -59731,7 +59720,7 @@
       </c>
       <c r="J972" s="7"/>
     </row>
-    <row r="973" spans="1:10" hidden="1">
+    <row r="973" spans="1:10">
       <c r="A973" s="5">
         <v>2026</v>
       </c>
@@ -59759,7 +59748,7 @@
       </c>
       <c r="J973" s="7"/>
     </row>
-    <row r="974" spans="1:10" hidden="1">
+    <row r="974" spans="1:10">
       <c r="A974" s="5">
         <v>2027</v>
       </c>
@@ -59787,7 +59776,7 @@
       </c>
       <c r="J974" s="7"/>
     </row>
-    <row r="975" spans="1:10" hidden="1">
+    <row r="975" spans="1:10">
       <c r="A975" s="5">
         <v>2027</v>
       </c>
@@ -59815,7 +59804,7 @@
       </c>
       <c r="J975" s="7"/>
     </row>
-    <row r="976" spans="1:10" hidden="1">
+    <row r="976" spans="1:10">
       <c r="A976" s="5">
         <v>2028</v>
       </c>
@@ -59843,7 +59832,7 @@
       </c>
       <c r="J976" s="7"/>
     </row>
-    <row r="977" spans="1:10" hidden="1">
+    <row r="977" spans="1:10">
       <c r="A977" s="5">
         <v>2028</v>
       </c>
@@ -59871,7 +59860,7 @@
       </c>
       <c r="J977" s="7"/>
     </row>
-    <row r="978" spans="1:10" hidden="1">
+    <row r="978" spans="1:10">
       <c r="A978" s="5">
         <v>2029</v>
       </c>
@@ -59899,7 +59888,7 @@
       </c>
       <c r="J978" s="7"/>
     </row>
-    <row r="979" spans="1:10" hidden="1">
+    <row r="979" spans="1:10">
       <c r="A979" s="5">
         <v>2029</v>
       </c>
@@ -59927,7 +59916,7 @@
       </c>
       <c r="J979" s="7"/>
     </row>
-    <row r="980" spans="1:10" hidden="1">
+    <row r="980" spans="1:10">
       <c r="A980" s="5"/>
       <c r="B980" s="6"/>
       <c r="C980" s="6"/>
@@ -59945,7 +59934,7 @@
       </c>
       <c r="J980" s="7"/>
     </row>
-    <row r="981" spans="1:10" hidden="1">
+    <row r="981" spans="1:10">
       <c r="A981" s="5"/>
       <c r="B981" s="6"/>
       <c r="C981" s="6"/>
@@ -59963,7 +59952,7 @@
       </c>
       <c r="J981" s="7"/>
     </row>
-    <row r="982" spans="1:10" hidden="1">
+    <row r="982" spans="1:10">
       <c r="A982" s="5"/>
       <c r="B982" s="6"/>
       <c r="C982" s="6"/>
@@ -59981,7 +59970,7 @@
       </c>
       <c r="J982" s="7"/>
     </row>
-    <row r="983" spans="1:10" hidden="1">
+    <row r="983" spans="1:10">
       <c r="A983" s="5"/>
       <c r="B983" s="6"/>
       <c r="C983" s="6"/>
@@ -59999,7 +59988,7 @@
       </c>
       <c r="J983" s="7"/>
     </row>
-    <row r="984" spans="1:10" hidden="1">
+    <row r="984" spans="1:10">
       <c r="A984" s="5"/>
       <c r="B984" s="6"/>
       <c r="C984" s="6"/>
@@ -60017,7 +60006,7 @@
       </c>
       <c r="J984" s="7"/>
     </row>
-    <row r="985" spans="1:10" hidden="1">
+    <row r="985" spans="1:10">
       <c r="A985" s="5"/>
       <c r="B985" s="6"/>
       <c r="C985" s="6"/>
@@ -60035,7 +60024,7 @@
       </c>
       <c r="J985" s="7"/>
     </row>
-    <row r="986" spans="1:10" hidden="1">
+    <row r="986" spans="1:10">
       <c r="A986" s="5"/>
       <c r="B986" s="6"/>
       <c r="C986" s="6"/>
@@ -60053,7 +60042,7 @@
       </c>
       <c r="J986" s="7"/>
     </row>
-    <row r="987" spans="1:10" hidden="1">
+    <row r="987" spans="1:10">
       <c r="A987" s="5"/>
       <c r="B987" s="6"/>
       <c r="C987" s="6"/>
@@ -60071,7 +60060,7 @@
       </c>
       <c r="J987" s="7"/>
     </row>
-    <row r="988" spans="1:10" hidden="1">
+    <row r="988" spans="1:10">
       <c r="A988" s="5"/>
       <c r="B988" s="6"/>
       <c r="C988" s="6"/>
@@ -60089,7 +60078,7 @@
       </c>
       <c r="J988" s="7"/>
     </row>
-    <row r="989" spans="1:10" hidden="1">
+    <row r="989" spans="1:10">
       <c r="A989" s="5"/>
       <c r="B989" s="6"/>
       <c r="C989" s="6"/>
@@ -60107,7 +60096,7 @@
       </c>
       <c r="J989" s="7"/>
     </row>
-    <row r="990" spans="1:10" hidden="1">
+    <row r="990" spans="1:10">
       <c r="A990" s="5"/>
       <c r="B990" s="6"/>
       <c r="C990" s="6"/>
@@ -60125,7 +60114,7 @@
       </c>
       <c r="J990" s="7"/>
     </row>
-    <row r="991" spans="1:10" hidden="1">
+    <row r="991" spans="1:10">
       <c r="A991" s="5"/>
       <c r="B991" s="6"/>
       <c r="C991" s="6"/>
@@ -60143,7 +60132,7 @@
       </c>
       <c r="J991" s="7"/>
     </row>
-    <row r="992" spans="1:10" hidden="1">
+    <row r="992" spans="1:10">
       <c r="A992" s="5"/>
       <c r="B992" s="6"/>
       <c r="C992" s="6"/>
@@ -60161,7 +60150,7 @@
       </c>
       <c r="J992" s="7"/>
     </row>
-    <row r="993" spans="1:10" hidden="1">
+    <row r="993" spans="1:10">
       <c r="A993" s="5"/>
       <c r="B993" s="6"/>
       <c r="C993" s="6"/>
@@ -60179,7 +60168,7 @@
       </c>
       <c r="J993" s="7"/>
     </row>
-    <row r="994" spans="1:10" hidden="1">
+    <row r="994" spans="1:10">
       <c r="A994" s="5"/>
       <c r="B994" s="6"/>
       <c r="C994" s="6"/>
@@ -60197,7 +60186,7 @@
       </c>
       <c r="J994" s="7"/>
     </row>
-    <row r="995" spans="1:10" hidden="1">
+    <row r="995" spans="1:10">
       <c r="A995" s="5"/>
       <c r="B995" s="6"/>
       <c r="C995" s="6"/>
@@ -60215,7 +60204,7 @@
       </c>
       <c r="J995" s="7"/>
     </row>
-    <row r="996" spans="1:10" hidden="1">
+    <row r="996" spans="1:10">
       <c r="A996" s="5"/>
       <c r="B996" s="6"/>
       <c r="C996" s="6"/>
@@ -60233,7 +60222,7 @@
       </c>
       <c r="J996" s="7"/>
     </row>
-    <row r="997" spans="1:10" hidden="1">
+    <row r="997" spans="1:10">
       <c r="A997" s="5"/>
       <c r="B997" s="6"/>
       <c r="C997" s="6"/>
@@ -60251,7 +60240,7 @@
       </c>
       <c r="J997" s="7"/>
     </row>
-    <row r="998" spans="1:10" hidden="1">
+    <row r="998" spans="1:10">
       <c r="A998" s="5"/>
       <c r="B998" s="6"/>
       <c r="C998" s="6"/>
@@ -60269,7 +60258,7 @@
       </c>
       <c r="J998" s="7"/>
     </row>
-    <row r="999" spans="1:10" hidden="1">
+    <row r="999" spans="1:10">
       <c r="A999" s="5"/>
       <c r="B999" s="6"/>
       <c r="C999" s="6"/>
@@ -60287,7 +60276,7 @@
       </c>
       <c r="J999" s="7"/>
     </row>
-    <row r="1000" spans="1:10" hidden="1">
+    <row r="1000" spans="1:10">
       <c r="A1000" s="8"/>
       <c r="B1000" s="9"/>
       <c r="C1000" s="9"/>
@@ -60331,32 +60320,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="5.5" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="41"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>108</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="4" spans="1:10" ht="6.4" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -65948,32 +65937,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="5.5" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="42"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
-      <c r="J1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="44"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
+      <c r="J1" s="40"/>
     </row>
     <row r="2" spans="1:10" ht="6.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
-      <c r="J2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
     </row>
     <row r="4" spans="1:10" ht="6.4" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -76275,28 +76264,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="5.5" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:8" ht="6.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="4" spans="1:8" ht="6.4" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -81002,30 +80991,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="5.5" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>124</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="42"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
-      <c r="I1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="44"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
+      <c r="I1" s="40"/>
     </row>
     <row r="2" spans="1:9" ht="6.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>125</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-      <c r="I2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
     </row>
     <row r="4" spans="1:9" ht="6.4" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -88445,28 +88434,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="5.5" customHeight="1">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="41" t="s">
         <v>128</v>
       </c>
-      <c r="B1" s="39"/>
-      <c r="C1" s="39"/>
-      <c r="D1" s="39"/>
-      <c r="E1" s="39"/>
-      <c r="F1" s="39"/>
-      <c r="G1" s="39"/>
-      <c r="H1" s="39"/>
+      <c r="B1" s="40"/>
+      <c r="C1" s="40"/>
+      <c r="D1" s="40"/>
+      <c r="E1" s="40"/>
+      <c r="F1" s="40"/>
+      <c r="G1" s="40"/>
+      <c r="H1" s="40"/>
     </row>
     <row r="2" spans="1:8" ht="6.75" customHeight="1">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="42" t="s">
         <v>129</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
+      <c r="B2" s="40"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
     </row>
     <row r="4" spans="1:8" ht="6.4" customHeight="1">
       <c r="A4" s="1" t="s">
@@ -88544,11 +88533,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="4.9000000000000004" customHeight="1">
-      <c r="A1" s="44" t="s">
+      <c r="A1" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="B1" s="45"/>
-      <c r="C1" s="45"/>
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
       <c r="E1" s="30" t="s">
         <v>639</v>
       </c>
